--- a/TimesheetBankJakarta_Anggit_Ari_Utomo_2.xlsx
+++ b/TimesheetBankJakarta_Anggit_Ari_Utomo_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vAA0120516\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\anggit\Documents\absen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040CA25B-6596-4399-A385-5DEBFD43A253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665529B1-CBC4-4C07-A5D2-9DC1FA0A8CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,16 +18,11 @@
     <sheet name="12 September - 11 Oktober 2023" sheetId="5" state="hidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="QveG/wJEr2tev23/2ioyQYA6m1Z6YzDTIKhi+yxqRFU="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="154">
   <si>
     <t>Lokasi Penempatan</t>
   </si>
@@ -2133,7 +2128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2467,6 +2462,30 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="18" fillId="6" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="18" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2476,48 +2495,144 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2533,101 +2648,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2659,79 +2705,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="18" fillId="6" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="18" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5456,27 +5454,27 @@
     </row>
     <row r="2" spans="1:12" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="137"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="135" t="s">
+      <c r="B2" s="136"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126"/>
-      <c r="H2" s="126"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
       <c r="I2" s="140"/>
       <c r="J2" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="126"/>
-      <c r="L2" s="127"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="134"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
       <c r="E3" s="141"/>
       <c r="F3" s="139"/>
       <c r="G3" s="139"/>
@@ -5488,9 +5486,9 @@
     </row>
     <row r="4" spans="1:12" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="128"/>
       <c r="E4" s="145" t="s">
         <v>144</v>
       </c>
@@ -5518,9 +5516,9 @@
       <c r="G5" s="146"/>
       <c r="H5" s="146"/>
       <c r="I5" s="147"/>
-      <c r="J5" s="117"/>
-      <c r="K5" s="117"/>
-      <c r="L5" s="116"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="123"/>
     </row>
     <row r="6" spans="1:12" ht="14.4">
       <c r="A6" s="1"/>
@@ -5538,9 +5536,9 @@
       <c r="G6" s="149"/>
       <c r="H6" s="149"/>
       <c r="I6" s="153"/>
-      <c r="J6" s="117"/>
-      <c r="K6" s="117"/>
-      <c r="L6" s="116"/>
+      <c r="J6" s="128"/>
+      <c r="K6" s="128"/>
+      <c r="L6" s="123"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1">
       <c r="A7" s="1"/>
@@ -5551,24 +5549,24 @@
         <v>6</v>
       </c>
       <c r="D7" s="158"/>
-      <c r="E7" s="135" t="s">
+      <c r="E7" s="132" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="140"/>
       <c r="G7" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="133" t="s">
+      <c r="H7" s="130" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="133" t="s">
+      <c r="I7" s="130" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="135" t="s">
+      <c r="J7" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="126"/>
-      <c r="L7" s="127"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="134"/>
     </row>
     <row r="8" spans="1:12" thickBot="1">
       <c r="A8" s="1"/>
@@ -5579,14 +5577,14 @@
       <c r="D8" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="136"/>
+      <c r="E8" s="135"/>
       <c r="F8" s="159"/>
-      <c r="G8" s="134"/>
-      <c r="H8" s="134"/>
-      <c r="I8" s="134"/>
-      <c r="J8" s="136"/>
-      <c r="K8" s="124"/>
-      <c r="L8" s="120"/>
+      <c r="G8" s="131"/>
+      <c r="H8" s="131"/>
+      <c r="I8" s="131"/>
+      <c r="J8" s="135"/>
+      <c r="K8" s="126"/>
+      <c r="L8" s="125"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1">
       <c r="A9" s="9"/>
@@ -5613,11 +5611,11 @@
       <c r="I9" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J9" s="111" t="s">
+      <c r="J9" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K9" s="112"/>
-      <c r="L9" s="113"/>
+      <c r="K9" s="120"/>
+      <c r="L9" s="121"/>
     </row>
     <row r="10" spans="1:12" thickBot="1">
       <c r="A10" s="9"/>
@@ -5680,11 +5678,11 @@
       <c r="I12" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J12" s="111" t="s">
+      <c r="J12" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K12" s="112"/>
-      <c r="L12" s="113"/>
+      <c r="K12" s="120"/>
+      <c r="L12" s="121"/>
     </row>
     <row r="13" spans="1:12" thickBot="1">
       <c r="A13" s="9"/>
@@ -5711,11 +5709,11 @@
       <c r="I13" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J13" s="111" t="s">
+      <c r="J13" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K13" s="112"/>
-      <c r="L13" s="113"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="121"/>
     </row>
     <row r="14" spans="1:12" thickBot="1">
       <c r="A14" s="9"/>
@@ -5742,11 +5740,11 @@
       <c r="I14" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J14" s="111" t="s">
+      <c r="J14" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K14" s="112"/>
-      <c r="L14" s="113"/>
+      <c r="K14" s="120"/>
+      <c r="L14" s="121"/>
     </row>
     <row r="15" spans="1:12" thickBot="1">
       <c r="A15" s="9"/>
@@ -5773,11 +5771,11 @@
       <c r="I15" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J15" s="111" t="s">
+      <c r="J15" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K15" s="112"/>
-      <c r="L15" s="113"/>
+      <c r="K15" s="120"/>
+      <c r="L15" s="121"/>
     </row>
     <row r="16" spans="1:12" thickBot="1">
       <c r="A16" s="9"/>
@@ -5804,11 +5802,11 @@
       <c r="I16" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J16" s="111" t="s">
+      <c r="J16" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K16" s="112"/>
-      <c r="L16" s="113"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="121"/>
     </row>
     <row r="17" spans="1:12" thickBot="1">
       <c r="A17" s="9"/>
@@ -5860,18 +5858,22 @@
       <c r="E19" s="105">
         <v>0.32291666666666669</v>
       </c>
-      <c r="F19" s="8"/>
+      <c r="F19" s="8">
+        <v>0.7368055555555556</v>
+      </c>
       <c r="G19" s="11">
         <f t="shared" ref="G19:G23" si="1">ROUND(MOD(F19-E19-TIME(1,0,0),1)*24,1)</f>
-        <v>15.3</v>
+        <v>8.9</v>
       </c>
       <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="111" t="s">
+      <c r="I19" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="J19" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K19" s="112"/>
-      <c r="L19" s="113"/>
+      <c r="K19" s="120"/>
+      <c r="L19" s="121"/>
     </row>
     <row r="20" spans="1:12" thickBot="1">
       <c r="A20" s="9"/>
@@ -5884,19 +5886,25 @@
       <c r="D20" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E20" s="105"/>
-      <c r="F20" s="8"/>
+      <c r="E20" s="105">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0.79513888888888884</v>
+      </c>
       <c r="G20" s="11">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="111" t="s">
+      <c r="I20" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="J20" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K20" s="112"/>
-      <c r="L20" s="113"/>
+      <c r="K20" s="120"/>
+      <c r="L20" s="121"/>
     </row>
     <row r="21" spans="1:12" thickBot="1">
       <c r="A21" s="9"/>
@@ -5909,19 +5917,23 @@
       <c r="D21" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E21" s="105"/>
+      <c r="E21" s="105">
+        <v>0.37291666666666667</v>
+      </c>
       <c r="F21" s="8"/>
       <c r="G21" s="11">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>14.1</v>
       </c>
       <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="111" t="s">
+      <c r="I21" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="J21" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K21" s="112"/>
-      <c r="L21" s="113"/>
+      <c r="K21" s="120"/>
+      <c r="L21" s="121"/>
     </row>
     <row r="22" spans="1:12" thickBot="1">
       <c r="A22" s="9"/>
@@ -5941,12 +5953,14 @@
         <v>23</v>
       </c>
       <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="111" t="s">
+      <c r="I22" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="J22" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K22" s="112"/>
-      <c r="L22" s="113"/>
+      <c r="K22" s="120"/>
+      <c r="L22" s="121"/>
     </row>
     <row r="23" spans="1:12" thickBot="1">
       <c r="A23" s="9"/>
@@ -5966,12 +5980,14 @@
         <v>23</v>
       </c>
       <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="111" t="s">
+      <c r="I23" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="J23" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K23" s="112"/>
-      <c r="L23" s="113"/>
+      <c r="K23" s="120"/>
+      <c r="L23" s="121"/>
     </row>
     <row r="24" spans="1:12" thickBot="1">
       <c r="A24" s="9"/>
@@ -6027,12 +6043,14 @@
         <v>23</v>
       </c>
       <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="111" t="s">
+      <c r="I26" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="J26" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K26" s="112"/>
-      <c r="L26" s="113"/>
+      <c r="K26" s="120"/>
+      <c r="L26" s="121"/>
     </row>
     <row r="27" spans="1:12" thickBot="1">
       <c r="A27" s="9"/>
@@ -6052,12 +6070,14 @@
         <v>23</v>
       </c>
       <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="111" t="s">
+      <c r="I27" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="J27" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K27" s="112"/>
-      <c r="L27" s="113"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="121"/>
     </row>
     <row r="28" spans="1:12" thickBot="1">
       <c r="A28" s="9"/>
@@ -6077,12 +6097,14 @@
         <v>23</v>
       </c>
       <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="111" t="s">
+      <c r="I28" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="J28" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K28" s="112"/>
-      <c r="L28" s="113"/>
+      <c r="K28" s="120"/>
+      <c r="L28" s="121"/>
     </row>
     <row r="29" spans="1:12" thickBot="1">
       <c r="A29" s="9"/>
@@ -6102,12 +6124,14 @@
         <v>23</v>
       </c>
       <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="111" t="s">
+      <c r="I29" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="J29" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K29" s="112"/>
-      <c r="L29" s="113"/>
+      <c r="K29" s="120"/>
+      <c r="L29" s="121"/>
     </row>
     <row r="30" spans="1:12" thickBot="1">
       <c r="A30" s="9"/>
@@ -6127,12 +6151,14 @@
         <v>23</v>
       </c>
       <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="111" t="s">
+      <c r="I30" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="J30" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K30" s="112"/>
-      <c r="L30" s="113"/>
+      <c r="K30" s="120"/>
+      <c r="L30" s="121"/>
     </row>
     <row r="31" spans="1:12" thickBot="1">
       <c r="A31" s="9"/>
@@ -6172,21 +6198,21 @@
     </row>
     <row r="33" spans="1:12" thickBot="1">
       <c r="A33" s="9"/>
-      <c r="B33" s="192">
+      <c r="B33" s="111">
         <v>46251</v>
       </c>
-      <c r="C33" s="193"/>
-      <c r="D33" s="193"/>
-      <c r="E33" s="194"/>
-      <c r="F33" s="193"/>
-      <c r="G33" s="195"/>
-      <c r="H33" s="196" t="s">
+      <c r="C33" s="112"/>
+      <c r="D33" s="112"/>
+      <c r="E33" s="113"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="114"/>
+      <c r="H33" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="I33" s="196"/>
-      <c r="J33" s="197"/>
-      <c r="K33" s="198"/>
-      <c r="L33" s="199"/>
+      <c r="I33" s="115"/>
+      <c r="J33" s="116"/>
+      <c r="K33" s="117"/>
+      <c r="L33" s="118"/>
     </row>
     <row r="34" spans="1:12" thickBot="1">
       <c r="A34" s="9"/>
@@ -6206,12 +6232,14 @@
         <v>23</v>
       </c>
       <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="111" t="s">
+      <c r="I34" s="200" t="s">
+        <v>149</v>
+      </c>
+      <c r="J34" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K34" s="112"/>
-      <c r="L34" s="113"/>
+      <c r="K34" s="120"/>
+      <c r="L34" s="121"/>
     </row>
     <row r="35" spans="1:12" thickBot="1">
       <c r="A35" s="9"/>
@@ -6231,12 +6259,14 @@
         <v>23</v>
       </c>
       <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="111" t="s">
+      <c r="I35" s="200" t="s">
+        <v>149</v>
+      </c>
+      <c r="J35" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K35" s="112"/>
-      <c r="L35" s="113"/>
+      <c r="K35" s="120"/>
+      <c r="L35" s="121"/>
     </row>
     <row r="36" spans="1:12" thickBot="1">
       <c r="A36" s="9"/>
@@ -6256,12 +6286,14 @@
         <v>23</v>
       </c>
       <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="111" t="s">
+      <c r="I36" s="200" t="s">
+        <v>149</v>
+      </c>
+      <c r="J36" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K36" s="112"/>
-      <c r="L36" s="113"/>
+      <c r="K36" s="120"/>
+      <c r="L36" s="121"/>
     </row>
     <row r="37" spans="1:12" thickBot="1">
       <c r="A37" s="9"/>
@@ -6281,12 +6313,14 @@
         <v>23</v>
       </c>
       <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="111" t="s">
+      <c r="I37" s="200" t="s">
+        <v>149</v>
+      </c>
+      <c r="J37" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="K37" s="112"/>
-      <c r="L37" s="113"/>
+      <c r="K37" s="120"/>
+      <c r="L37" s="121"/>
     </row>
     <row r="38" spans="1:12" thickBot="1">
       <c r="A38" s="9"/>
@@ -6335,16 +6369,16 @@
     </row>
     <row r="43" spans="1:12" ht="18" customHeight="1" thickBot="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="128" t="s">
+      <c r="B43" s="168" t="s">
         <v>13</v>
       </c>
-      <c r="C43" s="129"/>
-      <c r="D43" s="129"/>
-      <c r="E43" s="129"/>
-      <c r="F43" s="130"/>
+      <c r="C43" s="169"/>
+      <c r="D43" s="169"/>
+      <c r="E43" s="169"/>
+      <c r="F43" s="170"/>
       <c r="G43" s="18">
         <f>SUM(G9:G39)</f>
-        <v>365.6</v>
+        <v>337.29999999999995</v>
       </c>
       <c r="H43" s="19"/>
       <c r="I43" s="19"/>
@@ -6362,13 +6396,13 @@
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
       <c r="G44" s="23"/>
-      <c r="H44" s="125" t="s">
+      <c r="H44" s="167" t="s">
         <v>15</v>
       </c>
-      <c r="I44" s="126"/>
-      <c r="J44" s="126"/>
-      <c r="K44" s="126"/>
-      <c r="L44" s="127"/>
+      <c r="I44" s="133"/>
+      <c r="J44" s="133"/>
+      <c r="K44" s="133"/>
+      <c r="L44" s="134"/>
     </row>
     <row r="45" spans="1:12" ht="20.25" customHeight="1">
       <c r="A45" s="1"/>
@@ -6382,13 +6416,13 @@
       <c r="G45" s="26">
         <v>22</v>
       </c>
-      <c r="H45" s="121" t="s">
+      <c r="H45" s="165" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="117"/>
-      <c r="J45" s="117"/>
-      <c r="K45" s="117"/>
-      <c r="L45" s="116"/>
+      <c r="I45" s="128"/>
+      <c r="J45" s="128"/>
+      <c r="K45" s="128"/>
+      <c r="L45" s="123"/>
     </row>
     <row r="46" spans="1:12" ht="20.25" customHeight="1">
       <c r="A46" s="1"/>
@@ -6402,11 +6436,11 @@
       <c r="G46" s="27">
         <v>0</v>
       </c>
-      <c r="H46" s="122"/>
-      <c r="I46" s="117"/>
-      <c r="J46" s="117"/>
-      <c r="K46" s="117"/>
-      <c r="L46" s="116"/>
+      <c r="H46" s="137"/>
+      <c r="I46" s="128"/>
+      <c r="J46" s="128"/>
+      <c r="K46" s="128"/>
+      <c r="L46" s="123"/>
     </row>
     <row r="47" spans="1:12" ht="20.25" customHeight="1" thickBot="1">
       <c r="A47" s="1"/>
@@ -6420,11 +6454,11 @@
       <c r="G47" s="27">
         <v>0</v>
       </c>
-      <c r="H47" s="123"/>
-      <c r="I47" s="124"/>
-      <c r="J47" s="124"/>
-      <c r="K47" s="124"/>
-      <c r="L47" s="120"/>
+      <c r="H47" s="166"/>
+      <c r="I47" s="126"/>
+      <c r="J47" s="126"/>
+      <c r="K47" s="126"/>
+      <c r="L47" s="125"/>
     </row>
     <row r="48" spans="1:12" ht="20.25" customHeight="1">
       <c r="A48" s="1"/>
@@ -6438,13 +6472,13 @@
       <c r="G48" s="27">
         <v>0</v>
       </c>
-      <c r="H48" s="125" t="s">
+      <c r="H48" s="167" t="s">
         <v>21</v>
       </c>
-      <c r="I48" s="126"/>
-      <c r="J48" s="126"/>
-      <c r="K48" s="126"/>
-      <c r="L48" s="127"/>
+      <c r="I48" s="133"/>
+      <c r="J48" s="133"/>
+      <c r="K48" s="133"/>
+      <c r="L48" s="134"/>
     </row>
     <row r="49" spans="1:12" ht="20.25" customHeight="1">
       <c r="A49" s="1"/>
@@ -6458,13 +6492,13 @@
       <c r="G49" s="27">
         <v>0</v>
       </c>
-      <c r="H49" s="114" t="s">
+      <c r="H49" s="161" t="s">
         <v>23</v>
       </c>
-      <c r="I49" s="117"/>
-      <c r="J49" s="117"/>
-      <c r="K49" s="117"/>
-      <c r="L49" s="116"/>
+      <c r="I49" s="128"/>
+      <c r="J49" s="128"/>
+      <c r="K49" s="128"/>
+      <c r="L49" s="123"/>
     </row>
     <row r="50" spans="1:12" ht="20.25" customHeight="1" thickBot="1">
       <c r="A50" s="1"/>
@@ -6478,11 +6512,11 @@
       <c r="G50" s="27">
         <v>22</v>
       </c>
-      <c r="H50" s="123"/>
-      <c r="I50" s="124"/>
-      <c r="J50" s="124"/>
-      <c r="K50" s="124"/>
-      <c r="L50" s="120"/>
+      <c r="H50" s="166"/>
+      <c r="I50" s="126"/>
+      <c r="J50" s="126"/>
+      <c r="K50" s="126"/>
+      <c r="L50" s="125"/>
     </row>
     <row r="51" spans="1:12" ht="24" customHeight="1" thickBot="1">
       <c r="A51" s="1"/>
@@ -6501,10 +6535,10 @@
         <v>26</v>
       </c>
       <c r="I51" s="31"/>
-      <c r="J51" s="131" t="s">
+      <c r="J51" s="171" t="s">
         <v>27</v>
       </c>
-      <c r="K51" s="132"/>
+      <c r="K51" s="172"/>
       <c r="L51" s="32" t="s">
         <v>28</v>
       </c>
@@ -6523,10 +6557,10 @@
         <v>29</v>
       </c>
       <c r="I52" s="36"/>
-      <c r="J52" s="118" t="s">
+      <c r="J52" s="163" t="s">
         <v>29</v>
       </c>
-      <c r="K52" s="116"/>
+      <c r="K52" s="123"/>
       <c r="L52" s="37" t="s">
         <v>29</v>
       </c>
@@ -6548,10 +6582,10 @@
         <v>31</v>
       </c>
       <c r="I53" s="36"/>
-      <c r="J53" s="118" t="s">
+      <c r="J53" s="163" t="s">
         <v>31</v>
       </c>
-      <c r="K53" s="116"/>
+      <c r="K53" s="123"/>
       <c r="L53" s="37" t="s">
         <v>31</v>
       </c>
@@ -6567,16 +6601,16 @@
       <c r="F54" s="2"/>
       <c r="G54" s="26">
         <f>G43</f>
-        <v>365.6</v>
+        <v>337.29999999999995</v>
       </c>
       <c r="H54" s="35" t="s">
         <v>33</v>
       </c>
       <c r="I54" s="36"/>
-      <c r="J54" s="118" t="s">
+      <c r="J54" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="K54" s="116"/>
+      <c r="K54" s="123"/>
       <c r="L54" s="37" t="s">
         <v>33</v>
       </c>
@@ -6592,16 +6626,16 @@
       <c r="F55" s="39"/>
       <c r="G55" s="40">
         <f>G54/G53</f>
-        <v>2.0772727272727276</v>
+        <v>1.9164772727272725</v>
       </c>
       <c r="H55" s="41" t="s">
         <v>35</v>
       </c>
       <c r="I55" s="42"/>
-      <c r="J55" s="119" t="s">
+      <c r="J55" s="164" t="s">
         <v>35</v>
       </c>
-      <c r="K55" s="120"/>
+      <c r="K55" s="125"/>
       <c r="L55" s="43" t="s">
         <v>35</v>
       </c>
@@ -6623,32 +6657,32 @@
     <row r="57" spans="1:12" ht="15.75" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="28"/>
-      <c r="C57" s="114" t="s">
+      <c r="C57" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="D57" s="116"/>
-      <c r="E57" s="114" t="s">
+      <c r="D57" s="123"/>
+      <c r="E57" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="F57" s="117"/>
-      <c r="G57" s="116"/>
-      <c r="H57" s="114" t="s">
+      <c r="F57" s="128"/>
+      <c r="G57" s="123"/>
+      <c r="H57" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="I57" s="117"/>
-      <c r="J57" s="116"/>
-      <c r="K57" s="114" t="s">
+      <c r="I57" s="128"/>
+      <c r="J57" s="123"/>
+      <c r="K57" s="161" t="s">
         <v>39</v>
       </c>
-      <c r="L57" s="116"/>
+      <c r="L57" s="123"/>
     </row>
     <row r="58" spans="1:12" ht="15.75" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="114"/>
-      <c r="D58" s="115"/>
+      <c r="C58" s="161"/>
+      <c r="D58" s="162"/>
       <c r="E58" s="47"/>
       <c r="F58" s="1"/>
       <c r="G58" s="48"/>
@@ -6663,8 +6697,8 @@
       <c r="B59" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="C59" s="114"/>
-      <c r="D59" s="115"/>
+      <c r="C59" s="161"/>
+      <c r="D59" s="162"/>
       <c r="E59" s="47"/>
       <c r="F59" s="1"/>
       <c r="G59" s="48"/>
@@ -6679,8 +6713,8 @@
       <c r="B60" s="50">
         <v>46257</v>
       </c>
-      <c r="C60" s="114"/>
-      <c r="D60" s="115"/>
+      <c r="C60" s="161"/>
+      <c r="D60" s="162"/>
       <c r="E60" s="47"/>
       <c r="F60" s="1"/>
       <c r="G60" s="48"/>
@@ -6693,8 +6727,8 @@
     <row r="61" spans="1:12" ht="15.75" customHeight="1">
       <c r="A61" s="51"/>
       <c r="B61" s="47"/>
-      <c r="C61" s="114"/>
-      <c r="D61" s="115"/>
+      <c r="C61" s="161"/>
+      <c r="D61" s="162"/>
       <c r="E61" s="47"/>
       <c r="F61" s="1"/>
       <c r="G61" s="48"/>
@@ -6707,44 +6741,44 @@
     <row r="62" spans="1:12" ht="15.75" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="52"/>
-      <c r="C62" s="164" t="s">
+      <c r="C62" s="122" t="s">
         <v>151</v>
       </c>
-      <c r="D62" s="116"/>
-      <c r="E62" s="162" t="s">
+      <c r="D62" s="123"/>
+      <c r="E62" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="F62" s="117"/>
-      <c r="G62" s="116"/>
-      <c r="H62" s="163" t="s">
+      <c r="F62" s="128"/>
+      <c r="G62" s="123"/>
+      <c r="H62" s="129" t="s">
         <v>145</v>
       </c>
-      <c r="I62" s="117"/>
-      <c r="J62" s="116"/>
-      <c r="K62" s="162" t="s">
+      <c r="I62" s="128"/>
+      <c r="J62" s="123"/>
+      <c r="K62" s="127" t="s">
         <v>42</v>
       </c>
-      <c r="L62" s="116"/>
+      <c r="L62" s="123"/>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A63" s="1"/>
       <c r="B63" s="53"/>
-      <c r="C63" s="161"/>
-      <c r="D63" s="120"/>
-      <c r="E63" s="161" t="s">
+      <c r="C63" s="124"/>
+      <c r="D63" s="125"/>
+      <c r="E63" s="124" t="s">
         <v>43</v>
       </c>
-      <c r="F63" s="124"/>
-      <c r="G63" s="120"/>
-      <c r="H63" s="161" t="s">
+      <c r="F63" s="126"/>
+      <c r="G63" s="125"/>
+      <c r="H63" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="I63" s="124"/>
-      <c r="J63" s="120"/>
-      <c r="K63" s="161" t="s">
+      <c r="I63" s="126"/>
+      <c r="J63" s="125"/>
+      <c r="K63" s="124" t="s">
         <v>45</v>
       </c>
-      <c r="L63" s="120"/>
+      <c r="L63" s="125"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1">
       <c r="A64" s="1"/>
@@ -10284,32 +10318,22 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="J30:L30"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="H63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="C58:D61"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="H57:J57"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="H45:L47"/>
+    <mergeCell ref="H48:L48"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="H49:L50"/>
+    <mergeCell ref="H44:L44"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="J7:L8"/>
@@ -10326,22 +10350,32 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F8"/>
     <mergeCell ref="G7:G8"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="C58:D61"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="H57:J57"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="H45:L47"/>
-    <mergeCell ref="H48:L48"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="H49:L50"/>
-    <mergeCell ref="H44:L44"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="H63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="J16:L16"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.19685039370078741" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="81" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -10384,26 +10418,26 @@
     </row>
     <row r="2" spans="1:11" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="137"/>
-      <c r="C2" s="126"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="133"/>
       <c r="D2" s="140"/>
-      <c r="E2" s="135" t="s">
+      <c r="E2" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
       <c r="H2" s="140"/>
-      <c r="I2" s="135" t="s">
+      <c r="I2" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="126"/>
-      <c r="K2" s="127"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="134"/>
     </row>
     <row r="3" spans="1:11" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="165"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="182"/>
       <c r="E3" s="141"/>
       <c r="F3" s="139"/>
       <c r="G3" s="139"/>
@@ -10414,16 +10448,16 @@
     </row>
     <row r="4" spans="1:11" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="165"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="182"/>
       <c r="E4" s="145" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="146"/>
       <c r="G4" s="146"/>
       <c r="H4" s="147"/>
-      <c r="I4" s="166" t="s">
+      <c r="I4" s="183" t="s">
         <v>47</v>
       </c>
       <c r="J4" s="149"/>
@@ -10442,28 +10476,28 @@
       </c>
       <c r="G5" s="146"/>
       <c r="H5" s="147"/>
-      <c r="I5" s="167"/>
-      <c r="J5" s="117"/>
-      <c r="K5" s="116"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="123"/>
     </row>
     <row r="6" spans="1:11" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="171" t="s">
+      <c r="B6" s="188" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="169"/>
-      <c r="D6" s="170"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="187"/>
       <c r="E6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="168">
+      <c r="F6" s="185">
         <v>20230682322</v>
       </c>
-      <c r="G6" s="169"/>
-      <c r="H6" s="170"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="120"/>
+      <c r="G6" s="186"/>
+      <c r="H6" s="187"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="126"/>
+      <c r="K6" s="125"/>
     </row>
     <row r="7" spans="1:11" ht="14.4">
       <c r="A7" s="1"/>
@@ -10474,21 +10508,21 @@
         <v>6</v>
       </c>
       <c r="D7" s="158"/>
-      <c r="E7" s="137" t="s">
+      <c r="E7" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="127"/>
-      <c r="G7" s="172" t="s">
+      <c r="F7" s="134"/>
+      <c r="G7" s="189" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="173" t="s">
+      <c r="H7" s="190" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="126"/>
-      <c r="K7" s="127"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="134"/>
     </row>
     <row r="8" spans="1:11" ht="14.4">
       <c r="A8" s="1"/>
@@ -10499,13 +10533,13 @@
       <c r="D8" s="55">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="123"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="174"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="124"/>
-      <c r="K8" s="120"/>
+      <c r="E8" s="166"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="126"/>
+      <c r="H8" s="191"/>
+      <c r="I8" s="126"/>
+      <c r="J8" s="126"/>
+      <c r="K8" s="125"/>
     </row>
     <row r="9" spans="1:11" ht="14.4">
       <c r="A9" s="2"/>
@@ -10530,11 +10564,11 @@
       <c r="H9" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="175" t="s">
+      <c r="I9" s="177" t="s">
         <v>52</v>
       </c>
       <c r="J9" s="146"/>
-      <c r="K9" s="176"/>
+      <c r="K9" s="178"/>
     </row>
     <row r="10" spans="1:11" ht="14.4">
       <c r="A10" s="9"/>
@@ -10559,11 +10593,11 @@
       <c r="H10" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="175" t="s">
+      <c r="I10" s="177" t="s">
         <v>54</v>
       </c>
       <c r="J10" s="146"/>
-      <c r="K10" s="176"/>
+      <c r="K10" s="178"/>
     </row>
     <row r="11" spans="1:11" ht="14.4">
       <c r="A11" s="2"/>
@@ -10588,11 +10622,11 @@
       <c r="H11" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I11" s="175" t="s">
+      <c r="I11" s="177" t="s">
         <v>56</v>
       </c>
       <c r="J11" s="146"/>
-      <c r="K11" s="176"/>
+      <c r="K11" s="178"/>
     </row>
     <row r="12" spans="1:11" ht="14.4">
       <c r="A12" s="2"/>
@@ -10611,9 +10645,9 @@
         <v>0</v>
       </c>
       <c r="H12" s="13"/>
-      <c r="I12" s="175"/>
+      <c r="I12" s="177"/>
       <c r="J12" s="146"/>
-      <c r="K12" s="176"/>
+      <c r="K12" s="178"/>
     </row>
     <row r="13" spans="1:11" ht="14.4">
       <c r="A13" s="2"/>
@@ -10632,9 +10666,9 @@
         <v>0</v>
       </c>
       <c r="H13" s="13"/>
-      <c r="I13" s="175"/>
+      <c r="I13" s="177"/>
       <c r="J13" s="146"/>
-      <c r="K13" s="176"/>
+      <c r="K13" s="178"/>
     </row>
     <row r="14" spans="1:11" ht="14.4">
       <c r="A14" s="2"/>
@@ -10659,11 +10693,11 @@
       <c r="H14" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I14" s="175" t="s">
+      <c r="I14" s="177" t="s">
         <v>54</v>
       </c>
       <c r="J14" s="146"/>
-      <c r="K14" s="176"/>
+      <c r="K14" s="178"/>
     </row>
     <row r="15" spans="1:11" ht="14.4">
       <c r="A15" s="2"/>
@@ -10688,11 +10722,11 @@
       <c r="H15" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="175" t="s">
+      <c r="I15" s="177" t="s">
         <v>61</v>
       </c>
       <c r="J15" s="146"/>
-      <c r="K15" s="176"/>
+      <c r="K15" s="178"/>
     </row>
     <row r="16" spans="1:11" ht="14.4">
       <c r="A16" s="2"/>
@@ -10711,9 +10745,9 @@
         <v>0</v>
       </c>
       <c r="H16" s="11"/>
-      <c r="I16" s="177"/>
+      <c r="I16" s="181"/>
       <c r="J16" s="146"/>
-      <c r="K16" s="176"/>
+      <c r="K16" s="178"/>
     </row>
     <row r="17" spans="1:11" ht="14.4">
       <c r="A17" s="2"/>
@@ -10738,11 +10772,11 @@
       <c r="H17" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="175" t="s">
+      <c r="I17" s="177" t="s">
         <v>61</v>
       </c>
       <c r="J17" s="146"/>
-      <c r="K17" s="176"/>
+      <c r="K17" s="178"/>
     </row>
     <row r="18" spans="1:11" ht="14.4">
       <c r="A18" s="2"/>
@@ -10767,11 +10801,11 @@
       <c r="H18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="175" t="s">
+      <c r="I18" s="177" t="s">
         <v>61</v>
       </c>
       <c r="J18" s="146"/>
-      <c r="K18" s="176"/>
+      <c r="K18" s="178"/>
     </row>
     <row r="19" spans="1:11" ht="14.4">
       <c r="A19" s="2"/>
@@ -10790,9 +10824,9 @@
         <v>0</v>
       </c>
       <c r="H19" s="11"/>
-      <c r="I19" s="177"/>
+      <c r="I19" s="181"/>
       <c r="J19" s="146"/>
-      <c r="K19" s="176"/>
+      <c r="K19" s="178"/>
     </row>
     <row r="20" spans="1:11" ht="14.4">
       <c r="A20" s="2"/>
@@ -10811,9 +10845,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="11"/>
-      <c r="I20" s="177"/>
+      <c r="I20" s="181"/>
       <c r="J20" s="146"/>
-      <c r="K20" s="176"/>
+      <c r="K20" s="178"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1">
       <c r="A21" s="2"/>
@@ -10838,11 +10872,11 @@
       <c r="H21" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I21" s="175" t="s">
+      <c r="I21" s="177" t="s">
         <v>68</v>
       </c>
       <c r="J21" s="146"/>
-      <c r="K21" s="176"/>
+      <c r="K21" s="178"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
       <c r="A22" s="2"/>
@@ -10867,11 +10901,11 @@
       <c r="H22" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="175" t="s">
+      <c r="I22" s="177" t="s">
         <v>52</v>
       </c>
       <c r="J22" s="146"/>
-      <c r="K22" s="176"/>
+      <c r="K22" s="178"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
       <c r="A23" s="2"/>
@@ -10896,11 +10930,11 @@
       <c r="H23" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="175" t="s">
+      <c r="I23" s="177" t="s">
         <v>52</v>
       </c>
       <c r="J23" s="146"/>
-      <c r="K23" s="176"/>
+      <c r="K23" s="178"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="2"/>
@@ -10925,11 +10959,11 @@
       <c r="H24" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="175" t="s">
+      <c r="I24" s="177" t="s">
         <v>72</v>
       </c>
       <c r="J24" s="146"/>
-      <c r="K24" s="176"/>
+      <c r="K24" s="178"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1">
       <c r="A25" s="2"/>
@@ -10954,11 +10988,11 @@
       <c r="H25" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="175" t="s">
+      <c r="I25" s="177" t="s">
         <v>74</v>
       </c>
       <c r="J25" s="146"/>
-      <c r="K25" s="176"/>
+      <c r="K25" s="178"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1">
       <c r="A26" s="2"/>
@@ -10977,9 +11011,9 @@
         <v>0</v>
       </c>
       <c r="H26" s="11"/>
-      <c r="I26" s="177"/>
+      <c r="I26" s="181"/>
       <c r="J26" s="146"/>
-      <c r="K26" s="176"/>
+      <c r="K26" s="178"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
       <c r="A27" s="2"/>
@@ -10998,9 +11032,9 @@
         <v>0</v>
       </c>
       <c r="H27" s="11"/>
-      <c r="I27" s="177"/>
+      <c r="I27" s="181"/>
       <c r="J27" s="146"/>
-      <c r="K27" s="176"/>
+      <c r="K27" s="178"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1">
       <c r="A28" s="2"/>
@@ -11025,11 +11059,11 @@
       <c r="H28" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I28" s="175" t="s">
+      <c r="I28" s="177" t="s">
         <v>78</v>
       </c>
       <c r="J28" s="146"/>
-      <c r="K28" s="176"/>
+      <c r="K28" s="178"/>
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1">
       <c r="A29" s="2"/>
@@ -11054,11 +11088,11 @@
       <c r="H29" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="175" t="s">
+      <c r="I29" s="177" t="s">
         <v>80</v>
       </c>
       <c r="J29" s="146"/>
-      <c r="K29" s="176"/>
+      <c r="K29" s="178"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="2"/>
@@ -11083,11 +11117,11 @@
       <c r="H30" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I30" s="175" t="s">
+      <c r="I30" s="177" t="s">
         <v>82</v>
       </c>
       <c r="J30" s="146"/>
-      <c r="K30" s="176"/>
+      <c r="K30" s="178"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1">
       <c r="A31" s="2"/>
@@ -11112,11 +11146,11 @@
       <c r="H31" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I31" s="175" t="s">
+      <c r="I31" s="177" t="s">
         <v>84</v>
       </c>
       <c r="J31" s="146"/>
-      <c r="K31" s="176"/>
+      <c r="K31" s="178"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="2"/>
@@ -11141,11 +11175,11 @@
       <c r="H32" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I32" s="175" t="s">
+      <c r="I32" s="177" t="s">
         <v>86</v>
       </c>
       <c r="J32" s="146"/>
-      <c r="K32" s="176"/>
+      <c r="K32" s="178"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1">
       <c r="A33" s="2"/>
@@ -11164,9 +11198,9 @@
         <v>0</v>
       </c>
       <c r="H33" s="11"/>
-      <c r="I33" s="177"/>
+      <c r="I33" s="181"/>
       <c r="J33" s="146"/>
-      <c r="K33" s="176"/>
+      <c r="K33" s="178"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1">
       <c r="A34" s="2"/>
@@ -11185,9 +11219,9 @@
         <v>0</v>
       </c>
       <c r="H34" s="11"/>
-      <c r="I34" s="177"/>
+      <c r="I34" s="181"/>
       <c r="J34" s="146"/>
-      <c r="K34" s="176"/>
+      <c r="K34" s="178"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1">
       <c r="A35" s="2"/>
@@ -11212,11 +11246,11 @@
       <c r="H35" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I35" s="175" t="s">
+      <c r="I35" s="177" t="s">
         <v>90</v>
       </c>
       <c r="J35" s="146"/>
-      <c r="K35" s="176"/>
+      <c r="K35" s="178"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1">
       <c r="A36" s="2"/>
@@ -11241,11 +11275,11 @@
       <c r="H36" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I36" s="175" t="s">
+      <c r="I36" s="177" t="s">
         <v>52</v>
       </c>
       <c r="J36" s="146"/>
-      <c r="K36" s="176"/>
+      <c r="K36" s="178"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1">
       <c r="A37" s="2"/>
@@ -11270,11 +11304,11 @@
       <c r="H37" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I37" s="175" t="s">
+      <c r="I37" s="177" t="s">
         <v>68</v>
       </c>
       <c r="J37" s="146"/>
-      <c r="K37" s="176"/>
+      <c r="K37" s="178"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1">
       <c r="A38" s="2"/>
@@ -11299,11 +11333,11 @@
       <c r="H38" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I38" s="175" t="s">
+      <c r="I38" s="177" t="s">
         <v>94</v>
       </c>
       <c r="J38" s="146"/>
-      <c r="K38" s="176"/>
+      <c r="K38" s="178"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1">
       <c r="A39" s="2"/>
@@ -11328,7 +11362,7 @@
       <c r="H39" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I39" s="179" t="s">
+      <c r="I39" s="180" t="s">
         <v>94</v>
       </c>
       <c r="J39" s="149"/>
@@ -11336,13 +11370,13 @@
     </row>
     <row r="40" spans="1:11" ht="18" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="128" t="s">
+      <c r="B40" s="168" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="180"/>
-      <c r="D40" s="180"/>
-      <c r="E40" s="180"/>
-      <c r="F40" s="181"/>
+      <c r="C40" s="173"/>
+      <c r="D40" s="173"/>
+      <c r="E40" s="173"/>
+      <c r="F40" s="174"/>
       <c r="G40" s="18">
         <f>SUM(G9:G39)</f>
         <v>176</v>
@@ -11362,12 +11396,12 @@
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
       <c r="G41" s="23"/>
-      <c r="H41" s="182" t="s">
+      <c r="H41" s="175" t="s">
         <v>15</v>
       </c>
-      <c r="I41" s="126"/>
-      <c r="J41" s="126"/>
-      <c r="K41" s="127"/>
+      <c r="I41" s="133"/>
+      <c r="J41" s="133"/>
+      <c r="K41" s="134"/>
     </row>
     <row r="42" spans="1:11" ht="20.25" customHeight="1">
       <c r="A42" s="1"/>
@@ -11381,12 +11415,12 @@
       <c r="G42" s="26">
         <v>22</v>
       </c>
-      <c r="H42" s="183" t="s">
+      <c r="H42" s="176" t="s">
         <v>17</v>
       </c>
-      <c r="I42" s="117"/>
-      <c r="J42" s="117"/>
-      <c r="K42" s="116"/>
+      <c r="I42" s="128"/>
+      <c r="J42" s="128"/>
+      <c r="K42" s="123"/>
     </row>
     <row r="43" spans="1:11" ht="20.25" customHeight="1">
       <c r="A43" s="1"/>
@@ -11400,10 +11434,10 @@
       <c r="G43" s="27">
         <v>9</v>
       </c>
-      <c r="H43" s="117"/>
-      <c r="I43" s="117"/>
-      <c r="J43" s="117"/>
-      <c r="K43" s="116"/>
+      <c r="H43" s="128"/>
+      <c r="I43" s="128"/>
+      <c r="J43" s="128"/>
+      <c r="K43" s="123"/>
     </row>
     <row r="44" spans="1:11" ht="20.25" customHeight="1">
       <c r="A44" s="1"/>
@@ -11417,10 +11451,10 @@
       <c r="G44" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H44" s="124"/>
-      <c r="I44" s="124"/>
-      <c r="J44" s="124"/>
-      <c r="K44" s="120"/>
+      <c r="H44" s="126"/>
+      <c r="I44" s="126"/>
+      <c r="J44" s="126"/>
+      <c r="K44" s="125"/>
     </row>
     <row r="45" spans="1:11" ht="20.25" customHeight="1">
       <c r="A45" s="1"/>
@@ -11453,7 +11487,7 @@
       <c r="G46" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H46" s="178" t="s">
+      <c r="H46" s="179" t="s">
         <v>23</v>
       </c>
       <c r="I46" s="1"/>
@@ -11472,7 +11506,7 @@
       <c r="G47" s="27">
         <v>22</v>
       </c>
-      <c r="H47" s="124"/>
+      <c r="H47" s="126"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="48"/>
@@ -11493,10 +11527,10 @@
       <c r="H48" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="I48" s="131" t="s">
+      <c r="I48" s="171" t="s">
         <v>27</v>
       </c>
-      <c r="J48" s="132"/>
+      <c r="J48" s="172"/>
       <c r="K48" s="32" t="s">
         <v>28</v>
       </c>
@@ -11514,10 +11548,10 @@
       <c r="H49" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="I49" s="118" t="s">
+      <c r="I49" s="163" t="s">
         <v>29</v>
       </c>
-      <c r="J49" s="116"/>
+      <c r="J49" s="123"/>
       <c r="K49" s="37" t="s">
         <v>29</v>
       </c>
@@ -11538,10 +11572,10 @@
       <c r="H50" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="I50" s="118" t="s">
+      <c r="I50" s="163" t="s">
         <v>31</v>
       </c>
-      <c r="J50" s="116"/>
+      <c r="J50" s="123"/>
       <c r="K50" s="37" t="s">
         <v>31</v>
       </c>
@@ -11562,10 +11596,10 @@
       <c r="H51" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I51" s="118" t="s">
+      <c r="I51" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="116"/>
+      <c r="J51" s="123"/>
       <c r="K51" s="37" t="s">
         <v>33</v>
       </c>
@@ -11586,10 +11620,10 @@
       <c r="H52" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="I52" s="119" t="s">
+      <c r="I52" s="164" t="s">
         <v>35</v>
       </c>
-      <c r="J52" s="120"/>
+      <c r="J52" s="125"/>
       <c r="K52" s="43" t="s">
         <v>35</v>
       </c>
@@ -11612,23 +11646,23 @@
       <c r="B54" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="114" t="s">
+      <c r="C54" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="D54" s="116"/>
-      <c r="E54" s="114" t="s">
+      <c r="D54" s="123"/>
+      <c r="E54" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="F54" s="117"/>
-      <c r="G54" s="116"/>
-      <c r="H54" s="114" t="s">
+      <c r="F54" s="128"/>
+      <c r="G54" s="123"/>
+      <c r="H54" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="I54" s="116"/>
-      <c r="J54" s="114" t="s">
+      <c r="I54" s="123"/>
+      <c r="J54" s="161" t="s">
         <v>106</v>
       </c>
-      <c r="K54" s="116"/>
+      <c r="K54" s="123"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1">
       <c r="A55" s="1"/>
@@ -11685,42 +11719,42 @@
     <row r="59" spans="1:11" ht="15.75" customHeight="1">
       <c r="A59" s="51"/>
       <c r="B59" s="52"/>
-      <c r="C59" s="162" t="s">
+      <c r="C59" s="127" t="s">
         <v>107</v>
       </c>
-      <c r="D59" s="116"/>
-      <c r="E59" s="162" t="s">
+      <c r="D59" s="123"/>
+      <c r="E59" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="F59" s="117"/>
-      <c r="G59" s="116"/>
-      <c r="H59" s="162" t="s">
+      <c r="F59" s="128"/>
+      <c r="G59" s="123"/>
+      <c r="H59" s="127" t="s">
         <v>109</v>
       </c>
-      <c r="I59" s="116"/>
-      <c r="J59" s="162" t="s">
+      <c r="I59" s="123"/>
+      <c r="J59" s="127" t="s">
         <v>110</v>
       </c>
-      <c r="K59" s="116"/>
+      <c r="K59" s="123"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="53"/>
-      <c r="C60" s="161"/>
-      <c r="D60" s="120"/>
-      <c r="E60" s="161" t="s">
+      <c r="C60" s="124"/>
+      <c r="D60" s="125"/>
+      <c r="E60" s="124" t="s">
         <v>111</v>
       </c>
-      <c r="F60" s="124"/>
-      <c r="G60" s="120"/>
-      <c r="H60" s="161" t="s">
+      <c r="F60" s="126"/>
+      <c r="G60" s="125"/>
+      <c r="H60" s="124" t="s">
         <v>112</v>
       </c>
-      <c r="I60" s="120"/>
-      <c r="J60" s="161" t="s">
+      <c r="I60" s="125"/>
+      <c r="J60" s="124" t="s">
         <v>113</v>
       </c>
-      <c r="K60" s="120"/>
+      <c r="K60" s="125"/>
     </row>
     <row r="61" spans="1:11" ht="15.75" customHeight="1">
       <c r="A61" s="1"/>
@@ -15064,40 +15098,22 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="H42:K44"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:G60"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="H59:I59"/>
     <mergeCell ref="J59:K59"/>
     <mergeCell ref="B2:D5"/>
     <mergeCell ref="E2:H3"/>
@@ -15114,22 +15130,40 @@
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:K8"/>
     <mergeCell ref="I9:K9"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:G60"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="H42:K44"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I37:K37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -15173,26 +15207,26 @@
     </row>
     <row r="2" spans="1:11" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="137"/>
-      <c r="C2" s="126"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="133"/>
       <c r="D2" s="140"/>
-      <c r="E2" s="135" t="s">
+      <c r="E2" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
       <c r="H2" s="140"/>
-      <c r="I2" s="135" t="s">
+      <c r="I2" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="126"/>
-      <c r="K2" s="127"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="134"/>
     </row>
     <row r="3" spans="1:11" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="165"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="182"/>
       <c r="E3" s="141"/>
       <c r="F3" s="139"/>
       <c r="G3" s="139"/>
@@ -15203,16 +15237,16 @@
     </row>
     <row r="4" spans="1:11" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="165"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="182"/>
       <c r="E4" s="145" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="146"/>
       <c r="G4" s="146"/>
       <c r="H4" s="147"/>
-      <c r="I4" s="166" t="s">
+      <c r="I4" s="183" t="s">
         <v>116</v>
       </c>
       <c r="J4" s="149"/>
@@ -15231,28 +15265,28 @@
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="83"/>
-      <c r="I5" s="167"/>
-      <c r="J5" s="117"/>
-      <c r="K5" s="116"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="123"/>
     </row>
     <row r="6" spans="1:11" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="171" t="s">
+      <c r="B6" s="188" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="169"/>
-      <c r="D6" s="170"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="187"/>
       <c r="E6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="168">
+      <c r="F6" s="185">
         <v>20230682322</v>
       </c>
-      <c r="G6" s="169"/>
-      <c r="H6" s="170"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="120"/>
+      <c r="G6" s="186"/>
+      <c r="H6" s="187"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="126"/>
+      <c r="K6" s="125"/>
     </row>
     <row r="7" spans="1:11" ht="14.4">
       <c r="A7" s="1"/>
@@ -15263,21 +15297,21 @@
         <v>6</v>
       </c>
       <c r="D7" s="158"/>
-      <c r="E7" s="137" t="s">
+      <c r="E7" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="127"/>
-      <c r="G7" s="172" t="s">
+      <c r="F7" s="134"/>
+      <c r="G7" s="189" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="190" t="s">
+      <c r="H7" s="193" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="126"/>
-      <c r="K7" s="127"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="134"/>
     </row>
     <row r="8" spans="1:11" ht="14.4">
       <c r="A8" s="1"/>
@@ -15288,13 +15322,13 @@
       <c r="D8" s="55">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="123"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="174"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="124"/>
-      <c r="K8" s="120"/>
+      <c r="E8" s="166"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="126"/>
+      <c r="H8" s="191"/>
+      <c r="I8" s="126"/>
+      <c r="J8" s="126"/>
+      <c r="K8" s="125"/>
     </row>
     <row r="9" spans="1:11" ht="14.4">
       <c r="A9" s="1"/>
@@ -15320,11 +15354,11 @@
       <c r="H9" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I9" s="177" t="s">
+      <c r="I9" s="181" t="s">
         <v>117</v>
       </c>
       <c r="J9" s="146"/>
-      <c r="K9" s="176"/>
+      <c r="K9" s="178"/>
     </row>
     <row r="10" spans="1:11" ht="14.4">
       <c r="A10" s="82"/>
@@ -15350,11 +15384,11 @@
       <c r="H10" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I10" s="177" t="s">
+      <c r="I10" s="181" t="s">
         <v>118</v>
       </c>
       <c r="J10" s="146"/>
-      <c r="K10" s="176"/>
+      <c r="K10" s="178"/>
     </row>
     <row r="11" spans="1:11" ht="14.4">
       <c r="A11" s="1"/>
@@ -15380,11 +15414,11 @@
       <c r="H11" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I11" s="177" t="s">
+      <c r="I11" s="181" t="s">
         <v>119</v>
       </c>
       <c r="J11" s="146"/>
-      <c r="K11" s="176"/>
+      <c r="K11" s="178"/>
     </row>
     <row r="12" spans="1:11" ht="14.4">
       <c r="A12" s="1"/>
@@ -15410,11 +15444,11 @@
       <c r="H12" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I12" s="175" t="s">
+      <c r="I12" s="177" t="s">
         <v>120</v>
       </c>
       <c r="J12" s="146"/>
-      <c r="K12" s="176"/>
+      <c r="K12" s="178"/>
     </row>
     <row r="13" spans="1:11" ht="21.75" customHeight="1">
       <c r="A13" s="1"/>
@@ -15434,9 +15468,9 @@
         <v>0</v>
       </c>
       <c r="H13" s="83"/>
-      <c r="I13" s="175"/>
+      <c r="I13" s="177"/>
       <c r="J13" s="146"/>
-      <c r="K13" s="176"/>
+      <c r="K13" s="178"/>
     </row>
     <row r="14" spans="1:11" ht="21.75" customHeight="1">
       <c r="A14" s="1"/>
@@ -15456,9 +15490,9 @@
         <v>0</v>
       </c>
       <c r="H14" s="83"/>
-      <c r="I14" s="177"/>
+      <c r="I14" s="181"/>
       <c r="J14" s="146"/>
-      <c r="K14" s="176"/>
+      <c r="K14" s="178"/>
     </row>
     <row r="15" spans="1:11" ht="14.4">
       <c r="A15" s="1"/>
@@ -15484,11 +15518,11 @@
       <c r="H15" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="177" t="s">
+      <c r="I15" s="181" t="s">
         <v>121</v>
       </c>
       <c r="J15" s="146"/>
-      <c r="K15" s="176"/>
+      <c r="K15" s="178"/>
     </row>
     <row r="16" spans="1:11" ht="20.25" customHeight="1">
       <c r="A16" s="1"/>
@@ -15510,11 +15544,11 @@
       <c r="H16" s="93" t="s">
         <v>122</v>
       </c>
-      <c r="I16" s="177" t="s">
+      <c r="I16" s="181" t="s">
         <v>123</v>
       </c>
       <c r="J16" s="146"/>
-      <c r="K16" s="176"/>
+      <c r="K16" s="178"/>
     </row>
     <row r="17" spans="1:11" ht="14.4">
       <c r="A17" s="1"/>
@@ -15540,11 +15574,11 @@
       <c r="H17" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="191" t="s">
+      <c r="I17" s="192" t="s">
         <v>124</v>
       </c>
       <c r="J17" s="146"/>
-      <c r="K17" s="176"/>
+      <c r="K17" s="178"/>
     </row>
     <row r="18" spans="1:11" ht="14.4">
       <c r="A18" s="1"/>
@@ -15570,11 +15604,11 @@
       <c r="H18" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="177" t="s">
+      <c r="I18" s="181" t="s">
         <v>121</v>
       </c>
       <c r="J18" s="146"/>
-      <c r="K18" s="176"/>
+      <c r="K18" s="178"/>
     </row>
     <row r="19" spans="1:11" ht="14.4">
       <c r="A19" s="1"/>
@@ -15600,11 +15634,11 @@
       <c r="H19" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I19" s="177" t="s">
+      <c r="I19" s="181" t="s">
         <v>125</v>
       </c>
       <c r="J19" s="146"/>
-      <c r="K19" s="176"/>
+      <c r="K19" s="178"/>
     </row>
     <row r="20" spans="1:11" ht="21.75" customHeight="1">
       <c r="A20" s="1"/>
@@ -15624,9 +15658,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="83"/>
-      <c r="I20" s="177"/>
+      <c r="I20" s="181"/>
       <c r="J20" s="146"/>
-      <c r="K20" s="176"/>
+      <c r="K20" s="178"/>
     </row>
     <row r="21" spans="1:11" ht="21.75" customHeight="1">
       <c r="A21" s="1"/>
@@ -15646,9 +15680,9 @@
         <v>0</v>
       </c>
       <c r="H21" s="83"/>
-      <c r="I21" s="177"/>
+      <c r="I21" s="181"/>
       <c r="J21" s="146"/>
-      <c r="K21" s="176"/>
+      <c r="K21" s="178"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
@@ -15674,11 +15708,11 @@
       <c r="H22" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="177" t="s">
+      <c r="I22" s="181" t="s">
         <v>126</v>
       </c>
       <c r="J22" s="146"/>
-      <c r="K22" s="176"/>
+      <c r="K22" s="178"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
       <c r="A23" s="1"/>
@@ -15704,11 +15738,11 @@
       <c r="H23" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="177" t="s">
+      <c r="I23" s="181" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="146"/>
-      <c r="K23" s="176"/>
+      <c r="K23" s="178"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
@@ -15734,11 +15768,11 @@
       <c r="H24" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="177" t="s">
+      <c r="I24" s="181" t="s">
         <v>128</v>
       </c>
       <c r="J24" s="146"/>
-      <c r="K24" s="176"/>
+      <c r="K24" s="178"/>
     </row>
     <row r="25" spans="1:11" ht="21.75" customHeight="1">
       <c r="A25" s="1"/>
@@ -15758,9 +15792,9 @@
         <v>0</v>
       </c>
       <c r="H25" s="83"/>
-      <c r="I25" s="177"/>
+      <c r="I25" s="181"/>
       <c r="J25" s="146"/>
-      <c r="K25" s="176"/>
+      <c r="K25" s="178"/>
     </row>
     <row r="26" spans="1:11" ht="31.5" customHeight="1">
       <c r="A26" s="1"/>
@@ -15786,11 +15820,11 @@
       <c r="H26" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="177" t="s">
+      <c r="I26" s="181" t="s">
         <v>128</v>
       </c>
       <c r="J26" s="146"/>
-      <c r="K26" s="176"/>
+      <c r="K26" s="178"/>
     </row>
     <row r="27" spans="1:11" ht="21.75" customHeight="1">
       <c r="A27" s="1"/>
@@ -15810,9 +15844,9 @@
         <v>0</v>
       </c>
       <c r="H27" s="83"/>
-      <c r="I27" s="177"/>
+      <c r="I27" s="181"/>
       <c r="J27" s="146"/>
-      <c r="K27" s="176"/>
+      <c r="K27" s="178"/>
     </row>
     <row r="28" spans="1:11" ht="21.75" customHeight="1">
       <c r="A28" s="1"/>
@@ -15832,9 +15866,9 @@
         <v>0</v>
       </c>
       <c r="H28" s="83"/>
-      <c r="I28" s="177"/>
+      <c r="I28" s="181"/>
       <c r="J28" s="146"/>
-      <c r="K28" s="176"/>
+      <c r="K28" s="178"/>
     </row>
     <row r="29" spans="1:11" ht="29.25" customHeight="1">
       <c r="A29" s="1"/>
@@ -15860,11 +15894,11 @@
       <c r="H29" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="177" t="s">
+      <c r="I29" s="181" t="s">
         <v>128</v>
       </c>
       <c r="J29" s="146"/>
-      <c r="K29" s="176"/>
+      <c r="K29" s="178"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
@@ -15890,11 +15924,11 @@
       <c r="H30" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I30" s="177" t="s">
+      <c r="I30" s="181" t="s">
         <v>128</v>
       </c>
       <c r="J30" s="146"/>
-      <c r="K30" s="176"/>
+      <c r="K30" s="178"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1">
       <c r="A31" s="1"/>
@@ -15920,11 +15954,11 @@
       <c r="H31" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I31" s="177" t="s">
+      <c r="I31" s="181" t="s">
         <v>128</v>
       </c>
       <c r="J31" s="146"/>
-      <c r="K31" s="176"/>
+      <c r="K31" s="178"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="1"/>
@@ -15950,11 +15984,11 @@
       <c r="H32" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I32" s="177" t="s">
+      <c r="I32" s="181" t="s">
         <v>128</v>
       </c>
       <c r="J32" s="146"/>
-      <c r="K32" s="176"/>
+      <c r="K32" s="178"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1">
       <c r="A33" s="1"/>
@@ -15980,11 +16014,11 @@
       <c r="H33" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I33" s="177" t="s">
+      <c r="I33" s="181" t="s">
         <v>129</v>
       </c>
       <c r="J33" s="146"/>
-      <c r="K33" s="176"/>
+      <c r="K33" s="178"/>
     </row>
     <row r="34" spans="1:11" ht="21.75" customHeight="1">
       <c r="A34" s="1"/>
@@ -16004,9 +16038,9 @@
         <v>0</v>
       </c>
       <c r="H34" s="83"/>
-      <c r="I34" s="177"/>
+      <c r="I34" s="181"/>
       <c r="J34" s="146"/>
-      <c r="K34" s="176"/>
+      <c r="K34" s="178"/>
     </row>
     <row r="35" spans="1:11" ht="21.75" customHeight="1">
       <c r="A35" s="1"/>
@@ -16026,9 +16060,9 @@
         <v>0</v>
       </c>
       <c r="H35" s="83"/>
-      <c r="I35" s="177"/>
+      <c r="I35" s="181"/>
       <c r="J35" s="146"/>
-      <c r="K35" s="176"/>
+      <c r="K35" s="178"/>
     </row>
     <row r="36" spans="1:11" ht="21.75" customHeight="1">
       <c r="A36" s="1"/>
@@ -16050,11 +16084,11 @@
       <c r="H36" s="93" t="s">
         <v>115</v>
       </c>
-      <c r="I36" s="177" t="s">
+      <c r="I36" s="181" t="s">
         <v>130</v>
       </c>
       <c r="J36" s="146"/>
-      <c r="K36" s="176"/>
+      <c r="K36" s="178"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1">
       <c r="A37" s="1"/>
@@ -16080,11 +16114,11 @@
       <c r="H37" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I37" s="177" t="s">
+      <c r="I37" s="181" t="s">
         <v>131</v>
       </c>
       <c r="J37" s="146"/>
-      <c r="K37" s="176"/>
+      <c r="K37" s="178"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1">
       <c r="A38" s="1"/>
@@ -16110,20 +16144,20 @@
       <c r="H38" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I38" s="177" t="s">
+      <c r="I38" s="181" t="s">
         <v>132</v>
       </c>
       <c r="J38" s="146"/>
-      <c r="K38" s="176"/>
+      <c r="K38" s="178"/>
     </row>
     <row r="39" spans="1:11" ht="18" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="184" t="s">
+      <c r="B39" s="199" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="124"/>
-      <c r="D39" s="124"/>
-      <c r="E39" s="124"/>
+      <c r="C39" s="126"/>
+      <c r="D39" s="126"/>
+      <c r="E39" s="126"/>
       <c r="F39" s="159"/>
       <c r="G39" s="91">
         <f>SUM(G9:G38)</f>
@@ -16144,12 +16178,12 @@
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
       <c r="G40" s="23"/>
-      <c r="H40" s="185" t="s">
+      <c r="H40" s="196" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="126"/>
-      <c r="J40" s="126"/>
-      <c r="K40" s="127"/>
+      <c r="I40" s="133"/>
+      <c r="J40" s="133"/>
+      <c r="K40" s="134"/>
     </row>
     <row r="41" spans="1:11" ht="20.25" customHeight="1">
       <c r="A41" s="1"/>
@@ -16163,12 +16197,12 @@
       <c r="G41" s="26">
         <v>21</v>
       </c>
-      <c r="H41" s="186" t="s">
+      <c r="H41" s="197" t="s">
         <v>17</v>
       </c>
-      <c r="I41" s="117"/>
-      <c r="J41" s="117"/>
-      <c r="K41" s="116"/>
+      <c r="I41" s="128"/>
+      <c r="J41" s="128"/>
+      <c r="K41" s="123"/>
     </row>
     <row r="42" spans="1:11" ht="20.25" customHeight="1">
       <c r="A42" s="1"/>
@@ -16182,10 +16216,10 @@
       <c r="G42" s="27">
         <v>9</v>
       </c>
-      <c r="H42" s="117"/>
-      <c r="I42" s="117"/>
-      <c r="J42" s="117"/>
-      <c r="K42" s="116"/>
+      <c r="H42" s="128"/>
+      <c r="I42" s="128"/>
+      <c r="J42" s="128"/>
+      <c r="K42" s="123"/>
     </row>
     <row r="43" spans="1:11" ht="20.25" customHeight="1">
       <c r="A43" s="1"/>
@@ -16199,10 +16233,10 @@
       <c r="G43" s="27">
         <v>1</v>
       </c>
-      <c r="H43" s="124"/>
-      <c r="I43" s="124"/>
-      <c r="J43" s="124"/>
-      <c r="K43" s="120"/>
+      <c r="H43" s="126"/>
+      <c r="I43" s="126"/>
+      <c r="J43" s="126"/>
+      <c r="K43" s="125"/>
     </row>
     <row r="44" spans="1:11" ht="20.25" customHeight="1">
       <c r="A44" s="1"/>
@@ -16235,7 +16269,7 @@
       <c r="G45" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H45" s="186" t="s">
+      <c r="H45" s="197" t="s">
         <v>23</v>
       </c>
       <c r="I45" s="1"/>
@@ -16254,7 +16288,7 @@
       <c r="G46" s="27">
         <v>19</v>
       </c>
-      <c r="H46" s="124"/>
+      <c r="H46" s="126"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="48"/>
@@ -16275,10 +16309,10 @@
       <c r="H47" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="I47" s="131" t="s">
+      <c r="I47" s="171" t="s">
         <v>27</v>
       </c>
-      <c r="J47" s="132"/>
+      <c r="J47" s="172"/>
       <c r="K47" s="32" t="s">
         <v>28</v>
       </c>
@@ -16296,10 +16330,10 @@
       <c r="H48" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="I48" s="118" t="s">
+      <c r="I48" s="163" t="s">
         <v>29</v>
       </c>
-      <c r="J48" s="116"/>
+      <c r="J48" s="123"/>
       <c r="K48" s="37" t="s">
         <v>29</v>
       </c>
@@ -16319,10 +16353,10 @@
       <c r="H49" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="I49" s="118" t="s">
+      <c r="I49" s="163" t="s">
         <v>31</v>
       </c>
-      <c r="J49" s="116"/>
+      <c r="J49" s="123"/>
       <c r="K49" s="37" t="s">
         <v>31</v>
       </c>
@@ -16343,10 +16377,10 @@
       <c r="H50" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="I50" s="118" t="s">
+      <c r="I50" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="J50" s="116"/>
+      <c r="J50" s="123"/>
       <c r="K50" s="37" t="s">
         <v>33</v>
       </c>
@@ -16367,10 +16401,10 @@
       <c r="H51" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="I51" s="119" t="s">
+      <c r="I51" s="164" t="s">
         <v>35</v>
       </c>
-      <c r="J51" s="120"/>
+      <c r="J51" s="125"/>
       <c r="K51" s="43" t="s">
         <v>35</v>
       </c>
@@ -16393,23 +16427,23 @@
       <c r="B53" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C53" s="114" t="s">
+      <c r="C53" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="D53" s="116"/>
-      <c r="E53" s="114" t="s">
+      <c r="D53" s="123"/>
+      <c r="E53" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="F53" s="117"/>
-      <c r="G53" s="116"/>
-      <c r="H53" s="187" t="s">
+      <c r="F53" s="128"/>
+      <c r="G53" s="123"/>
+      <c r="H53" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="I53" s="116"/>
-      <c r="J53" s="114" t="s">
+      <c r="I53" s="123"/>
+      <c r="J53" s="161" t="s">
         <v>106</v>
       </c>
-      <c r="K53" s="116"/>
+      <c r="K53" s="123"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1">
       <c r="A54" s="1"/>
@@ -16466,42 +16500,42 @@
     <row r="58" spans="1:11" ht="15.75" customHeight="1">
       <c r="A58" s="51"/>
       <c r="B58" s="52"/>
-      <c r="C58" s="162" t="s">
+      <c r="C58" s="127" t="s">
         <v>143</v>
       </c>
-      <c r="D58" s="116"/>
-      <c r="E58" s="162" t="s">
+      <c r="D58" s="123"/>
+      <c r="E58" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="F58" s="117"/>
-      <c r="G58" s="116"/>
-      <c r="H58" s="188" t="s">
+      <c r="F58" s="128"/>
+      <c r="G58" s="123"/>
+      <c r="H58" s="194" t="s">
         <v>109</v>
       </c>
-      <c r="I58" s="116"/>
-      <c r="J58" s="162" t="s">
+      <c r="I58" s="123"/>
+      <c r="J58" s="127" t="s">
         <v>110</v>
       </c>
-      <c r="K58" s="116"/>
+      <c r="K58" s="123"/>
     </row>
     <row r="59" spans="1:11" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="53"/>
-      <c r="C59" s="161"/>
-      <c r="D59" s="120"/>
-      <c r="E59" s="161" t="s">
+      <c r="C59" s="124"/>
+      <c r="D59" s="125"/>
+      <c r="E59" s="124" t="s">
         <v>111</v>
       </c>
-      <c r="F59" s="124"/>
-      <c r="G59" s="120"/>
-      <c r="H59" s="189" t="s">
+      <c r="F59" s="126"/>
+      <c r="G59" s="125"/>
+      <c r="H59" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="I59" s="120"/>
-      <c r="J59" s="161" t="s">
+      <c r="I59" s="125"/>
+      <c r="J59" s="124" t="s">
         <v>113</v>
       </c>
-      <c r="K59" s="120"/>
+      <c r="K59" s="125"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
@@ -19846,54 +19880,11 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="B2:D5"/>
-    <mergeCell ref="E2:H3"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="B39:F39"/>
     <mergeCell ref="H40:K40"/>
     <mergeCell ref="H41:K43"/>
     <mergeCell ref="E53:G53"/>
@@ -19905,11 +19896,54 @@
     <mergeCell ref="I49:J49"/>
     <mergeCell ref="I50:J50"/>
     <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="E2:H3"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>

--- a/TimesheetBankJakarta_Anggit_Ari_Utomo_2.xlsx
+++ b/TimesheetBankJakarta_Anggit_Ari_Utomo_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\anggit\Documents\absen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665529B1-CBC4-4C07-A5D2-9DC1FA0A8CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1310801A-EC35-460E-8356-3882AD47CC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2128,7 +2128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="200">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2495,29 +2495,62 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2528,20 +2561,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2612,68 +2636,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2705,17 +2678,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2726,11 +2717,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5454,137 +5451,137 @@
     </row>
     <row r="2" spans="1:12" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="136"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="132" t="s">
+      <c r="B2" s="145"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="143" t="s">
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="148"/>
+      <c r="J2" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="133"/>
-      <c r="L2" s="134"/>
+      <c r="K2" s="134"/>
+      <c r="L2" s="135"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="128"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="142"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
-      <c r="L3" s="144"/>
+      <c r="B3" s="130"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="147"/>
+      <c r="L3" s="152"/>
     </row>
     <row r="4" spans="1:12" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="137"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="145" t="s">
+      <c r="B4" s="130"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="153" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="148" t="s">
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="154"/>
+      <c r="I4" s="155"/>
+      <c r="J4" s="156" t="s">
         <v>152</v>
       </c>
-      <c r="K4" s="149"/>
-      <c r="L4" s="150"/>
+      <c r="K4" s="157"/>
+      <c r="L4" s="158"/>
     </row>
     <row r="5" spans="1:12" ht="14.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="138"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="139"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="147"/>
       <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="151" t="s">
+      <c r="F5" s="159" t="s">
         <v>146</v>
       </c>
-      <c r="G5" s="146"/>
-      <c r="H5" s="146"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="123"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="154"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="124"/>
     </row>
     <row r="6" spans="1:12" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="154" t="s">
+      <c r="B6" s="162" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="149"/>
-      <c r="D6" s="149"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="157"/>
       <c r="E6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="152">
+      <c r="F6" s="160">
         <v>0</v>
       </c>
-      <c r="G6" s="149"/>
-      <c r="H6" s="149"/>
-      <c r="I6" s="153"/>
-      <c r="J6" s="128"/>
-      <c r="K6" s="128"/>
-      <c r="L6" s="123"/>
+      <c r="G6" s="157"/>
+      <c r="H6" s="157"/>
+      <c r="I6" s="161"/>
+      <c r="J6" s="125"/>
+      <c r="K6" s="125"/>
+      <c r="L6" s="124"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="163" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="157" t="s">
+      <c r="C7" s="165" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="158"/>
-      <c r="E7" s="132" t="s">
+      <c r="D7" s="166"/>
+      <c r="E7" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="140"/>
-      <c r="G7" s="160" t="s">
+      <c r="F7" s="148"/>
+      <c r="G7" s="168" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="130" t="s">
+      <c r="H7" s="141" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="130" t="s">
+      <c r="I7" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="132" t="s">
+      <c r="J7" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="133"/>
-      <c r="L7" s="134"/>
+      <c r="K7" s="134"/>
+      <c r="L7" s="135"/>
     </row>
     <row r="8" spans="1:12" thickBot="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="156"/>
+      <c r="B8" s="164"/>
       <c r="C8" s="8">
         <v>0.33333333333333331</v>
       </c>
       <c r="D8" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="135"/>
-      <c r="F8" s="159"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="131"/>
-      <c r="I8" s="131"/>
-      <c r="J8" s="135"/>
-      <c r="K8" s="126"/>
-      <c r="L8" s="125"/>
+      <c r="E8" s="144"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="142"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142"/>
+      <c r="J8" s="144"/>
+      <c r="K8" s="132"/>
+      <c r="L8" s="128"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1">
       <c r="A9" s="9"/>
@@ -5920,10 +5917,12 @@
       <c r="E21" s="105">
         <v>0.37291666666666667</v>
       </c>
-      <c r="F21" s="8"/>
+      <c r="F21" s="8">
+        <v>0.7368055555555556</v>
+      </c>
       <c r="G21" s="11">
         <f t="shared" si="1"/>
-        <v>14.1</v>
+        <v>7.7</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14" t="s">
@@ -5946,11 +5945,15 @@
       <c r="D22" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E22" s="105"/>
-      <c r="F22" s="8"/>
+      <c r="E22" s="105">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="F22" s="8">
+        <v>0.75763888888888886</v>
+      </c>
       <c r="G22" s="11">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="14" t="s">
@@ -5973,11 +5976,15 @@
       <c r="D23" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E23" s="105"/>
-      <c r="F23" s="8"/>
+      <c r="E23" s="105">
+        <v>0.32361111111111113</v>
+      </c>
+      <c r="F23" s="8">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="G23" s="11">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H23" s="14"/>
       <c r="I23" s="14" t="s">
@@ -6232,7 +6239,7 @@
         <v>23</v>
       </c>
       <c r="H34" s="14"/>
-      <c r="I34" s="200" t="s">
+      <c r="I34" s="14" t="s">
         <v>149</v>
       </c>
       <c r="J34" s="119" t="s">
@@ -6259,7 +6266,7 @@
         <v>23</v>
       </c>
       <c r="H35" s="14"/>
-      <c r="I35" s="200" t="s">
+      <c r="I35" s="14" t="s">
         <v>149</v>
       </c>
       <c r="J35" s="119" t="s">
@@ -6286,7 +6293,7 @@
         <v>23</v>
       </c>
       <c r="H36" s="14"/>
-      <c r="I36" s="200" t="s">
+      <c r="I36" s="14" t="s">
         <v>149</v>
       </c>
       <c r="J36" s="119" t="s">
@@ -6313,7 +6320,7 @@
         <v>23</v>
       </c>
       <c r="H37" s="14"/>
-      <c r="I37" s="200" t="s">
+      <c r="I37" s="14" t="s">
         <v>149</v>
       </c>
       <c r="J37" s="119" t="s">
@@ -6369,16 +6376,16 @@
     </row>
     <row r="43" spans="1:12" ht="18" customHeight="1" thickBot="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="168" t="s">
+      <c r="B43" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="C43" s="169"/>
-      <c r="D43" s="169"/>
-      <c r="E43" s="169"/>
-      <c r="F43" s="170"/>
+      <c r="C43" s="137"/>
+      <c r="D43" s="137"/>
+      <c r="E43" s="137"/>
+      <c r="F43" s="138"/>
       <c r="G43" s="18">
         <f>SUM(G9:G39)</f>
-        <v>337.29999999999995</v>
+        <v>301.39999999999998</v>
       </c>
       <c r="H43" s="19"/>
       <c r="I43" s="19"/>
@@ -6396,13 +6403,13 @@
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
       <c r="G44" s="23"/>
-      <c r="H44" s="167" t="s">
+      <c r="H44" s="133" t="s">
         <v>15</v>
       </c>
-      <c r="I44" s="133"/>
-      <c r="J44" s="133"/>
-      <c r="K44" s="133"/>
-      <c r="L44" s="134"/>
+      <c r="I44" s="134"/>
+      <c r="J44" s="134"/>
+      <c r="K44" s="134"/>
+      <c r="L44" s="135"/>
     </row>
     <row r="45" spans="1:12" ht="20.25" customHeight="1">
       <c r="A45" s="1"/>
@@ -6416,13 +6423,13 @@
       <c r="G45" s="26">
         <v>22</v>
       </c>
-      <c r="H45" s="165" t="s">
+      <c r="H45" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="128"/>
-      <c r="J45" s="128"/>
-      <c r="K45" s="128"/>
-      <c r="L45" s="123"/>
+      <c r="I45" s="125"/>
+      <c r="J45" s="125"/>
+      <c r="K45" s="125"/>
+      <c r="L45" s="124"/>
     </row>
     <row r="46" spans="1:12" ht="20.25" customHeight="1">
       <c r="A46" s="1"/>
@@ -6436,11 +6443,11 @@
       <c r="G46" s="27">
         <v>0</v>
       </c>
-      <c r="H46" s="137"/>
-      <c r="I46" s="128"/>
-      <c r="J46" s="128"/>
-      <c r="K46" s="128"/>
-      <c r="L46" s="123"/>
+      <c r="H46" s="130"/>
+      <c r="I46" s="125"/>
+      <c r="J46" s="125"/>
+      <c r="K46" s="125"/>
+      <c r="L46" s="124"/>
     </row>
     <row r="47" spans="1:12" ht="20.25" customHeight="1" thickBot="1">
       <c r="A47" s="1"/>
@@ -6454,11 +6461,11 @@
       <c r="G47" s="27">
         <v>0</v>
       </c>
-      <c r="H47" s="166"/>
-      <c r="I47" s="126"/>
-      <c r="J47" s="126"/>
-      <c r="K47" s="126"/>
-      <c r="L47" s="125"/>
+      <c r="H47" s="131"/>
+      <c r="I47" s="132"/>
+      <c r="J47" s="132"/>
+      <c r="K47" s="132"/>
+      <c r="L47" s="128"/>
     </row>
     <row r="48" spans="1:12" ht="20.25" customHeight="1">
       <c r="A48" s="1"/>
@@ -6472,13 +6479,13 @@
       <c r="G48" s="27">
         <v>0</v>
       </c>
-      <c r="H48" s="167" t="s">
+      <c r="H48" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="I48" s="133"/>
-      <c r="J48" s="133"/>
-      <c r="K48" s="133"/>
-      <c r="L48" s="134"/>
+      <c r="I48" s="134"/>
+      <c r="J48" s="134"/>
+      <c r="K48" s="134"/>
+      <c r="L48" s="135"/>
     </row>
     <row r="49" spans="1:12" ht="20.25" customHeight="1">
       <c r="A49" s="1"/>
@@ -6492,13 +6499,13 @@
       <c r="G49" s="27">
         <v>0</v>
       </c>
-      <c r="H49" s="161" t="s">
+      <c r="H49" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="I49" s="128"/>
-      <c r="J49" s="128"/>
-      <c r="K49" s="128"/>
-      <c r="L49" s="123"/>
+      <c r="I49" s="125"/>
+      <c r="J49" s="125"/>
+      <c r="K49" s="125"/>
+      <c r="L49" s="124"/>
     </row>
     <row r="50" spans="1:12" ht="20.25" customHeight="1" thickBot="1">
       <c r="A50" s="1"/>
@@ -6512,11 +6519,11 @@
       <c r="G50" s="27">
         <v>22</v>
       </c>
-      <c r="H50" s="166"/>
-      <c r="I50" s="126"/>
-      <c r="J50" s="126"/>
-      <c r="K50" s="126"/>
-      <c r="L50" s="125"/>
+      <c r="H50" s="131"/>
+      <c r="I50" s="132"/>
+      <c r="J50" s="132"/>
+      <c r="K50" s="132"/>
+      <c r="L50" s="128"/>
     </row>
     <row r="51" spans="1:12" ht="24" customHeight="1" thickBot="1">
       <c r="A51" s="1"/>
@@ -6535,10 +6542,10 @@
         <v>26</v>
       </c>
       <c r="I51" s="31"/>
-      <c r="J51" s="171" t="s">
+      <c r="J51" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="K51" s="172"/>
+      <c r="K51" s="140"/>
       <c r="L51" s="32" t="s">
         <v>28</v>
       </c>
@@ -6557,10 +6564,10 @@
         <v>29</v>
       </c>
       <c r="I52" s="36"/>
-      <c r="J52" s="163" t="s">
+      <c r="J52" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="K52" s="123"/>
+      <c r="K52" s="124"/>
       <c r="L52" s="37" t="s">
         <v>29</v>
       </c>
@@ -6582,10 +6589,10 @@
         <v>31</v>
       </c>
       <c r="I53" s="36"/>
-      <c r="J53" s="163" t="s">
+      <c r="J53" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="K53" s="123"/>
+      <c r="K53" s="124"/>
       <c r="L53" s="37" t="s">
         <v>31</v>
       </c>
@@ -6601,16 +6608,16 @@
       <c r="F54" s="2"/>
       <c r="G54" s="26">
         <f>G43</f>
-        <v>337.29999999999995</v>
+        <v>301.39999999999998</v>
       </c>
       <c r="H54" s="35" t="s">
         <v>33</v>
       </c>
       <c r="I54" s="36"/>
-      <c r="J54" s="163" t="s">
+      <c r="J54" s="126" t="s">
         <v>33</v>
       </c>
-      <c r="K54" s="123"/>
+      <c r="K54" s="124"/>
       <c r="L54" s="37" t="s">
         <v>33</v>
       </c>
@@ -6626,16 +6633,16 @@
       <c r="F55" s="39"/>
       <c r="G55" s="40">
         <f>G54/G53</f>
-        <v>1.9164772727272725</v>
+        <v>1.7124999999999999</v>
       </c>
       <c r="H55" s="41" t="s">
         <v>35</v>
       </c>
       <c r="I55" s="42"/>
-      <c r="J55" s="164" t="s">
+      <c r="J55" s="127" t="s">
         <v>35</v>
       </c>
-      <c r="K55" s="125"/>
+      <c r="K55" s="128"/>
       <c r="L55" s="43" t="s">
         <v>35</v>
       </c>
@@ -6657,32 +6664,32 @@
     <row r="57" spans="1:12" ht="15.75" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="28"/>
-      <c r="C57" s="161" t="s">
+      <c r="C57" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="D57" s="123"/>
-      <c r="E57" s="161" t="s">
+      <c r="D57" s="124"/>
+      <c r="E57" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="F57" s="128"/>
-      <c r="G57" s="123"/>
-      <c r="H57" s="161" t="s">
+      <c r="F57" s="125"/>
+      <c r="G57" s="124"/>
+      <c r="H57" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="I57" s="128"/>
-      <c r="J57" s="123"/>
-      <c r="K57" s="161" t="s">
+      <c r="I57" s="125"/>
+      <c r="J57" s="124"/>
+      <c r="K57" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="L57" s="123"/>
+      <c r="L57" s="124"/>
     </row>
     <row r="58" spans="1:12" ht="15.75" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="161"/>
-      <c r="D58" s="162"/>
+      <c r="C58" s="122"/>
+      <c r="D58" s="123"/>
       <c r="E58" s="47"/>
       <c r="F58" s="1"/>
       <c r="G58" s="48"/>
@@ -6697,8 +6704,8 @@
       <c r="B59" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="C59" s="161"/>
-      <c r="D59" s="162"/>
+      <c r="C59" s="122"/>
+      <c r="D59" s="123"/>
       <c r="E59" s="47"/>
       <c r="F59" s="1"/>
       <c r="G59" s="48"/>
@@ -6713,8 +6720,8 @@
       <c r="B60" s="50">
         <v>46257</v>
       </c>
-      <c r="C60" s="161"/>
-      <c r="D60" s="162"/>
+      <c r="C60" s="122"/>
+      <c r="D60" s="123"/>
       <c r="E60" s="47"/>
       <c r="F60" s="1"/>
       <c r="G60" s="48"/>
@@ -6727,8 +6734,8 @@
     <row r="61" spans="1:12" ht="15.75" customHeight="1">
       <c r="A61" s="51"/>
       <c r="B61" s="47"/>
-      <c r="C61" s="161"/>
-      <c r="D61" s="162"/>
+      <c r="C61" s="122"/>
+      <c r="D61" s="123"/>
       <c r="E61" s="47"/>
       <c r="F61" s="1"/>
       <c r="G61" s="48"/>
@@ -6741,44 +6748,44 @@
     <row r="62" spans="1:12" ht="15.75" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="52"/>
-      <c r="C62" s="122" t="s">
+      <c r="C62" s="172" t="s">
         <v>151</v>
       </c>
-      <c r="D62" s="123"/>
-      <c r="E62" s="127" t="s">
+      <c r="D62" s="124"/>
+      <c r="E62" s="170" t="s">
         <v>41</v>
       </c>
-      <c r="F62" s="128"/>
-      <c r="G62" s="123"/>
-      <c r="H62" s="129" t="s">
+      <c r="F62" s="125"/>
+      <c r="G62" s="124"/>
+      <c r="H62" s="171" t="s">
         <v>145</v>
       </c>
-      <c r="I62" s="128"/>
-      <c r="J62" s="123"/>
-      <c r="K62" s="127" t="s">
+      <c r="I62" s="125"/>
+      <c r="J62" s="124"/>
+      <c r="K62" s="170" t="s">
         <v>42</v>
       </c>
-      <c r="L62" s="123"/>
+      <c r="L62" s="124"/>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A63" s="1"/>
       <c r="B63" s="53"/>
-      <c r="C63" s="124"/>
-      <c r="D63" s="125"/>
-      <c r="E63" s="124" t="s">
+      <c r="C63" s="169"/>
+      <c r="D63" s="128"/>
+      <c r="E63" s="169" t="s">
         <v>43</v>
       </c>
-      <c r="F63" s="126"/>
-      <c r="G63" s="125"/>
-      <c r="H63" s="124" t="s">
+      <c r="F63" s="132"/>
+      <c r="G63" s="128"/>
+      <c r="H63" s="169" t="s">
         <v>44</v>
       </c>
-      <c r="I63" s="126"/>
-      <c r="J63" s="125"/>
-      <c r="K63" s="124" t="s">
+      <c r="I63" s="132"/>
+      <c r="J63" s="128"/>
+      <c r="K63" s="169" t="s">
         <v>45</v>
       </c>
-      <c r="L63" s="125"/>
+      <c r="L63" s="128"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1">
       <c r="A64" s="1"/>
@@ -10318,6 +10325,48 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="H63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:L8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="E2:I3"/>
+    <mergeCell ref="J2:L3"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="J4:L6"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:G8"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="C58:D61"/>
     <mergeCell ref="C57:D57"/>
@@ -10334,48 +10383,6 @@
     <mergeCell ref="J51:K51"/>
     <mergeCell ref="H49:L50"/>
     <mergeCell ref="H44:L44"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:L8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="B2:D5"/>
-    <mergeCell ref="E2:I3"/>
-    <mergeCell ref="J2:L3"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="J4:L6"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="H63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="J30:L30"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="J16:L16"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.19685039370078741" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="81" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -10418,128 +10425,128 @@
     </row>
     <row r="2" spans="1:11" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="136"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="140"/>
-      <c r="E2" s="132" t="s">
+      <c r="B2" s="145"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="132" t="s">
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="133"/>
-      <c r="K2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="135"/>
     </row>
     <row r="3" spans="1:11" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="144"/>
+      <c r="B3" s="130"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="152"/>
     </row>
     <row r="4" spans="1:11" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="137"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="182"/>
-      <c r="E4" s="145" t="s">
+      <c r="B4" s="130"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="183" t="s">
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="155"/>
+      <c r="I4" s="174" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="149"/>
-      <c r="K4" s="150"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="158"/>
     </row>
     <row r="5" spans="1:11" ht="14.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="138"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="142"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="150"/>
       <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="151" t="s">
+      <c r="F5" s="159" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="146"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="184"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="123"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="124"/>
     </row>
     <row r="6" spans="1:11" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="179" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="187"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="178"/>
       <c r="E6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="185">
+      <c r="F6" s="176">
         <v>20230682322</v>
       </c>
-      <c r="G6" s="186"/>
-      <c r="H6" s="187"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="126"/>
-      <c r="K6" s="125"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="144"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="128"/>
     </row>
     <row r="7" spans="1:11" ht="14.4">
       <c r="A7" s="1"/>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="163" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="157" t="s">
+      <c r="C7" s="165" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="158"/>
-      <c r="E7" s="136" t="s">
+      <c r="D7" s="166"/>
+      <c r="E7" s="145" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="134"/>
-      <c r="G7" s="189" t="s">
+      <c r="F7" s="135"/>
+      <c r="G7" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="190" t="s">
+      <c r="H7" s="181" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="143" t="s">
+      <c r="I7" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="133"/>
-      <c r="K7" s="134"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="135"/>
     </row>
     <row r="8" spans="1:11" ht="14.4">
       <c r="A8" s="1"/>
-      <c r="B8" s="156"/>
+      <c r="B8" s="164"/>
       <c r="C8" s="8">
         <v>0.33333333333333331</v>
       </c>
       <c r="D8" s="55">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="166"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="126"/>
-      <c r="H8" s="191"/>
-      <c r="I8" s="126"/>
-      <c r="J8" s="126"/>
-      <c r="K8" s="125"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="182"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="128"/>
     </row>
     <row r="9" spans="1:11" ht="14.4">
       <c r="A9" s="2"/>
@@ -10564,11 +10571,11 @@
       <c r="H9" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="177" t="s">
+      <c r="I9" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="146"/>
-      <c r="K9" s="178"/>
+      <c r="J9" s="154"/>
+      <c r="K9" s="184"/>
     </row>
     <row r="10" spans="1:11" ht="14.4">
       <c r="A10" s="9"/>
@@ -10593,11 +10600,11 @@
       <c r="H10" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="177" t="s">
+      <c r="I10" s="183" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="146"/>
-      <c r="K10" s="178"/>
+      <c r="J10" s="154"/>
+      <c r="K10" s="184"/>
     </row>
     <row r="11" spans="1:11" ht="14.4">
       <c r="A11" s="2"/>
@@ -10622,11 +10629,11 @@
       <c r="H11" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I11" s="177" t="s">
+      <c r="I11" s="183" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="146"/>
-      <c r="K11" s="178"/>
+      <c r="J11" s="154"/>
+      <c r="K11" s="184"/>
     </row>
     <row r="12" spans="1:11" ht="14.4">
       <c r="A12" s="2"/>
@@ -10645,9 +10652,9 @@
         <v>0</v>
       </c>
       <c r="H12" s="13"/>
-      <c r="I12" s="177"/>
-      <c r="J12" s="146"/>
-      <c r="K12" s="178"/>
+      <c r="I12" s="183"/>
+      <c r="J12" s="154"/>
+      <c r="K12" s="184"/>
     </row>
     <row r="13" spans="1:11" ht="14.4">
       <c r="A13" s="2"/>
@@ -10666,9 +10673,9 @@
         <v>0</v>
       </c>
       <c r="H13" s="13"/>
-      <c r="I13" s="177"/>
-      <c r="J13" s="146"/>
-      <c r="K13" s="178"/>
+      <c r="I13" s="183"/>
+      <c r="J13" s="154"/>
+      <c r="K13" s="184"/>
     </row>
     <row r="14" spans="1:11" ht="14.4">
       <c r="A14" s="2"/>
@@ -10693,11 +10700,11 @@
       <c r="H14" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I14" s="177" t="s">
+      <c r="I14" s="183" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="146"/>
-      <c r="K14" s="178"/>
+      <c r="J14" s="154"/>
+      <c r="K14" s="184"/>
     </row>
     <row r="15" spans="1:11" ht="14.4">
       <c r="A15" s="2"/>
@@ -10722,11 +10729,11 @@
       <c r="H15" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="177" t="s">
+      <c r="I15" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="146"/>
-      <c r="K15" s="178"/>
+      <c r="J15" s="154"/>
+      <c r="K15" s="184"/>
     </row>
     <row r="16" spans="1:11" ht="14.4">
       <c r="A16" s="2"/>
@@ -10745,9 +10752,9 @@
         <v>0</v>
       </c>
       <c r="H16" s="11"/>
-      <c r="I16" s="181"/>
-      <c r="J16" s="146"/>
-      <c r="K16" s="178"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="154"/>
+      <c r="K16" s="184"/>
     </row>
     <row r="17" spans="1:11" ht="14.4">
       <c r="A17" s="2"/>
@@ -10772,11 +10779,11 @@
       <c r="H17" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="177" t="s">
+      <c r="I17" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="J17" s="146"/>
-      <c r="K17" s="178"/>
+      <c r="J17" s="154"/>
+      <c r="K17" s="184"/>
     </row>
     <row r="18" spans="1:11" ht="14.4">
       <c r="A18" s="2"/>
@@ -10801,11 +10808,11 @@
       <c r="H18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="177" t="s">
+      <c r="I18" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="J18" s="146"/>
-      <c r="K18" s="178"/>
+      <c r="J18" s="154"/>
+      <c r="K18" s="184"/>
     </row>
     <row r="19" spans="1:11" ht="14.4">
       <c r="A19" s="2"/>
@@ -10824,9 +10831,9 @@
         <v>0</v>
       </c>
       <c r="H19" s="11"/>
-      <c r="I19" s="181"/>
-      <c r="J19" s="146"/>
-      <c r="K19" s="178"/>
+      <c r="I19" s="185"/>
+      <c r="J19" s="154"/>
+      <c r="K19" s="184"/>
     </row>
     <row r="20" spans="1:11" ht="14.4">
       <c r="A20" s="2"/>
@@ -10845,9 +10852,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="11"/>
-      <c r="I20" s="181"/>
-      <c r="J20" s="146"/>
-      <c r="K20" s="178"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="154"/>
+      <c r="K20" s="184"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1">
       <c r="A21" s="2"/>
@@ -10872,11 +10879,11 @@
       <c r="H21" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I21" s="177" t="s">
+      <c r="I21" s="183" t="s">
         <v>68</v>
       </c>
-      <c r="J21" s="146"/>
-      <c r="K21" s="178"/>
+      <c r="J21" s="154"/>
+      <c r="K21" s="184"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
       <c r="A22" s="2"/>
@@ -10901,11 +10908,11 @@
       <c r="H22" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="177" t="s">
+      <c r="I22" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="146"/>
-      <c r="K22" s="178"/>
+      <c r="J22" s="154"/>
+      <c r="K22" s="184"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
       <c r="A23" s="2"/>
@@ -10930,11 +10937,11 @@
       <c r="H23" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="177" t="s">
+      <c r="I23" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="146"/>
-      <c r="K23" s="178"/>
+      <c r="J23" s="154"/>
+      <c r="K23" s="184"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="2"/>
@@ -10959,11 +10966,11 @@
       <c r="H24" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="177" t="s">
+      <c r="I24" s="183" t="s">
         <v>72</v>
       </c>
-      <c r="J24" s="146"/>
-      <c r="K24" s="178"/>
+      <c r="J24" s="154"/>
+      <c r="K24" s="184"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1">
       <c r="A25" s="2"/>
@@ -10988,11 +10995,11 @@
       <c r="H25" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="177" t="s">
+      <c r="I25" s="183" t="s">
         <v>74</v>
       </c>
-      <c r="J25" s="146"/>
-      <c r="K25" s="178"/>
+      <c r="J25" s="154"/>
+      <c r="K25" s="184"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1">
       <c r="A26" s="2"/>
@@ -11011,9 +11018,9 @@
         <v>0</v>
       </c>
       <c r="H26" s="11"/>
-      <c r="I26" s="181"/>
-      <c r="J26" s="146"/>
-      <c r="K26" s="178"/>
+      <c r="I26" s="185"/>
+      <c r="J26" s="154"/>
+      <c r="K26" s="184"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
       <c r="A27" s="2"/>
@@ -11032,9 +11039,9 @@
         <v>0</v>
       </c>
       <c r="H27" s="11"/>
-      <c r="I27" s="181"/>
-      <c r="J27" s="146"/>
-      <c r="K27" s="178"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="154"/>
+      <c r="K27" s="184"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1">
       <c r="A28" s="2"/>
@@ -11059,11 +11066,11 @@
       <c r="H28" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I28" s="177" t="s">
+      <c r="I28" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="J28" s="146"/>
-      <c r="K28" s="178"/>
+      <c r="J28" s="154"/>
+      <c r="K28" s="184"/>
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1">
       <c r="A29" s="2"/>
@@ -11088,11 +11095,11 @@
       <c r="H29" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="177" t="s">
+      <c r="I29" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="J29" s="146"/>
-      <c r="K29" s="178"/>
+      <c r="J29" s="154"/>
+      <c r="K29" s="184"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="2"/>
@@ -11117,11 +11124,11 @@
       <c r="H30" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I30" s="177" t="s">
+      <c r="I30" s="183" t="s">
         <v>82</v>
       </c>
-      <c r="J30" s="146"/>
-      <c r="K30" s="178"/>
+      <c r="J30" s="154"/>
+      <c r="K30" s="184"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1">
       <c r="A31" s="2"/>
@@ -11146,11 +11153,11 @@
       <c r="H31" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I31" s="177" t="s">
+      <c r="I31" s="183" t="s">
         <v>84</v>
       </c>
-      <c r="J31" s="146"/>
-      <c r="K31" s="178"/>
+      <c r="J31" s="154"/>
+      <c r="K31" s="184"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="2"/>
@@ -11175,11 +11182,11 @@
       <c r="H32" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I32" s="177" t="s">
+      <c r="I32" s="183" t="s">
         <v>86</v>
       </c>
-      <c r="J32" s="146"/>
-      <c r="K32" s="178"/>
+      <c r="J32" s="154"/>
+      <c r="K32" s="184"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1">
       <c r="A33" s="2"/>
@@ -11198,9 +11205,9 @@
         <v>0</v>
       </c>
       <c r="H33" s="11"/>
-      <c r="I33" s="181"/>
-      <c r="J33" s="146"/>
-      <c r="K33" s="178"/>
+      <c r="I33" s="185"/>
+      <c r="J33" s="154"/>
+      <c r="K33" s="184"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1">
       <c r="A34" s="2"/>
@@ -11219,9 +11226,9 @@
         <v>0</v>
       </c>
       <c r="H34" s="11"/>
-      <c r="I34" s="181"/>
-      <c r="J34" s="146"/>
-      <c r="K34" s="178"/>
+      <c r="I34" s="185"/>
+      <c r="J34" s="154"/>
+      <c r="K34" s="184"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1">
       <c r="A35" s="2"/>
@@ -11246,11 +11253,11 @@
       <c r="H35" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I35" s="177" t="s">
+      <c r="I35" s="183" t="s">
         <v>90</v>
       </c>
-      <c r="J35" s="146"/>
-      <c r="K35" s="178"/>
+      <c r="J35" s="154"/>
+      <c r="K35" s="184"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1">
       <c r="A36" s="2"/>
@@ -11275,11 +11282,11 @@
       <c r="H36" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I36" s="177" t="s">
+      <c r="I36" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="J36" s="146"/>
-      <c r="K36" s="178"/>
+      <c r="J36" s="154"/>
+      <c r="K36" s="184"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1">
       <c r="A37" s="2"/>
@@ -11304,11 +11311,11 @@
       <c r="H37" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I37" s="177" t="s">
+      <c r="I37" s="183" t="s">
         <v>68</v>
       </c>
-      <c r="J37" s="146"/>
-      <c r="K37" s="178"/>
+      <c r="J37" s="154"/>
+      <c r="K37" s="184"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1">
       <c r="A38" s="2"/>
@@ -11333,11 +11340,11 @@
       <c r="H38" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I38" s="177" t="s">
+      <c r="I38" s="183" t="s">
         <v>94</v>
       </c>
-      <c r="J38" s="146"/>
-      <c r="K38" s="178"/>
+      <c r="J38" s="154"/>
+      <c r="K38" s="184"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1">
       <c r="A39" s="2"/>
@@ -11362,21 +11369,21 @@
       <c r="H39" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I39" s="180" t="s">
+      <c r="I39" s="187" t="s">
         <v>94</v>
       </c>
-      <c r="J39" s="149"/>
-      <c r="K39" s="150"/>
+      <c r="J39" s="157"/>
+      <c r="K39" s="158"/>
     </row>
     <row r="40" spans="1:11" ht="18" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="168" t="s">
+      <c r="B40" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="173"/>
-      <c r="D40" s="173"/>
-      <c r="E40" s="173"/>
-      <c r="F40" s="174"/>
+      <c r="C40" s="188"/>
+      <c r="D40" s="188"/>
+      <c r="E40" s="188"/>
+      <c r="F40" s="189"/>
       <c r="G40" s="18">
         <f>SUM(G9:G39)</f>
         <v>176</v>
@@ -11396,12 +11403,12 @@
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
       <c r="G41" s="23"/>
-      <c r="H41" s="175" t="s">
+      <c r="H41" s="190" t="s">
         <v>15</v>
       </c>
-      <c r="I41" s="133"/>
-      <c r="J41" s="133"/>
-      <c r="K41" s="134"/>
+      <c r="I41" s="134"/>
+      <c r="J41" s="134"/>
+      <c r="K41" s="135"/>
     </row>
     <row r="42" spans="1:11" ht="20.25" customHeight="1">
       <c r="A42" s="1"/>
@@ -11415,12 +11422,12 @@
       <c r="G42" s="26">
         <v>22</v>
       </c>
-      <c r="H42" s="176" t="s">
+      <c r="H42" s="191" t="s">
         <v>17</v>
       </c>
-      <c r="I42" s="128"/>
-      <c r="J42" s="128"/>
-      <c r="K42" s="123"/>
+      <c r="I42" s="125"/>
+      <c r="J42" s="125"/>
+      <c r="K42" s="124"/>
     </row>
     <row r="43" spans="1:11" ht="20.25" customHeight="1">
       <c r="A43" s="1"/>
@@ -11434,10 +11441,10 @@
       <c r="G43" s="27">
         <v>9</v>
       </c>
-      <c r="H43" s="128"/>
-      <c r="I43" s="128"/>
-      <c r="J43" s="128"/>
-      <c r="K43" s="123"/>
+      <c r="H43" s="125"/>
+      <c r="I43" s="125"/>
+      <c r="J43" s="125"/>
+      <c r="K43" s="124"/>
     </row>
     <row r="44" spans="1:11" ht="20.25" customHeight="1">
       <c r="A44" s="1"/>
@@ -11451,10 +11458,10 @@
       <c r="G44" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H44" s="126"/>
-      <c r="I44" s="126"/>
-      <c r="J44" s="126"/>
-      <c r="K44" s="125"/>
+      <c r="H44" s="132"/>
+      <c r="I44" s="132"/>
+      <c r="J44" s="132"/>
+      <c r="K44" s="128"/>
     </row>
     <row r="45" spans="1:11" ht="20.25" customHeight="1">
       <c r="A45" s="1"/>
@@ -11487,7 +11494,7 @@
       <c r="G46" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H46" s="179" t="s">
+      <c r="H46" s="186" t="s">
         <v>23</v>
       </c>
       <c r="I46" s="1"/>
@@ -11506,7 +11513,7 @@
       <c r="G47" s="27">
         <v>22</v>
       </c>
-      <c r="H47" s="126"/>
+      <c r="H47" s="132"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="48"/>
@@ -11527,10 +11534,10 @@
       <c r="H48" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="I48" s="171" t="s">
+      <c r="I48" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="J48" s="172"/>
+      <c r="J48" s="140"/>
       <c r="K48" s="32" t="s">
         <v>28</v>
       </c>
@@ -11548,10 +11555,10 @@
       <c r="H49" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="I49" s="163" t="s">
+      <c r="I49" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="J49" s="123"/>
+      <c r="J49" s="124"/>
       <c r="K49" s="37" t="s">
         <v>29</v>
       </c>
@@ -11572,10 +11579,10 @@
       <c r="H50" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="I50" s="163" t="s">
+      <c r="I50" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="J50" s="123"/>
+      <c r="J50" s="124"/>
       <c r="K50" s="37" t="s">
         <v>31</v>
       </c>
@@ -11596,10 +11603,10 @@
       <c r="H51" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I51" s="163" t="s">
+      <c r="I51" s="126" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="123"/>
+      <c r="J51" s="124"/>
       <c r="K51" s="37" t="s">
         <v>33</v>
       </c>
@@ -11620,10 +11627,10 @@
       <c r="H52" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="I52" s="164" t="s">
+      <c r="I52" s="127" t="s">
         <v>35</v>
       </c>
-      <c r="J52" s="125"/>
+      <c r="J52" s="128"/>
       <c r="K52" s="43" t="s">
         <v>35</v>
       </c>
@@ -11646,23 +11653,23 @@
       <c r="B54" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="161" t="s">
+      <c r="C54" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="D54" s="123"/>
-      <c r="E54" s="161" t="s">
+      <c r="D54" s="124"/>
+      <c r="E54" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="F54" s="128"/>
-      <c r="G54" s="123"/>
-      <c r="H54" s="161" t="s">
+      <c r="F54" s="125"/>
+      <c r="G54" s="124"/>
+      <c r="H54" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="I54" s="123"/>
-      <c r="J54" s="161" t="s">
+      <c r="I54" s="124"/>
+      <c r="J54" s="122" t="s">
         <v>106</v>
       </c>
-      <c r="K54" s="123"/>
+      <c r="K54" s="124"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1">
       <c r="A55" s="1"/>
@@ -11719,42 +11726,42 @@
     <row r="59" spans="1:11" ht="15.75" customHeight="1">
       <c r="A59" s="51"/>
       <c r="B59" s="52"/>
-      <c r="C59" s="127" t="s">
+      <c r="C59" s="170" t="s">
         <v>107</v>
       </c>
-      <c r="D59" s="123"/>
-      <c r="E59" s="127" t="s">
+      <c r="D59" s="124"/>
+      <c r="E59" s="170" t="s">
         <v>108</v>
       </c>
-      <c r="F59" s="128"/>
-      <c r="G59" s="123"/>
-      <c r="H59" s="127" t="s">
+      <c r="F59" s="125"/>
+      <c r="G59" s="124"/>
+      <c r="H59" s="170" t="s">
         <v>109</v>
       </c>
-      <c r="I59" s="123"/>
-      <c r="J59" s="127" t="s">
+      <c r="I59" s="124"/>
+      <c r="J59" s="170" t="s">
         <v>110</v>
       </c>
-      <c r="K59" s="123"/>
+      <c r="K59" s="124"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="53"/>
-      <c r="C60" s="124"/>
-      <c r="D60" s="125"/>
-      <c r="E60" s="124" t="s">
+      <c r="C60" s="169"/>
+      <c r="D60" s="128"/>
+      <c r="E60" s="169" t="s">
         <v>111</v>
       </c>
-      <c r="F60" s="126"/>
-      <c r="G60" s="125"/>
-      <c r="H60" s="124" t="s">
+      <c r="F60" s="132"/>
+      <c r="G60" s="128"/>
+      <c r="H60" s="169" t="s">
         <v>112</v>
       </c>
-      <c r="I60" s="125"/>
-      <c r="J60" s="124" t="s">
+      <c r="I60" s="128"/>
+      <c r="J60" s="169" t="s">
         <v>113</v>
       </c>
-      <c r="K60" s="125"/>
+      <c r="K60" s="128"/>
     </row>
     <row r="61" spans="1:11" ht="15.75" customHeight="1">
       <c r="A61" s="1"/>
@@ -15098,6 +15105,56 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="H42:K44"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="E2:H3"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K6"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:K8"/>
+    <mergeCell ref="I9:K9"/>
     <mergeCell ref="C60:D60"/>
     <mergeCell ref="E60:G60"/>
     <mergeCell ref="H60:I60"/>
@@ -15114,56 +15171,6 @@
     <mergeCell ref="C59:D59"/>
     <mergeCell ref="E59:G59"/>
     <mergeCell ref="H59:I59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="B2:D5"/>
-    <mergeCell ref="E2:H3"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K6"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="H42:K44"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I37:K37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -15207,56 +15214,56 @@
     </row>
     <row r="2" spans="1:11" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="136"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="140"/>
-      <c r="E2" s="132" t="s">
+      <c r="B2" s="145"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="132" t="s">
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="133"/>
-      <c r="K2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="135"/>
     </row>
     <row r="3" spans="1:11" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="144"/>
+      <c r="B3" s="130"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="152"/>
     </row>
     <row r="4" spans="1:11" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="137"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="182"/>
-      <c r="E4" s="145" t="s">
+      <c r="B4" s="130"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="183" t="s">
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="155"/>
+      <c r="I4" s="174" t="s">
         <v>116</v>
       </c>
-      <c r="J4" s="149"/>
-      <c r="K4" s="150"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="158"/>
     </row>
     <row r="5" spans="1:11" ht="14.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="138"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="142"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="150"/>
       <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
@@ -15265,70 +15272,70 @@
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="83"/>
-      <c r="I5" s="184"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="123"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="124"/>
     </row>
     <row r="6" spans="1:11" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="179" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="187"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="178"/>
       <c r="E6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="185">
+      <c r="F6" s="176">
         <v>20230682322</v>
       </c>
-      <c r="G6" s="186"/>
-      <c r="H6" s="187"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="126"/>
-      <c r="K6" s="125"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="144"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="128"/>
     </row>
     <row r="7" spans="1:11" ht="14.4">
       <c r="A7" s="1"/>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="163" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="157" t="s">
+      <c r="C7" s="165" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="158"/>
-      <c r="E7" s="136" t="s">
+      <c r="D7" s="166"/>
+      <c r="E7" s="145" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="134"/>
-      <c r="G7" s="189" t="s">
+      <c r="F7" s="135"/>
+      <c r="G7" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="193" t="s">
+      <c r="H7" s="198" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="143" t="s">
+      <c r="I7" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="133"/>
-      <c r="K7" s="134"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="135"/>
     </row>
     <row r="8" spans="1:11" ht="14.4">
       <c r="A8" s="1"/>
-      <c r="B8" s="156"/>
+      <c r="B8" s="164"/>
       <c r="C8" s="8">
         <v>0.33333333333333331</v>
       </c>
       <c r="D8" s="55">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="166"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="126"/>
-      <c r="H8" s="191"/>
-      <c r="I8" s="126"/>
-      <c r="J8" s="126"/>
-      <c r="K8" s="125"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="182"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="128"/>
     </row>
     <row r="9" spans="1:11" ht="14.4">
       <c r="A9" s="1"/>
@@ -15354,11 +15361,11 @@
       <c r="H9" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I9" s="181" t="s">
+      <c r="I9" s="185" t="s">
         <v>117</v>
       </c>
-      <c r="J9" s="146"/>
-      <c r="K9" s="178"/>
+      <c r="J9" s="154"/>
+      <c r="K9" s="184"/>
     </row>
     <row r="10" spans="1:11" ht="14.4">
       <c r="A10" s="82"/>
@@ -15384,11 +15391,11 @@
       <c r="H10" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I10" s="181" t="s">
+      <c r="I10" s="185" t="s">
         <v>118</v>
       </c>
-      <c r="J10" s="146"/>
-      <c r="K10" s="178"/>
+      <c r="J10" s="154"/>
+      <c r="K10" s="184"/>
     </row>
     <row r="11" spans="1:11" ht="14.4">
       <c r="A11" s="1"/>
@@ -15414,11 +15421,11 @@
       <c r="H11" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I11" s="181" t="s">
+      <c r="I11" s="185" t="s">
         <v>119</v>
       </c>
-      <c r="J11" s="146"/>
-      <c r="K11" s="178"/>
+      <c r="J11" s="154"/>
+      <c r="K11" s="184"/>
     </row>
     <row r="12" spans="1:11" ht="14.4">
       <c r="A12" s="1"/>
@@ -15444,11 +15451,11 @@
       <c r="H12" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I12" s="177" t="s">
+      <c r="I12" s="183" t="s">
         <v>120</v>
       </c>
-      <c r="J12" s="146"/>
-      <c r="K12" s="178"/>
+      <c r="J12" s="154"/>
+      <c r="K12" s="184"/>
     </row>
     <row r="13" spans="1:11" ht="21.75" customHeight="1">
       <c r="A13" s="1"/>
@@ -15468,9 +15475,9 @@
         <v>0</v>
       </c>
       <c r="H13" s="83"/>
-      <c r="I13" s="177"/>
-      <c r="J13" s="146"/>
-      <c r="K13" s="178"/>
+      <c r="I13" s="183"/>
+      <c r="J13" s="154"/>
+      <c r="K13" s="184"/>
     </row>
     <row r="14" spans="1:11" ht="21.75" customHeight="1">
       <c r="A14" s="1"/>
@@ -15490,9 +15497,9 @@
         <v>0</v>
       </c>
       <c r="H14" s="83"/>
-      <c r="I14" s="181"/>
-      <c r="J14" s="146"/>
-      <c r="K14" s="178"/>
+      <c r="I14" s="185"/>
+      <c r="J14" s="154"/>
+      <c r="K14" s="184"/>
     </row>
     <row r="15" spans="1:11" ht="14.4">
       <c r="A15" s="1"/>
@@ -15518,11 +15525,11 @@
       <c r="H15" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="181" t="s">
+      <c r="I15" s="185" t="s">
         <v>121</v>
       </c>
-      <c r="J15" s="146"/>
-      <c r="K15" s="178"/>
+      <c r="J15" s="154"/>
+      <c r="K15" s="184"/>
     </row>
     <row r="16" spans="1:11" ht="20.25" customHeight="1">
       <c r="A16" s="1"/>
@@ -15544,11 +15551,11 @@
       <c r="H16" s="93" t="s">
         <v>122</v>
       </c>
-      <c r="I16" s="181" t="s">
+      <c r="I16" s="185" t="s">
         <v>123</v>
       </c>
-      <c r="J16" s="146"/>
-      <c r="K16" s="178"/>
+      <c r="J16" s="154"/>
+      <c r="K16" s="184"/>
     </row>
     <row r="17" spans="1:11" ht="14.4">
       <c r="A17" s="1"/>
@@ -15574,11 +15581,11 @@
       <c r="H17" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="192" t="s">
+      <c r="I17" s="199" t="s">
         <v>124</v>
       </c>
-      <c r="J17" s="146"/>
-      <c r="K17" s="178"/>
+      <c r="J17" s="154"/>
+      <c r="K17" s="184"/>
     </row>
     <row r="18" spans="1:11" ht="14.4">
       <c r="A18" s="1"/>
@@ -15604,11 +15611,11 @@
       <c r="H18" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="181" t="s">
+      <c r="I18" s="185" t="s">
         <v>121</v>
       </c>
-      <c r="J18" s="146"/>
-      <c r="K18" s="178"/>
+      <c r="J18" s="154"/>
+      <c r="K18" s="184"/>
     </row>
     <row r="19" spans="1:11" ht="14.4">
       <c r="A19" s="1"/>
@@ -15634,11 +15641,11 @@
       <c r="H19" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I19" s="181" t="s">
+      <c r="I19" s="185" t="s">
         <v>125</v>
       </c>
-      <c r="J19" s="146"/>
-      <c r="K19" s="178"/>
+      <c r="J19" s="154"/>
+      <c r="K19" s="184"/>
     </row>
     <row r="20" spans="1:11" ht="21.75" customHeight="1">
       <c r="A20" s="1"/>
@@ -15658,9 +15665,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="83"/>
-      <c r="I20" s="181"/>
-      <c r="J20" s="146"/>
-      <c r="K20" s="178"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="154"/>
+      <c r="K20" s="184"/>
     </row>
     <row r="21" spans="1:11" ht="21.75" customHeight="1">
       <c r="A21" s="1"/>
@@ -15680,9 +15687,9 @@
         <v>0</v>
       </c>
       <c r="H21" s="83"/>
-      <c r="I21" s="181"/>
-      <c r="J21" s="146"/>
-      <c r="K21" s="178"/>
+      <c r="I21" s="185"/>
+      <c r="J21" s="154"/>
+      <c r="K21" s="184"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
@@ -15708,11 +15715,11 @@
       <c r="H22" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="181" t="s">
+      <c r="I22" s="185" t="s">
         <v>126</v>
       </c>
-      <c r="J22" s="146"/>
-      <c r="K22" s="178"/>
+      <c r="J22" s="154"/>
+      <c r="K22" s="184"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
       <c r="A23" s="1"/>
@@ -15738,11 +15745,11 @@
       <c r="H23" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="181" t="s">
+      <c r="I23" s="185" t="s">
         <v>127</v>
       </c>
-      <c r="J23" s="146"/>
-      <c r="K23" s="178"/>
+      <c r="J23" s="154"/>
+      <c r="K23" s="184"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
@@ -15768,11 +15775,11 @@
       <c r="H24" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="181" t="s">
+      <c r="I24" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J24" s="146"/>
-      <c r="K24" s="178"/>
+      <c r="J24" s="154"/>
+      <c r="K24" s="184"/>
     </row>
     <row r="25" spans="1:11" ht="21.75" customHeight="1">
       <c r="A25" s="1"/>
@@ -15792,9 +15799,9 @@
         <v>0</v>
       </c>
       <c r="H25" s="83"/>
-      <c r="I25" s="181"/>
-      <c r="J25" s="146"/>
-      <c r="K25" s="178"/>
+      <c r="I25" s="185"/>
+      <c r="J25" s="154"/>
+      <c r="K25" s="184"/>
     </row>
     <row r="26" spans="1:11" ht="31.5" customHeight="1">
       <c r="A26" s="1"/>
@@ -15820,11 +15827,11 @@
       <c r="H26" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="181" t="s">
+      <c r="I26" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J26" s="146"/>
-      <c r="K26" s="178"/>
+      <c r="J26" s="154"/>
+      <c r="K26" s="184"/>
     </row>
     <row r="27" spans="1:11" ht="21.75" customHeight="1">
       <c r="A27" s="1"/>
@@ -15844,9 +15851,9 @@
         <v>0</v>
       </c>
       <c r="H27" s="83"/>
-      <c r="I27" s="181"/>
-      <c r="J27" s="146"/>
-      <c r="K27" s="178"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="154"/>
+      <c r="K27" s="184"/>
     </row>
     <row r="28" spans="1:11" ht="21.75" customHeight="1">
       <c r="A28" s="1"/>
@@ -15866,9 +15873,9 @@
         <v>0</v>
       </c>
       <c r="H28" s="83"/>
-      <c r="I28" s="181"/>
-      <c r="J28" s="146"/>
-      <c r="K28" s="178"/>
+      <c r="I28" s="185"/>
+      <c r="J28" s="154"/>
+      <c r="K28" s="184"/>
     </row>
     <row r="29" spans="1:11" ht="29.25" customHeight="1">
       <c r="A29" s="1"/>
@@ -15894,11 +15901,11 @@
       <c r="H29" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="181" t="s">
+      <c r="I29" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J29" s="146"/>
-      <c r="K29" s="178"/>
+      <c r="J29" s="154"/>
+      <c r="K29" s="184"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
@@ -15924,11 +15931,11 @@
       <c r="H30" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I30" s="181" t="s">
+      <c r="I30" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J30" s="146"/>
-      <c r="K30" s="178"/>
+      <c r="J30" s="154"/>
+      <c r="K30" s="184"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1">
       <c r="A31" s="1"/>
@@ -15954,11 +15961,11 @@
       <c r="H31" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I31" s="181" t="s">
+      <c r="I31" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J31" s="146"/>
-      <c r="K31" s="178"/>
+      <c r="J31" s="154"/>
+      <c r="K31" s="184"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="1"/>
@@ -15984,11 +15991,11 @@
       <c r="H32" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I32" s="181" t="s">
+      <c r="I32" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J32" s="146"/>
-      <c r="K32" s="178"/>
+      <c r="J32" s="154"/>
+      <c r="K32" s="184"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1">
       <c r="A33" s="1"/>
@@ -16014,11 +16021,11 @@
       <c r="H33" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I33" s="181" t="s">
+      <c r="I33" s="185" t="s">
         <v>129</v>
       </c>
-      <c r="J33" s="146"/>
-      <c r="K33" s="178"/>
+      <c r="J33" s="154"/>
+      <c r="K33" s="184"/>
     </row>
     <row r="34" spans="1:11" ht="21.75" customHeight="1">
       <c r="A34" s="1"/>
@@ -16038,9 +16045,9 @@
         <v>0</v>
       </c>
       <c r="H34" s="83"/>
-      <c r="I34" s="181"/>
-      <c r="J34" s="146"/>
-      <c r="K34" s="178"/>
+      <c r="I34" s="185"/>
+      <c r="J34" s="154"/>
+      <c r="K34" s="184"/>
     </row>
     <row r="35" spans="1:11" ht="21.75" customHeight="1">
       <c r="A35" s="1"/>
@@ -16060,9 +16067,9 @@
         <v>0</v>
       </c>
       <c r="H35" s="83"/>
-      <c r="I35" s="181"/>
-      <c r="J35" s="146"/>
-      <c r="K35" s="178"/>
+      <c r="I35" s="185"/>
+      <c r="J35" s="154"/>
+      <c r="K35" s="184"/>
     </row>
     <row r="36" spans="1:11" ht="21.75" customHeight="1">
       <c r="A36" s="1"/>
@@ -16084,11 +16091,11 @@
       <c r="H36" s="93" t="s">
         <v>115</v>
       </c>
-      <c r="I36" s="181" t="s">
+      <c r="I36" s="185" t="s">
         <v>130</v>
       </c>
-      <c r="J36" s="146"/>
-      <c r="K36" s="178"/>
+      <c r="J36" s="154"/>
+      <c r="K36" s="184"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1">
       <c r="A37" s="1"/>
@@ -16114,11 +16121,11 @@
       <c r="H37" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I37" s="181" t="s">
+      <c r="I37" s="185" t="s">
         <v>131</v>
       </c>
-      <c r="J37" s="146"/>
-      <c r="K37" s="178"/>
+      <c r="J37" s="154"/>
+      <c r="K37" s="184"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1">
       <c r="A38" s="1"/>
@@ -16144,21 +16151,21 @@
       <c r="H38" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I38" s="181" t="s">
+      <c r="I38" s="185" t="s">
         <v>132</v>
       </c>
-      <c r="J38" s="146"/>
-      <c r="K38" s="178"/>
+      <c r="J38" s="154"/>
+      <c r="K38" s="184"/>
     </row>
     <row r="39" spans="1:11" ht="18" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="199" t="s">
+      <c r="B39" s="192" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="126"/>
-      <c r="D39" s="126"/>
-      <c r="E39" s="126"/>
-      <c r="F39" s="159"/>
+      <c r="C39" s="132"/>
+      <c r="D39" s="132"/>
+      <c r="E39" s="132"/>
+      <c r="F39" s="167"/>
       <c r="G39" s="91">
         <f>SUM(G9:G38)</f>
         <v>152</v>
@@ -16178,12 +16185,12 @@
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
       <c r="G40" s="23"/>
-      <c r="H40" s="196" t="s">
+      <c r="H40" s="193" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="133"/>
-      <c r="J40" s="133"/>
-      <c r="K40" s="134"/>
+      <c r="I40" s="134"/>
+      <c r="J40" s="134"/>
+      <c r="K40" s="135"/>
     </row>
     <row r="41" spans="1:11" ht="20.25" customHeight="1">
       <c r="A41" s="1"/>
@@ -16197,12 +16204,12 @@
       <c r="G41" s="26">
         <v>21</v>
       </c>
-      <c r="H41" s="197" t="s">
+      <c r="H41" s="194" t="s">
         <v>17</v>
       </c>
-      <c r="I41" s="128"/>
-      <c r="J41" s="128"/>
-      <c r="K41" s="123"/>
+      <c r="I41" s="125"/>
+      <c r="J41" s="125"/>
+      <c r="K41" s="124"/>
     </row>
     <row r="42" spans="1:11" ht="20.25" customHeight="1">
       <c r="A42" s="1"/>
@@ -16216,10 +16223,10 @@
       <c r="G42" s="27">
         <v>9</v>
       </c>
-      <c r="H42" s="128"/>
-      <c r="I42" s="128"/>
-      <c r="J42" s="128"/>
-      <c r="K42" s="123"/>
+      <c r="H42" s="125"/>
+      <c r="I42" s="125"/>
+      <c r="J42" s="125"/>
+      <c r="K42" s="124"/>
     </row>
     <row r="43" spans="1:11" ht="20.25" customHeight="1">
       <c r="A43" s="1"/>
@@ -16233,10 +16240,10 @@
       <c r="G43" s="27">
         <v>1</v>
       </c>
-      <c r="H43" s="126"/>
-      <c r="I43" s="126"/>
-      <c r="J43" s="126"/>
-      <c r="K43" s="125"/>
+      <c r="H43" s="132"/>
+      <c r="I43" s="132"/>
+      <c r="J43" s="132"/>
+      <c r="K43" s="128"/>
     </row>
     <row r="44" spans="1:11" ht="20.25" customHeight="1">
       <c r="A44" s="1"/>
@@ -16269,7 +16276,7 @@
       <c r="G45" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H45" s="197" t="s">
+      <c r="H45" s="194" t="s">
         <v>23</v>
       </c>
       <c r="I45" s="1"/>
@@ -16288,7 +16295,7 @@
       <c r="G46" s="27">
         <v>19</v>
       </c>
-      <c r="H46" s="126"/>
+      <c r="H46" s="132"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="48"/>
@@ -16309,10 +16316,10 @@
       <c r="H47" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="I47" s="171" t="s">
+      <c r="I47" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="J47" s="172"/>
+      <c r="J47" s="140"/>
       <c r="K47" s="32" t="s">
         <v>28</v>
       </c>
@@ -16330,10 +16337,10 @@
       <c r="H48" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="I48" s="163" t="s">
+      <c r="I48" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="J48" s="123"/>
+      <c r="J48" s="124"/>
       <c r="K48" s="37" t="s">
         <v>29</v>
       </c>
@@ -16353,10 +16360,10 @@
       <c r="H49" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="I49" s="163" t="s">
+      <c r="I49" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="J49" s="123"/>
+      <c r="J49" s="124"/>
       <c r="K49" s="37" t="s">
         <v>31</v>
       </c>
@@ -16377,10 +16384,10 @@
       <c r="H50" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="I50" s="163" t="s">
+      <c r="I50" s="126" t="s">
         <v>33</v>
       </c>
-      <c r="J50" s="123"/>
+      <c r="J50" s="124"/>
       <c r="K50" s="37" t="s">
         <v>33</v>
       </c>
@@ -16401,10 +16408,10 @@
       <c r="H51" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="I51" s="164" t="s">
+      <c r="I51" s="127" t="s">
         <v>35</v>
       </c>
-      <c r="J51" s="125"/>
+      <c r="J51" s="128"/>
       <c r="K51" s="43" t="s">
         <v>35</v>
       </c>
@@ -16427,23 +16434,23 @@
       <c r="B53" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C53" s="161" t="s">
+      <c r="C53" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="D53" s="123"/>
-      <c r="E53" s="161" t="s">
+      <c r="D53" s="124"/>
+      <c r="E53" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="F53" s="128"/>
-      <c r="G53" s="123"/>
-      <c r="H53" s="198" t="s">
+      <c r="F53" s="125"/>
+      <c r="G53" s="124"/>
+      <c r="H53" s="195" t="s">
         <v>38</v>
       </c>
-      <c r="I53" s="123"/>
-      <c r="J53" s="161" t="s">
+      <c r="I53" s="124"/>
+      <c r="J53" s="122" t="s">
         <v>106</v>
       </c>
-      <c r="K53" s="123"/>
+      <c r="K53" s="124"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1">
       <c r="A54" s="1"/>
@@ -16500,42 +16507,42 @@
     <row r="58" spans="1:11" ht="15.75" customHeight="1">
       <c r="A58" s="51"/>
       <c r="B58" s="52"/>
-      <c r="C58" s="127" t="s">
+      <c r="C58" s="170" t="s">
         <v>143</v>
       </c>
-      <c r="D58" s="123"/>
-      <c r="E58" s="127" t="s">
+      <c r="D58" s="124"/>
+      <c r="E58" s="170" t="s">
         <v>108</v>
       </c>
-      <c r="F58" s="128"/>
-      <c r="G58" s="123"/>
-      <c r="H58" s="194" t="s">
+      <c r="F58" s="125"/>
+      <c r="G58" s="124"/>
+      <c r="H58" s="196" t="s">
         <v>109</v>
       </c>
-      <c r="I58" s="123"/>
-      <c r="J58" s="127" t="s">
+      <c r="I58" s="124"/>
+      <c r="J58" s="170" t="s">
         <v>110</v>
       </c>
-      <c r="K58" s="123"/>
+      <c r="K58" s="124"/>
     </row>
     <row r="59" spans="1:11" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="53"/>
-      <c r="C59" s="124"/>
-      <c r="D59" s="125"/>
-      <c r="E59" s="124" t="s">
+      <c r="C59" s="169"/>
+      <c r="D59" s="128"/>
+      <c r="E59" s="169" t="s">
         <v>111</v>
       </c>
-      <c r="F59" s="126"/>
-      <c r="G59" s="125"/>
-      <c r="H59" s="195" t="s">
+      <c r="F59" s="132"/>
+      <c r="G59" s="128"/>
+      <c r="H59" s="197" t="s">
         <v>112</v>
       </c>
-      <c r="I59" s="125"/>
-      <c r="J59" s="124" t="s">
+      <c r="I59" s="128"/>
+      <c r="J59" s="169" t="s">
         <v>113</v>
       </c>
-      <c r="K59" s="125"/>
+      <c r="K59" s="128"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
@@ -19880,11 +19887,54 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="E2:H3"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="J59:K59"/>
     <mergeCell ref="H40:K40"/>
     <mergeCell ref="H41:K43"/>
     <mergeCell ref="E53:G53"/>
@@ -19896,54 +19946,11 @@
     <mergeCell ref="I49:J49"/>
     <mergeCell ref="I50:J50"/>
     <mergeCell ref="I51:J51"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B2:D5"/>
-    <mergeCell ref="E2:H3"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="B39:F39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>

--- a/TimesheetBankJakarta_Anggit_Ari_Utomo_2.xlsx
+++ b/TimesheetBankJakarta_Anggit_Ari_Utomo_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\anggit\Documents\absen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\anggit\absen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1310801A-EC35-460E-8356-3882AD47CC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227D4318-1055-4A54-B329-CC5383FBCD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6043,11 +6043,15 @@
       <c r="D26" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E26" s="105"/>
-      <c r="F26" s="8"/>
+      <c r="E26" s="105">
+        <v>0.33124999999999999</v>
+      </c>
+      <c r="F26" s="8">
+        <v>0.72430555555555554</v>
+      </c>
       <c r="G26" s="11">
         <f t="shared" ref="G26:G30" si="2">ROUND(MOD(F26-E26-TIME(1,0,0),1)*24,1)</f>
-        <v>23</v>
+        <v>8.4</v>
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="14" t="s">
@@ -6070,11 +6074,15 @@
       <c r="D27" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E27" s="105"/>
-      <c r="F27" s="8"/>
+      <c r="E27" s="105">
+        <v>0.31111111111111112</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0.73541666666666672</v>
+      </c>
       <c r="G27" s="11">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="H27" s="14"/>
       <c r="I27" s="14" t="s">
@@ -6097,11 +6105,15 @@
       <c r="D28" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E28" s="105"/>
-      <c r="F28" s="8"/>
+      <c r="E28" s="105">
+        <v>0.3263888888888889</v>
+      </c>
+      <c r="F28" s="8">
+        <v>0.74652777777777779</v>
+      </c>
       <c r="G28" s="11">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>9.1</v>
       </c>
       <c r="H28" s="14"/>
       <c r="I28" s="14" t="s">
@@ -6124,11 +6136,15 @@
       <c r="D29" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E29" s="105"/>
-      <c r="F29" s="8"/>
+      <c r="E29" s="105">
+        <v>0.34513888888888888</v>
+      </c>
+      <c r="F29" s="8">
+        <v>0.7270833333333333</v>
+      </c>
       <c r="G29" s="11">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H29" s="14"/>
       <c r="I29" s="14" t="s">
@@ -6151,11 +6167,13 @@
       <c r="D30" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E30" s="105"/>
+      <c r="E30" s="105">
+        <v>0.3</v>
+      </c>
       <c r="F30" s="8"/>
       <c r="G30" s="11">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>15.8</v>
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="14" t="s">
@@ -6385,7 +6403,7 @@
       <c r="F43" s="138"/>
       <c r="G43" s="18">
         <f>SUM(G9:G39)</f>
-        <v>301.39999999999998</v>
+        <v>237.1</v>
       </c>
       <c r="H43" s="19"/>
       <c r="I43" s="19"/>
@@ -6421,7 +6439,7 @@
       <c r="E45" s="25"/>
       <c r="F45" s="25"/>
       <c r="G45" s="26">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H45" s="129" t="s">
         <v>17</v>
@@ -6536,7 +6554,7 @@
       <c r="F51" s="25"/>
       <c r="G51" s="29">
         <f>G50/G45</f>
-        <v>1</v>
+        <v>1.0476190476190477</v>
       </c>
       <c r="H51" s="30" t="s">
         <v>26</v>
@@ -6583,7 +6601,7 @@
       <c r="F53" s="25"/>
       <c r="G53" s="27">
         <f>8*G45</f>
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H53" s="35" t="s">
         <v>31</v>
@@ -6608,7 +6626,7 @@
       <c r="F54" s="2"/>
       <c r="G54" s="26">
         <f>G43</f>
-        <v>301.39999999999998</v>
+        <v>237.1</v>
       </c>
       <c r="H54" s="35" t="s">
         <v>33</v>
@@ -6633,7 +6651,7 @@
       <c r="F55" s="39"/>
       <c r="G55" s="40">
         <f>G54/G53</f>
-        <v>1.7124999999999999</v>
+        <v>1.4113095238095237</v>
       </c>
       <c r="H55" s="41" t="s">
         <v>35</v>
@@ -10325,24 +10343,16 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J37:L37"/>
     <mergeCell ref="J13:L13"/>
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="J15:L15"/>
     <mergeCell ref="J16:L16"/>
     <mergeCell ref="J26:L26"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="J23:L23"/>
     <mergeCell ref="J19:L19"/>
     <mergeCell ref="J20:L20"/>
     <mergeCell ref="J21:L21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="J23:L23"/>
     <mergeCell ref="C63:D63"/>
     <mergeCell ref="E63:G63"/>
     <mergeCell ref="H63:J63"/>
@@ -10351,6 +10361,14 @@
     <mergeCell ref="H62:J62"/>
     <mergeCell ref="K62:L62"/>
     <mergeCell ref="C62:D62"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="J30:L30"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="J7:L8"/>

--- a/TimesheetBankJakarta_Anggit_Ari_Utomo_2.xlsx
+++ b/TimesheetBankJakarta_Anggit_Ari_Utomo_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\anggit\absen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227D4318-1055-4A54-B329-CC5383FBCD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9DAB18-BDBF-4065-82C1-B51E508721D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2495,62 +2495,29 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2561,11 +2528,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2636,17 +2612,68 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2678,35 +2705,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2717,17 +2726,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5451,137 +5451,137 @@
     </row>
     <row r="2" spans="1:12" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="145"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="143" t="s">
+      <c r="B2" s="136"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="148"/>
-      <c r="J2" s="151" t="s">
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="134"/>
-      <c r="L2" s="135"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="134"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="147"/>
-      <c r="H3" s="147"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="147"/>
-      <c r="K3" s="147"/>
-      <c r="L3" s="152"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="139"/>
+      <c r="H3" s="139"/>
+      <c r="I3" s="142"/>
+      <c r="J3" s="139"/>
+      <c r="K3" s="139"/>
+      <c r="L3" s="144"/>
     </row>
     <row r="4" spans="1:12" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="153" t="s">
+      <c r="B4" s="137"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="145" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="154"/>
-      <c r="G4" s="154"/>
-      <c r="H4" s="154"/>
-      <c r="I4" s="155"/>
-      <c r="J4" s="156" t="s">
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="148" t="s">
         <v>152</v>
       </c>
-      <c r="K4" s="157"/>
-      <c r="L4" s="158"/>
+      <c r="K4" s="149"/>
+      <c r="L4" s="150"/>
     </row>
     <row r="5" spans="1:12" ht="14.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="146"/>
-      <c r="C5" s="147"/>
-      <c r="D5" s="147"/>
+      <c r="B5" s="138"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="139"/>
       <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="159" t="s">
+      <c r="F5" s="151" t="s">
         <v>146</v>
       </c>
-      <c r="G5" s="154"/>
-      <c r="H5" s="154"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="125"/>
-      <c r="L5" s="124"/>
+      <c r="G5" s="146"/>
+      <c r="H5" s="146"/>
+      <c r="I5" s="147"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="127"/>
     </row>
     <row r="6" spans="1:12" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="162" t="s">
+      <c r="B6" s="154" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="157"/>
-      <c r="D6" s="157"/>
+      <c r="C6" s="149"/>
+      <c r="D6" s="149"/>
       <c r="E6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="160">
+      <c r="F6" s="152">
         <v>0</v>
       </c>
-      <c r="G6" s="157"/>
-      <c r="H6" s="157"/>
-      <c r="I6" s="161"/>
-      <c r="J6" s="125"/>
-      <c r="K6" s="125"/>
-      <c r="L6" s="124"/>
+      <c r="G6" s="149"/>
+      <c r="H6" s="149"/>
+      <c r="I6" s="153"/>
+      <c r="J6" s="126"/>
+      <c r="K6" s="126"/>
+      <c r="L6" s="127"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="163" t="s">
+      <c r="B7" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="165" t="s">
+      <c r="C7" s="157" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="166"/>
-      <c r="E7" s="143" t="s">
+      <c r="D7" s="158"/>
+      <c r="E7" s="132" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="148"/>
-      <c r="G7" s="168" t="s">
+      <c r="F7" s="140"/>
+      <c r="G7" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="141" t="s">
+      <c r="H7" s="130" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="141" t="s">
+      <c r="I7" s="130" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="143" t="s">
+      <c r="J7" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="134"/>
-      <c r="L7" s="135"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="134"/>
     </row>
     <row r="8" spans="1:12" thickBot="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="164"/>
+      <c r="B8" s="156"/>
       <c r="C8" s="8">
         <v>0.33333333333333331</v>
       </c>
       <c r="D8" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="144"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="142"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="142"/>
-      <c r="J8" s="144"/>
-      <c r="K8" s="132"/>
-      <c r="L8" s="128"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="159"/>
+      <c r="G8" s="131"/>
+      <c r="H8" s="131"/>
+      <c r="I8" s="131"/>
+      <c r="J8" s="135"/>
+      <c r="K8" s="124"/>
+      <c r="L8" s="123"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1">
       <c r="A9" s="9"/>
@@ -6170,10 +6170,12 @@
       <c r="E30" s="105">
         <v>0.3</v>
       </c>
-      <c r="F30" s="8"/>
+      <c r="F30" s="8">
+        <v>0.75277777777777777</v>
+      </c>
       <c r="G30" s="11">
         <f t="shared" si="2"/>
-        <v>15.8</v>
+        <v>9.9</v>
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="14" t="s">
@@ -6250,11 +6252,15 @@
       <c r="D34" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E34" s="105"/>
-      <c r="F34" s="8"/>
+      <c r="E34" s="105">
+        <v>0.32361111111111113</v>
+      </c>
+      <c r="F34" s="8">
+        <v>0.70902777777777781</v>
+      </c>
       <c r="G34" s="11">
         <f t="shared" ref="G34:G37" si="3">ROUND(MOD(F34-E34-TIME(1,0,0),1)*24,1)</f>
-        <v>23</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="H34" s="14"/>
       <c r="I34" s="14" t="s">
@@ -6277,11 +6283,13 @@
       <c r="D35" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E35" s="105"/>
+      <c r="E35" s="105">
+        <v>0.27500000000000002</v>
+      </c>
       <c r="F35" s="8"/>
       <c r="G35" s="11">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14" t="s">
@@ -6394,16 +6402,16 @@
     </row>
     <row r="43" spans="1:12" ht="18" customHeight="1" thickBot="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="136" t="s">
+      <c r="B43" s="168" t="s">
         <v>13</v>
       </c>
-      <c r="C43" s="137"/>
-      <c r="D43" s="137"/>
-      <c r="E43" s="137"/>
-      <c r="F43" s="138"/>
+      <c r="C43" s="169"/>
+      <c r="D43" s="169"/>
+      <c r="E43" s="169"/>
+      <c r="F43" s="170"/>
       <c r="G43" s="18">
         <f>SUM(G9:G39)</f>
-        <v>237.1</v>
+        <v>209.9</v>
       </c>
       <c r="H43" s="19"/>
       <c r="I43" s="19"/>
@@ -6421,13 +6429,13 @@
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
       <c r="G44" s="23"/>
-      <c r="H44" s="133" t="s">
+      <c r="H44" s="167" t="s">
         <v>15</v>
       </c>
-      <c r="I44" s="134"/>
-      <c r="J44" s="134"/>
-      <c r="K44" s="134"/>
-      <c r="L44" s="135"/>
+      <c r="I44" s="133"/>
+      <c r="J44" s="133"/>
+      <c r="K44" s="133"/>
+      <c r="L44" s="134"/>
     </row>
     <row r="45" spans="1:12" ht="20.25" customHeight="1">
       <c r="A45" s="1"/>
@@ -6441,13 +6449,13 @@
       <c r="G45" s="26">
         <v>21</v>
       </c>
-      <c r="H45" s="129" t="s">
+      <c r="H45" s="165" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="125"/>
-      <c r="J45" s="125"/>
-      <c r="K45" s="125"/>
-      <c r="L45" s="124"/>
+      <c r="I45" s="126"/>
+      <c r="J45" s="126"/>
+      <c r="K45" s="126"/>
+      <c r="L45" s="127"/>
     </row>
     <row r="46" spans="1:12" ht="20.25" customHeight="1">
       <c r="A46" s="1"/>
@@ -6461,11 +6469,11 @@
       <c r="G46" s="27">
         <v>0</v>
       </c>
-      <c r="H46" s="130"/>
-      <c r="I46" s="125"/>
-      <c r="J46" s="125"/>
-      <c r="K46" s="125"/>
-      <c r="L46" s="124"/>
+      <c r="H46" s="137"/>
+      <c r="I46" s="126"/>
+      <c r="J46" s="126"/>
+      <c r="K46" s="126"/>
+      <c r="L46" s="127"/>
     </row>
     <row r="47" spans="1:12" ht="20.25" customHeight="1" thickBot="1">
       <c r="A47" s="1"/>
@@ -6479,11 +6487,11 @@
       <c r="G47" s="27">
         <v>0</v>
       </c>
-      <c r="H47" s="131"/>
-      <c r="I47" s="132"/>
-      <c r="J47" s="132"/>
-      <c r="K47" s="132"/>
-      <c r="L47" s="128"/>
+      <c r="H47" s="166"/>
+      <c r="I47" s="124"/>
+      <c r="J47" s="124"/>
+      <c r="K47" s="124"/>
+      <c r="L47" s="123"/>
     </row>
     <row r="48" spans="1:12" ht="20.25" customHeight="1">
       <c r="A48" s="1"/>
@@ -6497,13 +6505,13 @@
       <c r="G48" s="27">
         <v>0</v>
       </c>
-      <c r="H48" s="133" t="s">
+      <c r="H48" s="167" t="s">
         <v>21</v>
       </c>
-      <c r="I48" s="134"/>
-      <c r="J48" s="134"/>
-      <c r="K48" s="134"/>
-      <c r="L48" s="135"/>
+      <c r="I48" s="133"/>
+      <c r="J48" s="133"/>
+      <c r="K48" s="133"/>
+      <c r="L48" s="134"/>
     </row>
     <row r="49" spans="1:12" ht="20.25" customHeight="1">
       <c r="A49" s="1"/>
@@ -6517,13 +6525,13 @@
       <c r="G49" s="27">
         <v>0</v>
       </c>
-      <c r="H49" s="122" t="s">
+      <c r="H49" s="161" t="s">
         <v>23</v>
       </c>
-      <c r="I49" s="125"/>
-      <c r="J49" s="125"/>
-      <c r="K49" s="125"/>
-      <c r="L49" s="124"/>
+      <c r="I49" s="126"/>
+      <c r="J49" s="126"/>
+      <c r="K49" s="126"/>
+      <c r="L49" s="127"/>
     </row>
     <row r="50" spans="1:12" ht="20.25" customHeight="1" thickBot="1">
       <c r="A50" s="1"/>
@@ -6537,11 +6545,11 @@
       <c r="G50" s="27">
         <v>22</v>
       </c>
-      <c r="H50" s="131"/>
-      <c r="I50" s="132"/>
-      <c r="J50" s="132"/>
-      <c r="K50" s="132"/>
-      <c r="L50" s="128"/>
+      <c r="H50" s="166"/>
+      <c r="I50" s="124"/>
+      <c r="J50" s="124"/>
+      <c r="K50" s="124"/>
+      <c r="L50" s="123"/>
     </row>
     <row r="51" spans="1:12" ht="24" customHeight="1" thickBot="1">
       <c r="A51" s="1"/>
@@ -6560,10 +6568,10 @@
         <v>26</v>
       </c>
       <c r="I51" s="31"/>
-      <c r="J51" s="139" t="s">
+      <c r="J51" s="171" t="s">
         <v>27</v>
       </c>
-      <c r="K51" s="140"/>
+      <c r="K51" s="172"/>
       <c r="L51" s="32" t="s">
         <v>28</v>
       </c>
@@ -6582,10 +6590,10 @@
         <v>29</v>
       </c>
       <c r="I52" s="36"/>
-      <c r="J52" s="126" t="s">
+      <c r="J52" s="163" t="s">
         <v>29</v>
       </c>
-      <c r="K52" s="124"/>
+      <c r="K52" s="127"/>
       <c r="L52" s="37" t="s">
         <v>29</v>
       </c>
@@ -6607,10 +6615,10 @@
         <v>31</v>
       </c>
       <c r="I53" s="36"/>
-      <c r="J53" s="126" t="s">
+      <c r="J53" s="163" t="s">
         <v>31</v>
       </c>
-      <c r="K53" s="124"/>
+      <c r="K53" s="127"/>
       <c r="L53" s="37" t="s">
         <v>31</v>
       </c>
@@ -6626,16 +6634,16 @@
       <c r="F54" s="2"/>
       <c r="G54" s="26">
         <f>G43</f>
-        <v>237.1</v>
+        <v>209.9</v>
       </c>
       <c r="H54" s="35" t="s">
         <v>33</v>
       </c>
       <c r="I54" s="36"/>
-      <c r="J54" s="126" t="s">
+      <c r="J54" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="K54" s="124"/>
+      <c r="K54" s="127"/>
       <c r="L54" s="37" t="s">
         <v>33</v>
       </c>
@@ -6651,16 +6659,16 @@
       <c r="F55" s="39"/>
       <c r="G55" s="40">
         <f>G54/G53</f>
-        <v>1.4113095238095237</v>
+        <v>1.2494047619047619</v>
       </c>
       <c r="H55" s="41" t="s">
         <v>35</v>
       </c>
       <c r="I55" s="42"/>
-      <c r="J55" s="127" t="s">
+      <c r="J55" s="164" t="s">
         <v>35</v>
       </c>
-      <c r="K55" s="128"/>
+      <c r="K55" s="123"/>
       <c r="L55" s="43" t="s">
         <v>35</v>
       </c>
@@ -6682,32 +6690,32 @@
     <row r="57" spans="1:12" ht="15.75" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="28"/>
-      <c r="C57" s="122" t="s">
+      <c r="C57" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="D57" s="124"/>
-      <c r="E57" s="122" t="s">
+      <c r="D57" s="127"/>
+      <c r="E57" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="F57" s="125"/>
-      <c r="G57" s="124"/>
-      <c r="H57" s="122" t="s">
+      <c r="F57" s="126"/>
+      <c r="G57" s="127"/>
+      <c r="H57" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="I57" s="125"/>
-      <c r="J57" s="124"/>
-      <c r="K57" s="122" t="s">
+      <c r="I57" s="126"/>
+      <c r="J57" s="127"/>
+      <c r="K57" s="161" t="s">
         <v>39</v>
       </c>
-      <c r="L57" s="124"/>
+      <c r="L57" s="127"/>
     </row>
     <row r="58" spans="1:12" ht="15.75" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="122"/>
-      <c r="D58" s="123"/>
+      <c r="C58" s="161"/>
+      <c r="D58" s="162"/>
       <c r="E58" s="47"/>
       <c r="F58" s="1"/>
       <c r="G58" s="48"/>
@@ -6722,8 +6730,8 @@
       <c r="B59" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="C59" s="122"/>
-      <c r="D59" s="123"/>
+      <c r="C59" s="161"/>
+      <c r="D59" s="162"/>
       <c r="E59" s="47"/>
       <c r="F59" s="1"/>
       <c r="G59" s="48"/>
@@ -6738,8 +6746,8 @@
       <c r="B60" s="50">
         <v>46257</v>
       </c>
-      <c r="C60" s="122"/>
-      <c r="D60" s="123"/>
+      <c r="C60" s="161"/>
+      <c r="D60" s="162"/>
       <c r="E60" s="47"/>
       <c r="F60" s="1"/>
       <c r="G60" s="48"/>
@@ -6752,8 +6760,8 @@
     <row r="61" spans="1:12" ht="15.75" customHeight="1">
       <c r="A61" s="51"/>
       <c r="B61" s="47"/>
-      <c r="C61" s="122"/>
-      <c r="D61" s="123"/>
+      <c r="C61" s="161"/>
+      <c r="D61" s="162"/>
       <c r="E61" s="47"/>
       <c r="F61" s="1"/>
       <c r="G61" s="48"/>
@@ -6766,44 +6774,44 @@
     <row r="62" spans="1:12" ht="15.75" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="52"/>
-      <c r="C62" s="172" t="s">
+      <c r="C62" s="129" t="s">
         <v>151</v>
       </c>
-      <c r="D62" s="124"/>
-      <c r="E62" s="170" t="s">
+      <c r="D62" s="127"/>
+      <c r="E62" s="125" t="s">
         <v>41</v>
       </c>
-      <c r="F62" s="125"/>
-      <c r="G62" s="124"/>
-      <c r="H62" s="171" t="s">
+      <c r="F62" s="126"/>
+      <c r="G62" s="127"/>
+      <c r="H62" s="128" t="s">
         <v>145</v>
       </c>
-      <c r="I62" s="125"/>
-      <c r="J62" s="124"/>
-      <c r="K62" s="170" t="s">
+      <c r="I62" s="126"/>
+      <c r="J62" s="127"/>
+      <c r="K62" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="L62" s="124"/>
+      <c r="L62" s="127"/>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A63" s="1"/>
       <c r="B63" s="53"/>
-      <c r="C63" s="169"/>
-      <c r="D63" s="128"/>
-      <c r="E63" s="169" t="s">
+      <c r="C63" s="122"/>
+      <c r="D63" s="123"/>
+      <c r="E63" s="122" t="s">
         <v>43</v>
       </c>
-      <c r="F63" s="132"/>
-      <c r="G63" s="128"/>
-      <c r="H63" s="169" t="s">
+      <c r="F63" s="124"/>
+      <c r="G63" s="123"/>
+      <c r="H63" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="I63" s="132"/>
-      <c r="J63" s="128"/>
-      <c r="K63" s="169" t="s">
+      <c r="I63" s="124"/>
+      <c r="J63" s="123"/>
+      <c r="K63" s="122" t="s">
         <v>45</v>
       </c>
-      <c r="L63" s="128"/>
+      <c r="L63" s="123"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1">
       <c r="A64" s="1"/>
@@ -10343,32 +10351,22 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="H63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="C58:D61"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="H57:J57"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="H45:L47"/>
+    <mergeCell ref="H48:L48"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="H49:L50"/>
+    <mergeCell ref="H44:L44"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="J7:L8"/>
@@ -10385,22 +10383,32 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F8"/>
     <mergeCell ref="G7:G8"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="C58:D61"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="H57:J57"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="H45:L47"/>
-    <mergeCell ref="H48:L48"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="H49:L50"/>
-    <mergeCell ref="H44:L44"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="H63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="J21:L21"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.19685039370078741" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="81" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -10443,128 +10451,128 @@
     </row>
     <row r="2" spans="1:11" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="145"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="148"/>
-      <c r="E2" s="143" t="s">
+      <c r="B2" s="136"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="143" t="s">
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="134"/>
-      <c r="K2" s="135"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="134"/>
     </row>
     <row r="3" spans="1:11" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="147"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="149"/>
-      <c r="J3" s="147"/>
-      <c r="K3" s="152"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="139"/>
+      <c r="H3" s="142"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="139"/>
+      <c r="K3" s="144"/>
     </row>
     <row r="4" spans="1:11" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="153" t="s">
+      <c r="B4" s="137"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="182"/>
+      <c r="E4" s="145" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="154"/>
-      <c r="G4" s="154"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="174" t="s">
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="183" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="157"/>
-      <c r="K4" s="158"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="150"/>
     </row>
     <row r="5" spans="1:11" ht="14.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="146"/>
-      <c r="C5" s="147"/>
-      <c r="D5" s="150"/>
+      <c r="B5" s="138"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="142"/>
       <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="159" t="s">
+      <c r="F5" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="154"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="124"/>
+      <c r="G5" s="146"/>
+      <c r="H5" s="147"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="127"/>
     </row>
     <row r="6" spans="1:11" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="179" t="s">
+      <c r="B6" s="188" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="177"/>
-      <c r="D6" s="178"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="187"/>
       <c r="E6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="176">
+      <c r="F6" s="185">
         <v>20230682322</v>
       </c>
-      <c r="G6" s="177"/>
-      <c r="H6" s="178"/>
-      <c r="I6" s="144"/>
-      <c r="J6" s="132"/>
-      <c r="K6" s="128"/>
+      <c r="G6" s="186"/>
+      <c r="H6" s="187"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="124"/>
+      <c r="K6" s="123"/>
     </row>
     <row r="7" spans="1:11" ht="14.4">
       <c r="A7" s="1"/>
-      <c r="B7" s="163" t="s">
+      <c r="B7" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="165" t="s">
+      <c r="C7" s="157" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="166"/>
-      <c r="E7" s="145" t="s">
+      <c r="D7" s="158"/>
+      <c r="E7" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="135"/>
-      <c r="G7" s="180" t="s">
+      <c r="F7" s="134"/>
+      <c r="G7" s="189" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="181" t="s">
+      <c r="H7" s="190" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="151" t="s">
+      <c r="I7" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="134"/>
-      <c r="K7" s="135"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="134"/>
     </row>
     <row r="8" spans="1:11" ht="14.4">
       <c r="A8" s="1"/>
-      <c r="B8" s="164"/>
+      <c r="B8" s="156"/>
       <c r="C8" s="8">
         <v>0.33333333333333331</v>
       </c>
       <c r="D8" s="55">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="131"/>
-      <c r="F8" s="128"/>
-      <c r="G8" s="132"/>
-      <c r="H8" s="182"/>
-      <c r="I8" s="132"/>
-      <c r="J8" s="132"/>
-      <c r="K8" s="128"/>
+      <c r="E8" s="166"/>
+      <c r="F8" s="123"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="191"/>
+      <c r="I8" s="124"/>
+      <c r="J8" s="124"/>
+      <c r="K8" s="123"/>
     </row>
     <row r="9" spans="1:11" ht="14.4">
       <c r="A9" s="2"/>
@@ -10589,11 +10597,11 @@
       <c r="H9" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="183" t="s">
+      <c r="I9" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="154"/>
-      <c r="K9" s="184"/>
+      <c r="J9" s="146"/>
+      <c r="K9" s="178"/>
     </row>
     <row r="10" spans="1:11" ht="14.4">
       <c r="A10" s="9"/>
@@ -10618,11 +10626,11 @@
       <c r="H10" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="183" t="s">
+      <c r="I10" s="177" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="154"/>
-      <c r="K10" s="184"/>
+      <c r="J10" s="146"/>
+      <c r="K10" s="178"/>
     </row>
     <row r="11" spans="1:11" ht="14.4">
       <c r="A11" s="2"/>
@@ -10647,11 +10655,11 @@
       <c r="H11" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I11" s="183" t="s">
+      <c r="I11" s="177" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="154"/>
-      <c r="K11" s="184"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="178"/>
     </row>
     <row r="12" spans="1:11" ht="14.4">
       <c r="A12" s="2"/>
@@ -10670,9 +10678,9 @@
         <v>0</v>
       </c>
       <c r="H12" s="13"/>
-      <c r="I12" s="183"/>
-      <c r="J12" s="154"/>
-      <c r="K12" s="184"/>
+      <c r="I12" s="177"/>
+      <c r="J12" s="146"/>
+      <c r="K12" s="178"/>
     </row>
     <row r="13" spans="1:11" ht="14.4">
       <c r="A13" s="2"/>
@@ -10691,9 +10699,9 @@
         <v>0</v>
       </c>
       <c r="H13" s="13"/>
-      <c r="I13" s="183"/>
-      <c r="J13" s="154"/>
-      <c r="K13" s="184"/>
+      <c r="I13" s="177"/>
+      <c r="J13" s="146"/>
+      <c r="K13" s="178"/>
     </row>
     <row r="14" spans="1:11" ht="14.4">
       <c r="A14" s="2"/>
@@ -10718,11 +10726,11 @@
       <c r="H14" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I14" s="183" t="s">
+      <c r="I14" s="177" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="154"/>
-      <c r="K14" s="184"/>
+      <c r="J14" s="146"/>
+      <c r="K14" s="178"/>
     </row>
     <row r="15" spans="1:11" ht="14.4">
       <c r="A15" s="2"/>
@@ -10747,11 +10755,11 @@
       <c r="H15" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="183" t="s">
+      <c r="I15" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="154"/>
-      <c r="K15" s="184"/>
+      <c r="J15" s="146"/>
+      <c r="K15" s="178"/>
     </row>
     <row r="16" spans="1:11" ht="14.4">
       <c r="A16" s="2"/>
@@ -10770,9 +10778,9 @@
         <v>0</v>
       </c>
       <c r="H16" s="11"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="154"/>
-      <c r="K16" s="184"/>
+      <c r="I16" s="181"/>
+      <c r="J16" s="146"/>
+      <c r="K16" s="178"/>
     </row>
     <row r="17" spans="1:11" ht="14.4">
       <c r="A17" s="2"/>
@@ -10797,11 +10805,11 @@
       <c r="H17" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="183" t="s">
+      <c r="I17" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="J17" s="154"/>
-      <c r="K17" s="184"/>
+      <c r="J17" s="146"/>
+      <c r="K17" s="178"/>
     </row>
     <row r="18" spans="1:11" ht="14.4">
       <c r="A18" s="2"/>
@@ -10826,11 +10834,11 @@
       <c r="H18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="183" t="s">
+      <c r="I18" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="J18" s="154"/>
-      <c r="K18" s="184"/>
+      <c r="J18" s="146"/>
+      <c r="K18" s="178"/>
     </row>
     <row r="19" spans="1:11" ht="14.4">
       <c r="A19" s="2"/>
@@ -10849,9 +10857,9 @@
         <v>0</v>
       </c>
       <c r="H19" s="11"/>
-      <c r="I19" s="185"/>
-      <c r="J19" s="154"/>
-      <c r="K19" s="184"/>
+      <c r="I19" s="181"/>
+      <c r="J19" s="146"/>
+      <c r="K19" s="178"/>
     </row>
     <row r="20" spans="1:11" ht="14.4">
       <c r="A20" s="2"/>
@@ -10870,9 +10878,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="11"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="154"/>
-      <c r="K20" s="184"/>
+      <c r="I20" s="181"/>
+      <c r="J20" s="146"/>
+      <c r="K20" s="178"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1">
       <c r="A21" s="2"/>
@@ -10897,11 +10905,11 @@
       <c r="H21" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I21" s="183" t="s">
+      <c r="I21" s="177" t="s">
         <v>68</v>
       </c>
-      <c r="J21" s="154"/>
-      <c r="K21" s="184"/>
+      <c r="J21" s="146"/>
+      <c r="K21" s="178"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
       <c r="A22" s="2"/>
@@ -10926,11 +10934,11 @@
       <c r="H22" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="183" t="s">
+      <c r="I22" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="154"/>
-      <c r="K22" s="184"/>
+      <c r="J22" s="146"/>
+      <c r="K22" s="178"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
       <c r="A23" s="2"/>
@@ -10955,11 +10963,11 @@
       <c r="H23" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="183" t="s">
+      <c r="I23" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="154"/>
-      <c r="K23" s="184"/>
+      <c r="J23" s="146"/>
+      <c r="K23" s="178"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="2"/>
@@ -10984,11 +10992,11 @@
       <c r="H24" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="183" t="s">
+      <c r="I24" s="177" t="s">
         <v>72</v>
       </c>
-      <c r="J24" s="154"/>
-      <c r="K24" s="184"/>
+      <c r="J24" s="146"/>
+      <c r="K24" s="178"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1">
       <c r="A25" s="2"/>
@@ -11013,11 +11021,11 @@
       <c r="H25" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="183" t="s">
+      <c r="I25" s="177" t="s">
         <v>74</v>
       </c>
-      <c r="J25" s="154"/>
-      <c r="K25" s="184"/>
+      <c r="J25" s="146"/>
+      <c r="K25" s="178"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1">
       <c r="A26" s="2"/>
@@ -11036,9 +11044,9 @@
         <v>0</v>
       </c>
       <c r="H26" s="11"/>
-      <c r="I26" s="185"/>
-      <c r="J26" s="154"/>
-      <c r="K26" s="184"/>
+      <c r="I26" s="181"/>
+      <c r="J26" s="146"/>
+      <c r="K26" s="178"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
       <c r="A27" s="2"/>
@@ -11057,9 +11065,9 @@
         <v>0</v>
       </c>
       <c r="H27" s="11"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="154"/>
-      <c r="K27" s="184"/>
+      <c r="I27" s="181"/>
+      <c r="J27" s="146"/>
+      <c r="K27" s="178"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1">
       <c r="A28" s="2"/>
@@ -11084,11 +11092,11 @@
       <c r="H28" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I28" s="183" t="s">
+      <c r="I28" s="177" t="s">
         <v>78</v>
       </c>
-      <c r="J28" s="154"/>
-      <c r="K28" s="184"/>
+      <c r="J28" s="146"/>
+      <c r="K28" s="178"/>
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1">
       <c r="A29" s="2"/>
@@ -11113,11 +11121,11 @@
       <c r="H29" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="183" t="s">
+      <c r="I29" s="177" t="s">
         <v>80</v>
       </c>
-      <c r="J29" s="154"/>
-      <c r="K29" s="184"/>
+      <c r="J29" s="146"/>
+      <c r="K29" s="178"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="2"/>
@@ -11142,11 +11150,11 @@
       <c r="H30" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I30" s="183" t="s">
+      <c r="I30" s="177" t="s">
         <v>82</v>
       </c>
-      <c r="J30" s="154"/>
-      <c r="K30" s="184"/>
+      <c r="J30" s="146"/>
+      <c r="K30" s="178"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1">
       <c r="A31" s="2"/>
@@ -11171,11 +11179,11 @@
       <c r="H31" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I31" s="183" t="s">
+      <c r="I31" s="177" t="s">
         <v>84</v>
       </c>
-      <c r="J31" s="154"/>
-      <c r="K31" s="184"/>
+      <c r="J31" s="146"/>
+      <c r="K31" s="178"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="2"/>
@@ -11200,11 +11208,11 @@
       <c r="H32" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I32" s="183" t="s">
+      <c r="I32" s="177" t="s">
         <v>86</v>
       </c>
-      <c r="J32" s="154"/>
-      <c r="K32" s="184"/>
+      <c r="J32" s="146"/>
+      <c r="K32" s="178"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1">
       <c r="A33" s="2"/>
@@ -11223,9 +11231,9 @@
         <v>0</v>
       </c>
       <c r="H33" s="11"/>
-      <c r="I33" s="185"/>
-      <c r="J33" s="154"/>
-      <c r="K33" s="184"/>
+      <c r="I33" s="181"/>
+      <c r="J33" s="146"/>
+      <c r="K33" s="178"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1">
       <c r="A34" s="2"/>
@@ -11244,9 +11252,9 @@
         <v>0</v>
       </c>
       <c r="H34" s="11"/>
-      <c r="I34" s="185"/>
-      <c r="J34" s="154"/>
-      <c r="K34" s="184"/>
+      <c r="I34" s="181"/>
+      <c r="J34" s="146"/>
+      <c r="K34" s="178"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1">
       <c r="A35" s="2"/>
@@ -11271,11 +11279,11 @@
       <c r="H35" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I35" s="183" t="s">
+      <c r="I35" s="177" t="s">
         <v>90</v>
       </c>
-      <c r="J35" s="154"/>
-      <c r="K35" s="184"/>
+      <c r="J35" s="146"/>
+      <c r="K35" s="178"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1">
       <c r="A36" s="2"/>
@@ -11300,11 +11308,11 @@
       <c r="H36" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I36" s="183" t="s">
+      <c r="I36" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="J36" s="154"/>
-      <c r="K36" s="184"/>
+      <c r="J36" s="146"/>
+      <c r="K36" s="178"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1">
       <c r="A37" s="2"/>
@@ -11329,11 +11337,11 @@
       <c r="H37" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I37" s="183" t="s">
+      <c r="I37" s="177" t="s">
         <v>68</v>
       </c>
-      <c r="J37" s="154"/>
-      <c r="K37" s="184"/>
+      <c r="J37" s="146"/>
+      <c r="K37" s="178"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1">
       <c r="A38" s="2"/>
@@ -11358,11 +11366,11 @@
       <c r="H38" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I38" s="183" t="s">
+      <c r="I38" s="177" t="s">
         <v>94</v>
       </c>
-      <c r="J38" s="154"/>
-      <c r="K38" s="184"/>
+      <c r="J38" s="146"/>
+      <c r="K38" s="178"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1">
       <c r="A39" s="2"/>
@@ -11387,21 +11395,21 @@
       <c r="H39" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I39" s="187" t="s">
+      <c r="I39" s="180" t="s">
         <v>94</v>
       </c>
-      <c r="J39" s="157"/>
-      <c r="K39" s="158"/>
+      <c r="J39" s="149"/>
+      <c r="K39" s="150"/>
     </row>
     <row r="40" spans="1:11" ht="18" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="136" t="s">
+      <c r="B40" s="168" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="188"/>
-      <c r="D40" s="188"/>
-      <c r="E40" s="188"/>
-      <c r="F40" s="189"/>
+      <c r="C40" s="173"/>
+      <c r="D40" s="173"/>
+      <c r="E40" s="173"/>
+      <c r="F40" s="174"/>
       <c r="G40" s="18">
         <f>SUM(G9:G39)</f>
         <v>176</v>
@@ -11421,12 +11429,12 @@
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
       <c r="G41" s="23"/>
-      <c r="H41" s="190" t="s">
+      <c r="H41" s="175" t="s">
         <v>15</v>
       </c>
-      <c r="I41" s="134"/>
-      <c r="J41" s="134"/>
-      <c r="K41" s="135"/>
+      <c r="I41" s="133"/>
+      <c r="J41" s="133"/>
+      <c r="K41" s="134"/>
     </row>
     <row r="42" spans="1:11" ht="20.25" customHeight="1">
       <c r="A42" s="1"/>
@@ -11440,12 +11448,12 @@
       <c r="G42" s="26">
         <v>22</v>
       </c>
-      <c r="H42" s="191" t="s">
+      <c r="H42" s="176" t="s">
         <v>17</v>
       </c>
-      <c r="I42" s="125"/>
-      <c r="J42" s="125"/>
-      <c r="K42" s="124"/>
+      <c r="I42" s="126"/>
+      <c r="J42" s="126"/>
+      <c r="K42" s="127"/>
     </row>
     <row r="43" spans="1:11" ht="20.25" customHeight="1">
       <c r="A43" s="1"/>
@@ -11459,10 +11467,10 @@
       <c r="G43" s="27">
         <v>9</v>
       </c>
-      <c r="H43" s="125"/>
-      <c r="I43" s="125"/>
-      <c r="J43" s="125"/>
-      <c r="K43" s="124"/>
+      <c r="H43" s="126"/>
+      <c r="I43" s="126"/>
+      <c r="J43" s="126"/>
+      <c r="K43" s="127"/>
     </row>
     <row r="44" spans="1:11" ht="20.25" customHeight="1">
       <c r="A44" s="1"/>
@@ -11476,10 +11484,10 @@
       <c r="G44" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H44" s="132"/>
-      <c r="I44" s="132"/>
-      <c r="J44" s="132"/>
-      <c r="K44" s="128"/>
+      <c r="H44" s="124"/>
+      <c r="I44" s="124"/>
+      <c r="J44" s="124"/>
+      <c r="K44" s="123"/>
     </row>
     <row r="45" spans="1:11" ht="20.25" customHeight="1">
       <c r="A45" s="1"/>
@@ -11512,7 +11520,7 @@
       <c r="G46" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H46" s="186" t="s">
+      <c r="H46" s="179" t="s">
         <v>23</v>
       </c>
       <c r="I46" s="1"/>
@@ -11531,7 +11539,7 @@
       <c r="G47" s="27">
         <v>22</v>
       </c>
-      <c r="H47" s="132"/>
+      <c r="H47" s="124"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="48"/>
@@ -11552,10 +11560,10 @@
       <c r="H48" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="I48" s="139" t="s">
+      <c r="I48" s="171" t="s">
         <v>27</v>
       </c>
-      <c r="J48" s="140"/>
+      <c r="J48" s="172"/>
       <c r="K48" s="32" t="s">
         <v>28</v>
       </c>
@@ -11573,10 +11581,10 @@
       <c r="H49" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="I49" s="126" t="s">
+      <c r="I49" s="163" t="s">
         <v>29</v>
       </c>
-      <c r="J49" s="124"/>
+      <c r="J49" s="127"/>
       <c r="K49" s="37" t="s">
         <v>29</v>
       </c>
@@ -11597,10 +11605,10 @@
       <c r="H50" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="I50" s="126" t="s">
+      <c r="I50" s="163" t="s">
         <v>31</v>
       </c>
-      <c r="J50" s="124"/>
+      <c r="J50" s="127"/>
       <c r="K50" s="37" t="s">
         <v>31</v>
       </c>
@@ -11621,10 +11629,10 @@
       <c r="H51" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I51" s="126" t="s">
+      <c r="I51" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="124"/>
+      <c r="J51" s="127"/>
       <c r="K51" s="37" t="s">
         <v>33</v>
       </c>
@@ -11645,10 +11653,10 @@
       <c r="H52" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="I52" s="127" t="s">
+      <c r="I52" s="164" t="s">
         <v>35</v>
       </c>
-      <c r="J52" s="128"/>
+      <c r="J52" s="123"/>
       <c r="K52" s="43" t="s">
         <v>35</v>
       </c>
@@ -11671,23 +11679,23 @@
       <c r="B54" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="122" t="s">
+      <c r="C54" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="D54" s="124"/>
-      <c r="E54" s="122" t="s">
+      <c r="D54" s="127"/>
+      <c r="E54" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="F54" s="125"/>
-      <c r="G54" s="124"/>
-      <c r="H54" s="122" t="s">
+      <c r="F54" s="126"/>
+      <c r="G54" s="127"/>
+      <c r="H54" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="I54" s="124"/>
-      <c r="J54" s="122" t="s">
+      <c r="I54" s="127"/>
+      <c r="J54" s="161" t="s">
         <v>106</v>
       </c>
-      <c r="K54" s="124"/>
+      <c r="K54" s="127"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1">
       <c r="A55" s="1"/>
@@ -11744,42 +11752,42 @@
     <row r="59" spans="1:11" ht="15.75" customHeight="1">
       <c r="A59" s="51"/>
       <c r="B59" s="52"/>
-      <c r="C59" s="170" t="s">
+      <c r="C59" s="125" t="s">
         <v>107</v>
       </c>
-      <c r="D59" s="124"/>
-      <c r="E59" s="170" t="s">
+      <c r="D59" s="127"/>
+      <c r="E59" s="125" t="s">
         <v>108</v>
       </c>
-      <c r="F59" s="125"/>
-      <c r="G59" s="124"/>
-      <c r="H59" s="170" t="s">
+      <c r="F59" s="126"/>
+      <c r="G59" s="127"/>
+      <c r="H59" s="125" t="s">
         <v>109</v>
       </c>
-      <c r="I59" s="124"/>
-      <c r="J59" s="170" t="s">
+      <c r="I59" s="127"/>
+      <c r="J59" s="125" t="s">
         <v>110</v>
       </c>
-      <c r="K59" s="124"/>
+      <c r="K59" s="127"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="53"/>
-      <c r="C60" s="169"/>
-      <c r="D60" s="128"/>
-      <c r="E60" s="169" t="s">
+      <c r="C60" s="122"/>
+      <c r="D60" s="123"/>
+      <c r="E60" s="122" t="s">
         <v>111</v>
       </c>
-      <c r="F60" s="132"/>
-      <c r="G60" s="128"/>
-      <c r="H60" s="169" t="s">
+      <c r="F60" s="124"/>
+      <c r="G60" s="123"/>
+      <c r="H60" s="122" t="s">
         <v>112</v>
       </c>
-      <c r="I60" s="128"/>
-      <c r="J60" s="169" t="s">
+      <c r="I60" s="123"/>
+      <c r="J60" s="122" t="s">
         <v>113</v>
       </c>
-      <c r="K60" s="128"/>
+      <c r="K60" s="123"/>
     </row>
     <row r="61" spans="1:11" ht="15.75" customHeight="1">
       <c r="A61" s="1"/>
@@ -15123,40 +15131,22 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="H42:K44"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:G60"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="H59:I59"/>
     <mergeCell ref="J59:K59"/>
     <mergeCell ref="B2:D5"/>
     <mergeCell ref="E2:H3"/>
@@ -15173,22 +15163,40 @@
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:K8"/>
     <mergeCell ref="I9:K9"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:G60"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="H42:K44"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I37:K37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -15232,56 +15240,56 @@
     </row>
     <row r="2" spans="1:11" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="145"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="148"/>
-      <c r="E2" s="143" t="s">
+      <c r="B2" s="136"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="143" t="s">
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="134"/>
-      <c r="K2" s="135"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="134"/>
     </row>
     <row r="3" spans="1:11" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="147"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="149"/>
-      <c r="J3" s="147"/>
-      <c r="K3" s="152"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="139"/>
+      <c r="H3" s="142"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="139"/>
+      <c r="K3" s="144"/>
     </row>
     <row r="4" spans="1:11" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="153" t="s">
+      <c r="B4" s="137"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="182"/>
+      <c r="E4" s="145" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="154"/>
-      <c r="G4" s="154"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="174" t="s">
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="J4" s="157"/>
-      <c r="K4" s="158"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="150"/>
     </row>
     <row r="5" spans="1:11" ht="14.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="146"/>
-      <c r="C5" s="147"/>
-      <c r="D5" s="150"/>
+      <c r="B5" s="138"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="142"/>
       <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
@@ -15290,70 +15298,70 @@
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="83"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="124"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="127"/>
     </row>
     <row r="6" spans="1:11" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="179" t="s">
+      <c r="B6" s="188" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="177"/>
-      <c r="D6" s="178"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="187"/>
       <c r="E6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="176">
+      <c r="F6" s="185">
         <v>20230682322</v>
       </c>
-      <c r="G6" s="177"/>
-      <c r="H6" s="178"/>
-      <c r="I6" s="144"/>
-      <c r="J6" s="132"/>
-      <c r="K6" s="128"/>
+      <c r="G6" s="186"/>
+      <c r="H6" s="187"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="124"/>
+      <c r="K6" s="123"/>
     </row>
     <row r="7" spans="1:11" ht="14.4">
       <c r="A7" s="1"/>
-      <c r="B7" s="163" t="s">
+      <c r="B7" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="165" t="s">
+      <c r="C7" s="157" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="166"/>
-      <c r="E7" s="145" t="s">
+      <c r="D7" s="158"/>
+      <c r="E7" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="135"/>
-      <c r="G7" s="180" t="s">
+      <c r="F7" s="134"/>
+      <c r="G7" s="189" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="198" t="s">
+      <c r="H7" s="193" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="151" t="s">
+      <c r="I7" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="134"/>
-      <c r="K7" s="135"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="134"/>
     </row>
     <row r="8" spans="1:11" ht="14.4">
       <c r="A8" s="1"/>
-      <c r="B8" s="164"/>
+      <c r="B8" s="156"/>
       <c r="C8" s="8">
         <v>0.33333333333333331</v>
       </c>
       <c r="D8" s="55">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="131"/>
-      <c r="F8" s="128"/>
-      <c r="G8" s="132"/>
-      <c r="H8" s="182"/>
-      <c r="I8" s="132"/>
-      <c r="J8" s="132"/>
-      <c r="K8" s="128"/>
+      <c r="E8" s="166"/>
+      <c r="F8" s="123"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="191"/>
+      <c r="I8" s="124"/>
+      <c r="J8" s="124"/>
+      <c r="K8" s="123"/>
     </row>
     <row r="9" spans="1:11" ht="14.4">
       <c r="A9" s="1"/>
@@ -15379,11 +15387,11 @@
       <c r="H9" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I9" s="185" t="s">
+      <c r="I9" s="181" t="s">
         <v>117</v>
       </c>
-      <c r="J9" s="154"/>
-      <c r="K9" s="184"/>
+      <c r="J9" s="146"/>
+      <c r="K9" s="178"/>
     </row>
     <row r="10" spans="1:11" ht="14.4">
       <c r="A10" s="82"/>
@@ -15409,11 +15417,11 @@
       <c r="H10" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I10" s="185" t="s">
+      <c r="I10" s="181" t="s">
         <v>118</v>
       </c>
-      <c r="J10" s="154"/>
-      <c r="K10" s="184"/>
+      <c r="J10" s="146"/>
+      <c r="K10" s="178"/>
     </row>
     <row r="11" spans="1:11" ht="14.4">
       <c r="A11" s="1"/>
@@ -15439,11 +15447,11 @@
       <c r="H11" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I11" s="185" t="s">
+      <c r="I11" s="181" t="s">
         <v>119</v>
       </c>
-      <c r="J11" s="154"/>
-      <c r="K11" s="184"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="178"/>
     </row>
     <row r="12" spans="1:11" ht="14.4">
       <c r="A12" s="1"/>
@@ -15469,11 +15477,11 @@
       <c r="H12" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I12" s="183" t="s">
+      <c r="I12" s="177" t="s">
         <v>120</v>
       </c>
-      <c r="J12" s="154"/>
-      <c r="K12" s="184"/>
+      <c r="J12" s="146"/>
+      <c r="K12" s="178"/>
     </row>
     <row r="13" spans="1:11" ht="21.75" customHeight="1">
       <c r="A13" s="1"/>
@@ -15493,9 +15501,9 @@
         <v>0</v>
       </c>
       <c r="H13" s="83"/>
-      <c r="I13" s="183"/>
-      <c r="J13" s="154"/>
-      <c r="K13" s="184"/>
+      <c r="I13" s="177"/>
+      <c r="J13" s="146"/>
+      <c r="K13" s="178"/>
     </row>
     <row r="14" spans="1:11" ht="21.75" customHeight="1">
       <c r="A14" s="1"/>
@@ -15515,9 +15523,9 @@
         <v>0</v>
       </c>
       <c r="H14" s="83"/>
-      <c r="I14" s="185"/>
-      <c r="J14" s="154"/>
-      <c r="K14" s="184"/>
+      <c r="I14" s="181"/>
+      <c r="J14" s="146"/>
+      <c r="K14" s="178"/>
     </row>
     <row r="15" spans="1:11" ht="14.4">
       <c r="A15" s="1"/>
@@ -15543,11 +15551,11 @@
       <c r="H15" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="185" t="s">
+      <c r="I15" s="181" t="s">
         <v>121</v>
       </c>
-      <c r="J15" s="154"/>
-      <c r="K15" s="184"/>
+      <c r="J15" s="146"/>
+      <c r="K15" s="178"/>
     </row>
     <row r="16" spans="1:11" ht="20.25" customHeight="1">
       <c r="A16" s="1"/>
@@ -15569,11 +15577,11 @@
       <c r="H16" s="93" t="s">
         <v>122</v>
       </c>
-      <c r="I16" s="185" t="s">
+      <c r="I16" s="181" t="s">
         <v>123</v>
       </c>
-      <c r="J16" s="154"/>
-      <c r="K16" s="184"/>
+      <c r="J16" s="146"/>
+      <c r="K16" s="178"/>
     </row>
     <row r="17" spans="1:11" ht="14.4">
       <c r="A17" s="1"/>
@@ -15599,11 +15607,11 @@
       <c r="H17" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="199" t="s">
+      <c r="I17" s="192" t="s">
         <v>124</v>
       </c>
-      <c r="J17" s="154"/>
-      <c r="K17" s="184"/>
+      <c r="J17" s="146"/>
+      <c r="K17" s="178"/>
     </row>
     <row r="18" spans="1:11" ht="14.4">
       <c r="A18" s="1"/>
@@ -15629,11 +15637,11 @@
       <c r="H18" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="185" t="s">
+      <c r="I18" s="181" t="s">
         <v>121</v>
       </c>
-      <c r="J18" s="154"/>
-      <c r="K18" s="184"/>
+      <c r="J18" s="146"/>
+      <c r="K18" s="178"/>
     </row>
     <row r="19" spans="1:11" ht="14.4">
       <c r="A19" s="1"/>
@@ -15659,11 +15667,11 @@
       <c r="H19" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I19" s="185" t="s">
+      <c r="I19" s="181" t="s">
         <v>125</v>
       </c>
-      <c r="J19" s="154"/>
-      <c r="K19" s="184"/>
+      <c r="J19" s="146"/>
+      <c r="K19" s="178"/>
     </row>
     <row r="20" spans="1:11" ht="21.75" customHeight="1">
       <c r="A20" s="1"/>
@@ -15683,9 +15691,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="83"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="154"/>
-      <c r="K20" s="184"/>
+      <c r="I20" s="181"/>
+      <c r="J20" s="146"/>
+      <c r="K20" s="178"/>
     </row>
     <row r="21" spans="1:11" ht="21.75" customHeight="1">
       <c r="A21" s="1"/>
@@ -15705,9 +15713,9 @@
         <v>0</v>
       </c>
       <c r="H21" s="83"/>
-      <c r="I21" s="185"/>
-      <c r="J21" s="154"/>
-      <c r="K21" s="184"/>
+      <c r="I21" s="181"/>
+      <c r="J21" s="146"/>
+      <c r="K21" s="178"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
@@ -15733,11 +15741,11 @@
       <c r="H22" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="185" t="s">
+      <c r="I22" s="181" t="s">
         <v>126</v>
       </c>
-      <c r="J22" s="154"/>
-      <c r="K22" s="184"/>
+      <c r="J22" s="146"/>
+      <c r="K22" s="178"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
       <c r="A23" s="1"/>
@@ -15763,11 +15771,11 @@
       <c r="H23" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="185" t="s">
+      <c r="I23" s="181" t="s">
         <v>127</v>
       </c>
-      <c r="J23" s="154"/>
-      <c r="K23" s="184"/>
+      <c r="J23" s="146"/>
+      <c r="K23" s="178"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
@@ -15793,11 +15801,11 @@
       <c r="H24" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="185" t="s">
+      <c r="I24" s="181" t="s">
         <v>128</v>
       </c>
-      <c r="J24" s="154"/>
-      <c r="K24" s="184"/>
+      <c r="J24" s="146"/>
+      <c r="K24" s="178"/>
     </row>
     <row r="25" spans="1:11" ht="21.75" customHeight="1">
       <c r="A25" s="1"/>
@@ -15817,9 +15825,9 @@
         <v>0</v>
       </c>
       <c r="H25" s="83"/>
-      <c r="I25" s="185"/>
-      <c r="J25" s="154"/>
-      <c r="K25" s="184"/>
+      <c r="I25" s="181"/>
+      <c r="J25" s="146"/>
+      <c r="K25" s="178"/>
     </row>
     <row r="26" spans="1:11" ht="31.5" customHeight="1">
       <c r="A26" s="1"/>
@@ -15845,11 +15853,11 @@
       <c r="H26" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="185" t="s">
+      <c r="I26" s="181" t="s">
         <v>128</v>
       </c>
-      <c r="J26" s="154"/>
-      <c r="K26" s="184"/>
+      <c r="J26" s="146"/>
+      <c r="K26" s="178"/>
     </row>
     <row r="27" spans="1:11" ht="21.75" customHeight="1">
       <c r="A27" s="1"/>
@@ -15869,9 +15877,9 @@
         <v>0</v>
       </c>
       <c r="H27" s="83"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="154"/>
-      <c r="K27" s="184"/>
+      <c r="I27" s="181"/>
+      <c r="J27" s="146"/>
+      <c r="K27" s="178"/>
     </row>
     <row r="28" spans="1:11" ht="21.75" customHeight="1">
       <c r="A28" s="1"/>
@@ -15891,9 +15899,9 @@
         <v>0</v>
       </c>
       <c r="H28" s="83"/>
-      <c r="I28" s="185"/>
-      <c r="J28" s="154"/>
-      <c r="K28" s="184"/>
+      <c r="I28" s="181"/>
+      <c r="J28" s="146"/>
+      <c r="K28" s="178"/>
     </row>
     <row r="29" spans="1:11" ht="29.25" customHeight="1">
       <c r="A29" s="1"/>
@@ -15919,11 +15927,11 @@
       <c r="H29" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="185" t="s">
+      <c r="I29" s="181" t="s">
         <v>128</v>
       </c>
-      <c r="J29" s="154"/>
-      <c r="K29" s="184"/>
+      <c r="J29" s="146"/>
+      <c r="K29" s="178"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
@@ -15949,11 +15957,11 @@
       <c r="H30" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I30" s="185" t="s">
+      <c r="I30" s="181" t="s">
         <v>128</v>
       </c>
-      <c r="J30" s="154"/>
-      <c r="K30" s="184"/>
+      <c r="J30" s="146"/>
+      <c r="K30" s="178"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1">
       <c r="A31" s="1"/>
@@ -15979,11 +15987,11 @@
       <c r="H31" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I31" s="185" t="s">
+      <c r="I31" s="181" t="s">
         <v>128</v>
       </c>
-      <c r="J31" s="154"/>
-      <c r="K31" s="184"/>
+      <c r="J31" s="146"/>
+      <c r="K31" s="178"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="1"/>
@@ -16009,11 +16017,11 @@
       <c r="H32" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I32" s="185" t="s">
+      <c r="I32" s="181" t="s">
         <v>128</v>
       </c>
-      <c r="J32" s="154"/>
-      <c r="K32" s="184"/>
+      <c r="J32" s="146"/>
+      <c r="K32" s="178"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1">
       <c r="A33" s="1"/>
@@ -16039,11 +16047,11 @@
       <c r="H33" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I33" s="185" t="s">
+      <c r="I33" s="181" t="s">
         <v>129</v>
       </c>
-      <c r="J33" s="154"/>
-      <c r="K33" s="184"/>
+      <c r="J33" s="146"/>
+      <c r="K33" s="178"/>
     </row>
     <row r="34" spans="1:11" ht="21.75" customHeight="1">
       <c r="A34" s="1"/>
@@ -16063,9 +16071,9 @@
         <v>0</v>
       </c>
       <c r="H34" s="83"/>
-      <c r="I34" s="185"/>
-      <c r="J34" s="154"/>
-      <c r="K34" s="184"/>
+      <c r="I34" s="181"/>
+      <c r="J34" s="146"/>
+      <c r="K34" s="178"/>
     </row>
     <row r="35" spans="1:11" ht="21.75" customHeight="1">
       <c r="A35" s="1"/>
@@ -16085,9 +16093,9 @@
         <v>0</v>
       </c>
       <c r="H35" s="83"/>
-      <c r="I35" s="185"/>
-      <c r="J35" s="154"/>
-      <c r="K35" s="184"/>
+      <c r="I35" s="181"/>
+      <c r="J35" s="146"/>
+      <c r="K35" s="178"/>
     </row>
     <row r="36" spans="1:11" ht="21.75" customHeight="1">
       <c r="A36" s="1"/>
@@ -16109,11 +16117,11 @@
       <c r="H36" s="93" t="s">
         <v>115</v>
       </c>
-      <c r="I36" s="185" t="s">
+      <c r="I36" s="181" t="s">
         <v>130</v>
       </c>
-      <c r="J36" s="154"/>
-      <c r="K36" s="184"/>
+      <c r="J36" s="146"/>
+      <c r="K36" s="178"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1">
       <c r="A37" s="1"/>
@@ -16139,11 +16147,11 @@
       <c r="H37" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I37" s="185" t="s">
+      <c r="I37" s="181" t="s">
         <v>131</v>
       </c>
-      <c r="J37" s="154"/>
-      <c r="K37" s="184"/>
+      <c r="J37" s="146"/>
+      <c r="K37" s="178"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1">
       <c r="A38" s="1"/>
@@ -16169,21 +16177,21 @@
       <c r="H38" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I38" s="185" t="s">
+      <c r="I38" s="181" t="s">
         <v>132</v>
       </c>
-      <c r="J38" s="154"/>
-      <c r="K38" s="184"/>
+      <c r="J38" s="146"/>
+      <c r="K38" s="178"/>
     </row>
     <row r="39" spans="1:11" ht="18" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="192" t="s">
+      <c r="B39" s="199" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="132"/>
-      <c r="D39" s="132"/>
-      <c r="E39" s="132"/>
-      <c r="F39" s="167"/>
+      <c r="C39" s="124"/>
+      <c r="D39" s="124"/>
+      <c r="E39" s="124"/>
+      <c r="F39" s="159"/>
       <c r="G39" s="91">
         <f>SUM(G9:G38)</f>
         <v>152</v>
@@ -16203,12 +16211,12 @@
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
       <c r="G40" s="23"/>
-      <c r="H40" s="193" t="s">
+      <c r="H40" s="196" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="134"/>
-      <c r="J40" s="134"/>
-      <c r="K40" s="135"/>
+      <c r="I40" s="133"/>
+      <c r="J40" s="133"/>
+      <c r="K40" s="134"/>
     </row>
     <row r="41" spans="1:11" ht="20.25" customHeight="1">
       <c r="A41" s="1"/>
@@ -16222,12 +16230,12 @@
       <c r="G41" s="26">
         <v>21</v>
       </c>
-      <c r="H41" s="194" t="s">
+      <c r="H41" s="197" t="s">
         <v>17</v>
       </c>
-      <c r="I41" s="125"/>
-      <c r="J41" s="125"/>
-      <c r="K41" s="124"/>
+      <c r="I41" s="126"/>
+      <c r="J41" s="126"/>
+      <c r="K41" s="127"/>
     </row>
     <row r="42" spans="1:11" ht="20.25" customHeight="1">
       <c r="A42" s="1"/>
@@ -16241,10 +16249,10 @@
       <c r="G42" s="27">
         <v>9</v>
       </c>
-      <c r="H42" s="125"/>
-      <c r="I42" s="125"/>
-      <c r="J42" s="125"/>
-      <c r="K42" s="124"/>
+      <c r="H42" s="126"/>
+      <c r="I42" s="126"/>
+      <c r="J42" s="126"/>
+      <c r="K42" s="127"/>
     </row>
     <row r="43" spans="1:11" ht="20.25" customHeight="1">
       <c r="A43" s="1"/>
@@ -16258,10 +16266,10 @@
       <c r="G43" s="27">
         <v>1</v>
       </c>
-      <c r="H43" s="132"/>
-      <c r="I43" s="132"/>
-      <c r="J43" s="132"/>
-      <c r="K43" s="128"/>
+      <c r="H43" s="124"/>
+      <c r="I43" s="124"/>
+      <c r="J43" s="124"/>
+      <c r="K43" s="123"/>
     </row>
     <row r="44" spans="1:11" ht="20.25" customHeight="1">
       <c r="A44" s="1"/>
@@ -16294,7 +16302,7 @@
       <c r="G45" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H45" s="194" t="s">
+      <c r="H45" s="197" t="s">
         <v>23</v>
       </c>
       <c r="I45" s="1"/>
@@ -16313,7 +16321,7 @@
       <c r="G46" s="27">
         <v>19</v>
       </c>
-      <c r="H46" s="132"/>
+      <c r="H46" s="124"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="48"/>
@@ -16334,10 +16342,10 @@
       <c r="H47" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="I47" s="139" t="s">
+      <c r="I47" s="171" t="s">
         <v>27</v>
       </c>
-      <c r="J47" s="140"/>
+      <c r="J47" s="172"/>
       <c r="K47" s="32" t="s">
         <v>28</v>
       </c>
@@ -16355,10 +16363,10 @@
       <c r="H48" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="I48" s="126" t="s">
+      <c r="I48" s="163" t="s">
         <v>29</v>
       </c>
-      <c r="J48" s="124"/>
+      <c r="J48" s="127"/>
       <c r="K48" s="37" t="s">
         <v>29</v>
       </c>
@@ -16378,10 +16386,10 @@
       <c r="H49" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="I49" s="126" t="s">
+      <c r="I49" s="163" t="s">
         <v>31</v>
       </c>
-      <c r="J49" s="124"/>
+      <c r="J49" s="127"/>
       <c r="K49" s="37" t="s">
         <v>31</v>
       </c>
@@ -16402,10 +16410,10 @@
       <c r="H50" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="I50" s="126" t="s">
+      <c r="I50" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="J50" s="124"/>
+      <c r="J50" s="127"/>
       <c r="K50" s="37" t="s">
         <v>33</v>
       </c>
@@ -16426,10 +16434,10 @@
       <c r="H51" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="I51" s="127" t="s">
+      <c r="I51" s="164" t="s">
         <v>35</v>
       </c>
-      <c r="J51" s="128"/>
+      <c r="J51" s="123"/>
       <c r="K51" s="43" t="s">
         <v>35</v>
       </c>
@@ -16452,23 +16460,23 @@
       <c r="B53" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C53" s="122" t="s">
+      <c r="C53" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="D53" s="124"/>
-      <c r="E53" s="122" t="s">
+      <c r="D53" s="127"/>
+      <c r="E53" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="F53" s="125"/>
-      <c r="G53" s="124"/>
-      <c r="H53" s="195" t="s">
+      <c r="F53" s="126"/>
+      <c r="G53" s="127"/>
+      <c r="H53" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="I53" s="124"/>
-      <c r="J53" s="122" t="s">
+      <c r="I53" s="127"/>
+      <c r="J53" s="161" t="s">
         <v>106</v>
       </c>
-      <c r="K53" s="124"/>
+      <c r="K53" s="127"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1">
       <c r="A54" s="1"/>
@@ -16525,42 +16533,42 @@
     <row r="58" spans="1:11" ht="15.75" customHeight="1">
       <c r="A58" s="51"/>
       <c r="B58" s="52"/>
-      <c r="C58" s="170" t="s">
+      <c r="C58" s="125" t="s">
         <v>143</v>
       </c>
-      <c r="D58" s="124"/>
-      <c r="E58" s="170" t="s">
+      <c r="D58" s="127"/>
+      <c r="E58" s="125" t="s">
         <v>108</v>
       </c>
-      <c r="F58" s="125"/>
-      <c r="G58" s="124"/>
-      <c r="H58" s="196" t="s">
+      <c r="F58" s="126"/>
+      <c r="G58" s="127"/>
+      <c r="H58" s="194" t="s">
         <v>109</v>
       </c>
-      <c r="I58" s="124"/>
-      <c r="J58" s="170" t="s">
+      <c r="I58" s="127"/>
+      <c r="J58" s="125" t="s">
         <v>110</v>
       </c>
-      <c r="K58" s="124"/>
+      <c r="K58" s="127"/>
     </row>
     <row r="59" spans="1:11" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="53"/>
-      <c r="C59" s="169"/>
-      <c r="D59" s="128"/>
-      <c r="E59" s="169" t="s">
+      <c r="C59" s="122"/>
+      <c r="D59" s="123"/>
+      <c r="E59" s="122" t="s">
         <v>111</v>
       </c>
-      <c r="F59" s="132"/>
-      <c r="G59" s="128"/>
-      <c r="H59" s="197" t="s">
+      <c r="F59" s="124"/>
+      <c r="G59" s="123"/>
+      <c r="H59" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="I59" s="128"/>
-      <c r="J59" s="169" t="s">
+      <c r="I59" s="123"/>
+      <c r="J59" s="122" t="s">
         <v>113</v>
       </c>
-      <c r="K59" s="128"/>
+      <c r="K59" s="123"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
@@ -19905,54 +19913,11 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="B2:D5"/>
-    <mergeCell ref="E2:H3"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="B39:F39"/>
     <mergeCell ref="H40:K40"/>
     <mergeCell ref="H41:K43"/>
     <mergeCell ref="E53:G53"/>
@@ -19964,11 +19929,54 @@
     <mergeCell ref="I49:J49"/>
     <mergeCell ref="I50:J50"/>
     <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="E2:H3"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>

--- a/TimesheetBankJakarta_Anggit_Ari_Utomo_2.xlsx
+++ b/TimesheetBankJakarta_Anggit_Ari_Utomo_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\anggit\absen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9DAB18-BDBF-4065-82C1-B51E508721D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF4F9BE-BEE6-4C77-BF16-6FD7099F30DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2495,29 +2495,62 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2528,20 +2561,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2612,68 +2636,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2705,17 +2678,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2726,8 +2717,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5451,137 +5451,137 @@
     </row>
     <row r="2" spans="1:12" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="136"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="132" t="s">
+      <c r="B2" s="145"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="143" t="s">
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="148"/>
+      <c r="J2" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="133"/>
-      <c r="L2" s="134"/>
+      <c r="K2" s="134"/>
+      <c r="L2" s="135"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="142"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
-      <c r="L3" s="144"/>
+      <c r="B3" s="130"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="147"/>
+      <c r="L3" s="152"/>
     </row>
     <row r="4" spans="1:12" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="137"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="145" t="s">
+      <c r="B4" s="130"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="153" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="148" t="s">
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="154"/>
+      <c r="I4" s="155"/>
+      <c r="J4" s="156" t="s">
         <v>152</v>
       </c>
-      <c r="K4" s="149"/>
-      <c r="L4" s="150"/>
+      <c r="K4" s="157"/>
+      <c r="L4" s="158"/>
     </row>
     <row r="5" spans="1:12" ht="14.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="138"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="139"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="147"/>
       <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="151" t="s">
+      <c r="F5" s="159" t="s">
         <v>146</v>
       </c>
-      <c r="G5" s="146"/>
-      <c r="H5" s="146"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="126"/>
-      <c r="L5" s="127"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="154"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="124"/>
     </row>
     <row r="6" spans="1:12" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="154" t="s">
+      <c r="B6" s="162" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="149"/>
-      <c r="D6" s="149"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="157"/>
       <c r="E6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="152">
+      <c r="F6" s="160">
         <v>0</v>
       </c>
-      <c r="G6" s="149"/>
-      <c r="H6" s="149"/>
-      <c r="I6" s="153"/>
-      <c r="J6" s="126"/>
-      <c r="K6" s="126"/>
-      <c r="L6" s="127"/>
+      <c r="G6" s="157"/>
+      <c r="H6" s="157"/>
+      <c r="I6" s="161"/>
+      <c r="J6" s="125"/>
+      <c r="K6" s="125"/>
+      <c r="L6" s="124"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="163" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="157" t="s">
+      <c r="C7" s="165" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="158"/>
-      <c r="E7" s="132" t="s">
+      <c r="D7" s="166"/>
+      <c r="E7" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="140"/>
-      <c r="G7" s="160" t="s">
+      <c r="F7" s="148"/>
+      <c r="G7" s="168" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="130" t="s">
+      <c r="H7" s="141" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="130" t="s">
+      <c r="I7" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="132" t="s">
+      <c r="J7" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="133"/>
-      <c r="L7" s="134"/>
+      <c r="K7" s="134"/>
+      <c r="L7" s="135"/>
     </row>
     <row r="8" spans="1:12" thickBot="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="156"/>
+      <c r="B8" s="164"/>
       <c r="C8" s="8">
         <v>0.33333333333333331</v>
       </c>
       <c r="D8" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="135"/>
-      <c r="F8" s="159"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="131"/>
-      <c r="I8" s="131"/>
-      <c r="J8" s="135"/>
-      <c r="K8" s="124"/>
-      <c r="L8" s="123"/>
+      <c r="E8" s="144"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="142"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142"/>
+      <c r="J8" s="144"/>
+      <c r="K8" s="132"/>
+      <c r="L8" s="128"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1">
       <c r="A9" s="9"/>
@@ -6286,10 +6286,12 @@
       <c r="E35" s="105">
         <v>0.27500000000000002</v>
       </c>
-      <c r="F35" s="8"/>
+      <c r="F35" s="8">
+        <v>0.74097222222222225</v>
+      </c>
       <c r="G35" s="11">
         <f t="shared" si="3"/>
-        <v>16.399999999999999</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14" t="s">
@@ -6312,11 +6314,15 @@
       <c r="D36" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E36" s="105"/>
-      <c r="F36" s="8"/>
+      <c r="E36" s="105">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="F36" s="8">
+        <v>0.72499999999999998</v>
+      </c>
       <c r="G36" s="11">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="H36" s="14"/>
       <c r="I36" s="14" t="s">
@@ -6339,11 +6345,15 @@
       <c r="D37" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E37" s="105"/>
-      <c r="F37" s="8"/>
+      <c r="E37" s="105">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F37" s="8">
+        <v>0.72916666666666663</v>
+      </c>
       <c r="G37" s="11">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>8.5</v>
       </c>
       <c r="H37" s="14"/>
       <c r="I37" s="14" t="s">
@@ -6402,16 +6412,16 @@
     </row>
     <row r="43" spans="1:12" ht="18" customHeight="1" thickBot="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="168" t="s">
+      <c r="B43" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="C43" s="169"/>
-      <c r="D43" s="169"/>
-      <c r="E43" s="169"/>
-      <c r="F43" s="170"/>
+      <c r="C43" s="137"/>
+      <c r="D43" s="137"/>
+      <c r="E43" s="137"/>
+      <c r="F43" s="138"/>
       <c r="G43" s="18">
         <f>SUM(G9:G39)</f>
-        <v>209.9</v>
+        <v>174.5</v>
       </c>
       <c r="H43" s="19"/>
       <c r="I43" s="19"/>
@@ -6429,13 +6439,13 @@
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
       <c r="G44" s="23"/>
-      <c r="H44" s="167" t="s">
+      <c r="H44" s="133" t="s">
         <v>15</v>
       </c>
-      <c r="I44" s="133"/>
-      <c r="J44" s="133"/>
-      <c r="K44" s="133"/>
-      <c r="L44" s="134"/>
+      <c r="I44" s="134"/>
+      <c r="J44" s="134"/>
+      <c r="K44" s="134"/>
+      <c r="L44" s="135"/>
     </row>
     <row r="45" spans="1:12" ht="20.25" customHeight="1">
       <c r="A45" s="1"/>
@@ -6449,13 +6459,13 @@
       <c r="G45" s="26">
         <v>21</v>
       </c>
-      <c r="H45" s="165" t="s">
+      <c r="H45" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="126"/>
-      <c r="J45" s="126"/>
-      <c r="K45" s="126"/>
-      <c r="L45" s="127"/>
+      <c r="I45" s="125"/>
+      <c r="J45" s="125"/>
+      <c r="K45" s="125"/>
+      <c r="L45" s="124"/>
     </row>
     <row r="46" spans="1:12" ht="20.25" customHeight="1">
       <c r="A46" s="1"/>
@@ -6469,11 +6479,11 @@
       <c r="G46" s="27">
         <v>0</v>
       </c>
-      <c r="H46" s="137"/>
-      <c r="I46" s="126"/>
-      <c r="J46" s="126"/>
-      <c r="K46" s="126"/>
-      <c r="L46" s="127"/>
+      <c r="H46" s="130"/>
+      <c r="I46" s="125"/>
+      <c r="J46" s="125"/>
+      <c r="K46" s="125"/>
+      <c r="L46" s="124"/>
     </row>
     <row r="47" spans="1:12" ht="20.25" customHeight="1" thickBot="1">
       <c r="A47" s="1"/>
@@ -6487,11 +6497,11 @@
       <c r="G47" s="27">
         <v>0</v>
       </c>
-      <c r="H47" s="166"/>
-      <c r="I47" s="124"/>
-      <c r="J47" s="124"/>
-      <c r="K47" s="124"/>
-      <c r="L47" s="123"/>
+      <c r="H47" s="131"/>
+      <c r="I47" s="132"/>
+      <c r="J47" s="132"/>
+      <c r="K47" s="132"/>
+      <c r="L47" s="128"/>
     </row>
     <row r="48" spans="1:12" ht="20.25" customHeight="1">
       <c r="A48" s="1"/>
@@ -6505,13 +6515,13 @@
       <c r="G48" s="27">
         <v>0</v>
       </c>
-      <c r="H48" s="167" t="s">
+      <c r="H48" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="I48" s="133"/>
-      <c r="J48" s="133"/>
-      <c r="K48" s="133"/>
-      <c r="L48" s="134"/>
+      <c r="I48" s="134"/>
+      <c r="J48" s="134"/>
+      <c r="K48" s="134"/>
+      <c r="L48" s="135"/>
     </row>
     <row r="49" spans="1:12" ht="20.25" customHeight="1">
       <c r="A49" s="1"/>
@@ -6525,13 +6535,13 @@
       <c r="G49" s="27">
         <v>0</v>
       </c>
-      <c r="H49" s="161" t="s">
+      <c r="H49" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="I49" s="126"/>
-      <c r="J49" s="126"/>
-      <c r="K49" s="126"/>
-      <c r="L49" s="127"/>
+      <c r="I49" s="125"/>
+      <c r="J49" s="125"/>
+      <c r="K49" s="125"/>
+      <c r="L49" s="124"/>
     </row>
     <row r="50" spans="1:12" ht="20.25" customHeight="1" thickBot="1">
       <c r="A50" s="1"/>
@@ -6545,11 +6555,11 @@
       <c r="G50" s="27">
         <v>22</v>
       </c>
-      <c r="H50" s="166"/>
-      <c r="I50" s="124"/>
-      <c r="J50" s="124"/>
-      <c r="K50" s="124"/>
-      <c r="L50" s="123"/>
+      <c r="H50" s="131"/>
+      <c r="I50" s="132"/>
+      <c r="J50" s="132"/>
+      <c r="K50" s="132"/>
+      <c r="L50" s="128"/>
     </row>
     <row r="51" spans="1:12" ht="24" customHeight="1" thickBot="1">
       <c r="A51" s="1"/>
@@ -6568,10 +6578,10 @@
         <v>26</v>
       </c>
       <c r="I51" s="31"/>
-      <c r="J51" s="171" t="s">
+      <c r="J51" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="K51" s="172"/>
+      <c r="K51" s="140"/>
       <c r="L51" s="32" t="s">
         <v>28</v>
       </c>
@@ -6590,10 +6600,10 @@
         <v>29</v>
       </c>
       <c r="I52" s="36"/>
-      <c r="J52" s="163" t="s">
+      <c r="J52" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="K52" s="127"/>
+      <c r="K52" s="124"/>
       <c r="L52" s="37" t="s">
         <v>29</v>
       </c>
@@ -6615,10 +6625,10 @@
         <v>31</v>
       </c>
       <c r="I53" s="36"/>
-      <c r="J53" s="163" t="s">
+      <c r="J53" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="K53" s="127"/>
+      <c r="K53" s="124"/>
       <c r="L53" s="37" t="s">
         <v>31</v>
       </c>
@@ -6634,16 +6644,16 @@
       <c r="F54" s="2"/>
       <c r="G54" s="26">
         <f>G43</f>
-        <v>209.9</v>
+        <v>174.5</v>
       </c>
       <c r="H54" s="35" t="s">
         <v>33</v>
       </c>
       <c r="I54" s="36"/>
-      <c r="J54" s="163" t="s">
+      <c r="J54" s="126" t="s">
         <v>33</v>
       </c>
-      <c r="K54" s="127"/>
+      <c r="K54" s="124"/>
       <c r="L54" s="37" t="s">
         <v>33</v>
       </c>
@@ -6659,16 +6669,16 @@
       <c r="F55" s="39"/>
       <c r="G55" s="40">
         <f>G54/G53</f>
-        <v>1.2494047619047619</v>
+        <v>1.0386904761904763</v>
       </c>
       <c r="H55" s="41" t="s">
         <v>35</v>
       </c>
       <c r="I55" s="42"/>
-      <c r="J55" s="164" t="s">
+      <c r="J55" s="127" t="s">
         <v>35</v>
       </c>
-      <c r="K55" s="123"/>
+      <c r="K55" s="128"/>
       <c r="L55" s="43" t="s">
         <v>35</v>
       </c>
@@ -6690,32 +6700,32 @@
     <row r="57" spans="1:12" ht="15.75" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="28"/>
-      <c r="C57" s="161" t="s">
+      <c r="C57" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="D57" s="127"/>
-      <c r="E57" s="161" t="s">
+      <c r="D57" s="124"/>
+      <c r="E57" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="F57" s="126"/>
-      <c r="G57" s="127"/>
-      <c r="H57" s="161" t="s">
+      <c r="F57" s="125"/>
+      <c r="G57" s="124"/>
+      <c r="H57" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="I57" s="126"/>
-      <c r="J57" s="127"/>
-      <c r="K57" s="161" t="s">
+      <c r="I57" s="125"/>
+      <c r="J57" s="124"/>
+      <c r="K57" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="L57" s="127"/>
+      <c r="L57" s="124"/>
     </row>
     <row r="58" spans="1:12" ht="15.75" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="161"/>
-      <c r="D58" s="162"/>
+      <c r="C58" s="122"/>
+      <c r="D58" s="123"/>
       <c r="E58" s="47"/>
       <c r="F58" s="1"/>
       <c r="G58" s="48"/>
@@ -6730,8 +6740,8 @@
       <c r="B59" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="C59" s="161"/>
-      <c r="D59" s="162"/>
+      <c r="C59" s="122"/>
+      <c r="D59" s="123"/>
       <c r="E59" s="47"/>
       <c r="F59" s="1"/>
       <c r="G59" s="48"/>
@@ -6746,8 +6756,8 @@
       <c r="B60" s="50">
         <v>46257</v>
       </c>
-      <c r="C60" s="161"/>
-      <c r="D60" s="162"/>
+      <c r="C60" s="122"/>
+      <c r="D60" s="123"/>
       <c r="E60" s="47"/>
       <c r="F60" s="1"/>
       <c r="G60" s="48"/>
@@ -6760,8 +6770,8 @@
     <row r="61" spans="1:12" ht="15.75" customHeight="1">
       <c r="A61" s="51"/>
       <c r="B61" s="47"/>
-      <c r="C61" s="161"/>
-      <c r="D61" s="162"/>
+      <c r="C61" s="122"/>
+      <c r="D61" s="123"/>
       <c r="E61" s="47"/>
       <c r="F61" s="1"/>
       <c r="G61" s="48"/>
@@ -6774,44 +6784,44 @@
     <row r="62" spans="1:12" ht="15.75" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="52"/>
-      <c r="C62" s="129" t="s">
+      <c r="C62" s="172" t="s">
         <v>151</v>
       </c>
-      <c r="D62" s="127"/>
-      <c r="E62" s="125" t="s">
+      <c r="D62" s="124"/>
+      <c r="E62" s="170" t="s">
         <v>41</v>
       </c>
-      <c r="F62" s="126"/>
-      <c r="G62" s="127"/>
-      <c r="H62" s="128" t="s">
+      <c r="F62" s="125"/>
+      <c r="G62" s="124"/>
+      <c r="H62" s="171" t="s">
         <v>145</v>
       </c>
-      <c r="I62" s="126"/>
-      <c r="J62" s="127"/>
-      <c r="K62" s="125" t="s">
+      <c r="I62" s="125"/>
+      <c r="J62" s="124"/>
+      <c r="K62" s="170" t="s">
         <v>42</v>
       </c>
-      <c r="L62" s="127"/>
+      <c r="L62" s="124"/>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A63" s="1"/>
       <c r="B63" s="53"/>
-      <c r="C63" s="122"/>
-      <c r="D63" s="123"/>
-      <c r="E63" s="122" t="s">
+      <c r="C63" s="169"/>
+      <c r="D63" s="128"/>
+      <c r="E63" s="169" t="s">
         <v>43</v>
       </c>
-      <c r="F63" s="124"/>
-      <c r="G63" s="123"/>
-      <c r="H63" s="122" t="s">
+      <c r="F63" s="132"/>
+      <c r="G63" s="128"/>
+      <c r="H63" s="169" t="s">
         <v>44</v>
       </c>
-      <c r="I63" s="124"/>
-      <c r="J63" s="123"/>
-      <c r="K63" s="122" t="s">
+      <c r="I63" s="132"/>
+      <c r="J63" s="128"/>
+      <c r="K63" s="169" t="s">
         <v>45</v>
       </c>
-      <c r="L63" s="123"/>
+      <c r="L63" s="128"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1">
       <c r="A64" s="1"/>
@@ -10351,6 +10361,48 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="H63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:L8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="E2:I3"/>
+    <mergeCell ref="J2:L3"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="J4:L6"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:G8"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="C58:D61"/>
     <mergeCell ref="C57:D57"/>
@@ -10367,48 +10419,6 @@
     <mergeCell ref="J51:K51"/>
     <mergeCell ref="H49:L50"/>
     <mergeCell ref="H44:L44"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:L8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="B2:D5"/>
-    <mergeCell ref="E2:I3"/>
-    <mergeCell ref="J2:L3"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="J4:L6"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="J30:L30"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="H63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="J21:L21"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.19685039370078741" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="81" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -10451,128 +10461,128 @@
     </row>
     <row r="2" spans="1:11" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="136"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="140"/>
-      <c r="E2" s="132" t="s">
+      <c r="B2" s="145"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="132" t="s">
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="133"/>
-      <c r="K2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="135"/>
     </row>
     <row r="3" spans="1:11" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="144"/>
+      <c r="B3" s="130"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="152"/>
     </row>
     <row r="4" spans="1:11" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="137"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="182"/>
-      <c r="E4" s="145" t="s">
+      <c r="B4" s="130"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="183" t="s">
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="155"/>
+      <c r="I4" s="174" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="149"/>
-      <c r="K4" s="150"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="158"/>
     </row>
     <row r="5" spans="1:11" ht="14.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="138"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="142"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="150"/>
       <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="151" t="s">
+      <c r="F5" s="159" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="146"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="184"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="127"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="124"/>
     </row>
     <row r="6" spans="1:11" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="179" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="187"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="178"/>
       <c r="E6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="185">
+      <c r="F6" s="176">
         <v>20230682322</v>
       </c>
-      <c r="G6" s="186"/>
-      <c r="H6" s="187"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="123"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="144"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="128"/>
     </row>
     <row r="7" spans="1:11" ht="14.4">
       <c r="A7" s="1"/>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="163" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="157" t="s">
+      <c r="C7" s="165" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="158"/>
-      <c r="E7" s="136" t="s">
+      <c r="D7" s="166"/>
+      <c r="E7" s="145" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="134"/>
-      <c r="G7" s="189" t="s">
+      <c r="F7" s="135"/>
+      <c r="G7" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="190" t="s">
+      <c r="H7" s="181" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="143" t="s">
+      <c r="I7" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="133"/>
-      <c r="K7" s="134"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="135"/>
     </row>
     <row r="8" spans="1:11" ht="14.4">
       <c r="A8" s="1"/>
-      <c r="B8" s="156"/>
+      <c r="B8" s="164"/>
       <c r="C8" s="8">
         <v>0.33333333333333331</v>
       </c>
       <c r="D8" s="55">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="166"/>
-      <c r="F8" s="123"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="191"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="124"/>
-      <c r="K8" s="123"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="182"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="128"/>
     </row>
     <row r="9" spans="1:11" ht="14.4">
       <c r="A9" s="2"/>
@@ -10597,11 +10607,11 @@
       <c r="H9" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="177" t="s">
+      <c r="I9" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="146"/>
-      <c r="K9" s="178"/>
+      <c r="J9" s="154"/>
+      <c r="K9" s="184"/>
     </row>
     <row r="10" spans="1:11" ht="14.4">
       <c r="A10" s="9"/>
@@ -10626,11 +10636,11 @@
       <c r="H10" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="177" t="s">
+      <c r="I10" s="183" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="146"/>
-      <c r="K10" s="178"/>
+      <c r="J10" s="154"/>
+      <c r="K10" s="184"/>
     </row>
     <row r="11" spans="1:11" ht="14.4">
       <c r="A11" s="2"/>
@@ -10655,11 +10665,11 @@
       <c r="H11" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I11" s="177" t="s">
+      <c r="I11" s="183" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="146"/>
-      <c r="K11" s="178"/>
+      <c r="J11" s="154"/>
+      <c r="K11" s="184"/>
     </row>
     <row r="12" spans="1:11" ht="14.4">
       <c r="A12" s="2"/>
@@ -10678,9 +10688,9 @@
         <v>0</v>
       </c>
       <c r="H12" s="13"/>
-      <c r="I12" s="177"/>
-      <c r="J12" s="146"/>
-      <c r="K12" s="178"/>
+      <c r="I12" s="183"/>
+      <c r="J12" s="154"/>
+      <c r="K12" s="184"/>
     </row>
     <row r="13" spans="1:11" ht="14.4">
       <c r="A13" s="2"/>
@@ -10699,9 +10709,9 @@
         <v>0</v>
       </c>
       <c r="H13" s="13"/>
-      <c r="I13" s="177"/>
-      <c r="J13" s="146"/>
-      <c r="K13" s="178"/>
+      <c r="I13" s="183"/>
+      <c r="J13" s="154"/>
+      <c r="K13" s="184"/>
     </row>
     <row r="14" spans="1:11" ht="14.4">
       <c r="A14" s="2"/>
@@ -10726,11 +10736,11 @@
       <c r="H14" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I14" s="177" t="s">
+      <c r="I14" s="183" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="146"/>
-      <c r="K14" s="178"/>
+      <c r="J14" s="154"/>
+      <c r="K14" s="184"/>
     </row>
     <row r="15" spans="1:11" ht="14.4">
       <c r="A15" s="2"/>
@@ -10755,11 +10765,11 @@
       <c r="H15" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="177" t="s">
+      <c r="I15" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="146"/>
-      <c r="K15" s="178"/>
+      <c r="J15" s="154"/>
+      <c r="K15" s="184"/>
     </row>
     <row r="16" spans="1:11" ht="14.4">
       <c r="A16" s="2"/>
@@ -10778,9 +10788,9 @@
         <v>0</v>
       </c>
       <c r="H16" s="11"/>
-      <c r="I16" s="181"/>
-      <c r="J16" s="146"/>
-      <c r="K16" s="178"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="154"/>
+      <c r="K16" s="184"/>
     </row>
     <row r="17" spans="1:11" ht="14.4">
       <c r="A17" s="2"/>
@@ -10805,11 +10815,11 @@
       <c r="H17" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="177" t="s">
+      <c r="I17" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="J17" s="146"/>
-      <c r="K17" s="178"/>
+      <c r="J17" s="154"/>
+      <c r="K17" s="184"/>
     </row>
     <row r="18" spans="1:11" ht="14.4">
       <c r="A18" s="2"/>
@@ -10834,11 +10844,11 @@
       <c r="H18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="177" t="s">
+      <c r="I18" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="J18" s="146"/>
-      <c r="K18" s="178"/>
+      <c r="J18" s="154"/>
+      <c r="K18" s="184"/>
     </row>
     <row r="19" spans="1:11" ht="14.4">
       <c r="A19" s="2"/>
@@ -10857,9 +10867,9 @@
         <v>0</v>
       </c>
       <c r="H19" s="11"/>
-      <c r="I19" s="181"/>
-      <c r="J19" s="146"/>
-      <c r="K19" s="178"/>
+      <c r="I19" s="185"/>
+      <c r="J19" s="154"/>
+      <c r="K19" s="184"/>
     </row>
     <row r="20" spans="1:11" ht="14.4">
       <c r="A20" s="2"/>
@@ -10878,9 +10888,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="11"/>
-      <c r="I20" s="181"/>
-      <c r="J20" s="146"/>
-      <c r="K20" s="178"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="154"/>
+      <c r="K20" s="184"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1">
       <c r="A21" s="2"/>
@@ -10905,11 +10915,11 @@
       <c r="H21" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I21" s="177" t="s">
+      <c r="I21" s="183" t="s">
         <v>68</v>
       </c>
-      <c r="J21" s="146"/>
-      <c r="K21" s="178"/>
+      <c r="J21" s="154"/>
+      <c r="K21" s="184"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
       <c r="A22" s="2"/>
@@ -10934,11 +10944,11 @@
       <c r="H22" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="177" t="s">
+      <c r="I22" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="146"/>
-      <c r="K22" s="178"/>
+      <c r="J22" s="154"/>
+      <c r="K22" s="184"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
       <c r="A23" s="2"/>
@@ -10963,11 +10973,11 @@
       <c r="H23" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="177" t="s">
+      <c r="I23" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="146"/>
-      <c r="K23" s="178"/>
+      <c r="J23" s="154"/>
+      <c r="K23" s="184"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="2"/>
@@ -10992,11 +11002,11 @@
       <c r="H24" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="177" t="s">
+      <c r="I24" s="183" t="s">
         <v>72</v>
       </c>
-      <c r="J24" s="146"/>
-      <c r="K24" s="178"/>
+      <c r="J24" s="154"/>
+      <c r="K24" s="184"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1">
       <c r="A25" s="2"/>
@@ -11021,11 +11031,11 @@
       <c r="H25" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="177" t="s">
+      <c r="I25" s="183" t="s">
         <v>74</v>
       </c>
-      <c r="J25" s="146"/>
-      <c r="K25" s="178"/>
+      <c r="J25" s="154"/>
+      <c r="K25" s="184"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1">
       <c r="A26" s="2"/>
@@ -11044,9 +11054,9 @@
         <v>0</v>
       </c>
       <c r="H26" s="11"/>
-      <c r="I26" s="181"/>
-      <c r="J26" s="146"/>
-      <c r="K26" s="178"/>
+      <c r="I26" s="185"/>
+      <c r="J26" s="154"/>
+      <c r="K26" s="184"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
       <c r="A27" s="2"/>
@@ -11065,9 +11075,9 @@
         <v>0</v>
       </c>
       <c r="H27" s="11"/>
-      <c r="I27" s="181"/>
-      <c r="J27" s="146"/>
-      <c r="K27" s="178"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="154"/>
+      <c r="K27" s="184"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1">
       <c r="A28" s="2"/>
@@ -11092,11 +11102,11 @@
       <c r="H28" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I28" s="177" t="s">
+      <c r="I28" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="J28" s="146"/>
-      <c r="K28" s="178"/>
+      <c r="J28" s="154"/>
+      <c r="K28" s="184"/>
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1">
       <c r="A29" s="2"/>
@@ -11121,11 +11131,11 @@
       <c r="H29" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="177" t="s">
+      <c r="I29" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="J29" s="146"/>
-      <c r="K29" s="178"/>
+      <c r="J29" s="154"/>
+      <c r="K29" s="184"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="2"/>
@@ -11150,11 +11160,11 @@
       <c r="H30" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I30" s="177" t="s">
+      <c r="I30" s="183" t="s">
         <v>82</v>
       </c>
-      <c r="J30" s="146"/>
-      <c r="K30" s="178"/>
+      <c r="J30" s="154"/>
+      <c r="K30" s="184"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1">
       <c r="A31" s="2"/>
@@ -11179,11 +11189,11 @@
       <c r="H31" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I31" s="177" t="s">
+      <c r="I31" s="183" t="s">
         <v>84</v>
       </c>
-      <c r="J31" s="146"/>
-      <c r="K31" s="178"/>
+      <c r="J31" s="154"/>
+      <c r="K31" s="184"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="2"/>
@@ -11208,11 +11218,11 @@
       <c r="H32" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I32" s="177" t="s">
+      <c r="I32" s="183" t="s">
         <v>86</v>
       </c>
-      <c r="J32" s="146"/>
-      <c r="K32" s="178"/>
+      <c r="J32" s="154"/>
+      <c r="K32" s="184"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1">
       <c r="A33" s="2"/>
@@ -11231,9 +11241,9 @@
         <v>0</v>
       </c>
       <c r="H33" s="11"/>
-      <c r="I33" s="181"/>
-      <c r="J33" s="146"/>
-      <c r="K33" s="178"/>
+      <c r="I33" s="185"/>
+      <c r="J33" s="154"/>
+      <c r="K33" s="184"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1">
       <c r="A34" s="2"/>
@@ -11252,9 +11262,9 @@
         <v>0</v>
       </c>
       <c r="H34" s="11"/>
-      <c r="I34" s="181"/>
-      <c r="J34" s="146"/>
-      <c r="K34" s="178"/>
+      <c r="I34" s="185"/>
+      <c r="J34" s="154"/>
+      <c r="K34" s="184"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1">
       <c r="A35" s="2"/>
@@ -11279,11 +11289,11 @@
       <c r="H35" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I35" s="177" t="s">
+      <c r="I35" s="183" t="s">
         <v>90</v>
       </c>
-      <c r="J35" s="146"/>
-      <c r="K35" s="178"/>
+      <c r="J35" s="154"/>
+      <c r="K35" s="184"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1">
       <c r="A36" s="2"/>
@@ -11308,11 +11318,11 @@
       <c r="H36" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I36" s="177" t="s">
+      <c r="I36" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="J36" s="146"/>
-      <c r="K36" s="178"/>
+      <c r="J36" s="154"/>
+      <c r="K36" s="184"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1">
       <c r="A37" s="2"/>
@@ -11337,11 +11347,11 @@
       <c r="H37" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I37" s="177" t="s">
+      <c r="I37" s="183" t="s">
         <v>68</v>
       </c>
-      <c r="J37" s="146"/>
-      <c r="K37" s="178"/>
+      <c r="J37" s="154"/>
+      <c r="K37" s="184"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1">
       <c r="A38" s="2"/>
@@ -11366,11 +11376,11 @@
       <c r="H38" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I38" s="177" t="s">
+      <c r="I38" s="183" t="s">
         <v>94</v>
       </c>
-      <c r="J38" s="146"/>
-      <c r="K38" s="178"/>
+      <c r="J38" s="154"/>
+      <c r="K38" s="184"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1">
       <c r="A39" s="2"/>
@@ -11395,21 +11405,21 @@
       <c r="H39" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I39" s="180" t="s">
+      <c r="I39" s="187" t="s">
         <v>94</v>
       </c>
-      <c r="J39" s="149"/>
-      <c r="K39" s="150"/>
+      <c r="J39" s="157"/>
+      <c r="K39" s="158"/>
     </row>
     <row r="40" spans="1:11" ht="18" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="168" t="s">
+      <c r="B40" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="173"/>
-      <c r="D40" s="173"/>
-      <c r="E40" s="173"/>
-      <c r="F40" s="174"/>
+      <c r="C40" s="188"/>
+      <c r="D40" s="188"/>
+      <c r="E40" s="188"/>
+      <c r="F40" s="189"/>
       <c r="G40" s="18">
         <f>SUM(G9:G39)</f>
         <v>176</v>
@@ -11429,12 +11439,12 @@
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
       <c r="G41" s="23"/>
-      <c r="H41" s="175" t="s">
+      <c r="H41" s="190" t="s">
         <v>15</v>
       </c>
-      <c r="I41" s="133"/>
-      <c r="J41" s="133"/>
-      <c r="K41" s="134"/>
+      <c r="I41" s="134"/>
+      <c r="J41" s="134"/>
+      <c r="K41" s="135"/>
     </row>
     <row r="42" spans="1:11" ht="20.25" customHeight="1">
       <c r="A42" s="1"/>
@@ -11448,12 +11458,12 @@
       <c r="G42" s="26">
         <v>22</v>
       </c>
-      <c r="H42" s="176" t="s">
+      <c r="H42" s="191" t="s">
         <v>17</v>
       </c>
-      <c r="I42" s="126"/>
-      <c r="J42" s="126"/>
-      <c r="K42" s="127"/>
+      <c r="I42" s="125"/>
+      <c r="J42" s="125"/>
+      <c r="K42" s="124"/>
     </row>
     <row r="43" spans="1:11" ht="20.25" customHeight="1">
       <c r="A43" s="1"/>
@@ -11467,10 +11477,10 @@
       <c r="G43" s="27">
         <v>9</v>
       </c>
-      <c r="H43" s="126"/>
-      <c r="I43" s="126"/>
-      <c r="J43" s="126"/>
-      <c r="K43" s="127"/>
+      <c r="H43" s="125"/>
+      <c r="I43" s="125"/>
+      <c r="J43" s="125"/>
+      <c r="K43" s="124"/>
     </row>
     <row r="44" spans="1:11" ht="20.25" customHeight="1">
       <c r="A44" s="1"/>
@@ -11484,10 +11494,10 @@
       <c r="G44" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H44" s="124"/>
-      <c r="I44" s="124"/>
-      <c r="J44" s="124"/>
-      <c r="K44" s="123"/>
+      <c r="H44" s="132"/>
+      <c r="I44" s="132"/>
+      <c r="J44" s="132"/>
+      <c r="K44" s="128"/>
     </row>
     <row r="45" spans="1:11" ht="20.25" customHeight="1">
       <c r="A45" s="1"/>
@@ -11520,7 +11530,7 @@
       <c r="G46" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H46" s="179" t="s">
+      <c r="H46" s="186" t="s">
         <v>23</v>
       </c>
       <c r="I46" s="1"/>
@@ -11539,7 +11549,7 @@
       <c r="G47" s="27">
         <v>22</v>
       </c>
-      <c r="H47" s="124"/>
+      <c r="H47" s="132"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="48"/>
@@ -11560,10 +11570,10 @@
       <c r="H48" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="I48" s="171" t="s">
+      <c r="I48" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="J48" s="172"/>
+      <c r="J48" s="140"/>
       <c r="K48" s="32" t="s">
         <v>28</v>
       </c>
@@ -11581,10 +11591,10 @@
       <c r="H49" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="I49" s="163" t="s">
+      <c r="I49" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="J49" s="127"/>
+      <c r="J49" s="124"/>
       <c r="K49" s="37" t="s">
         <v>29</v>
       </c>
@@ -11605,10 +11615,10 @@
       <c r="H50" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="I50" s="163" t="s">
+      <c r="I50" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="J50" s="127"/>
+      <c r="J50" s="124"/>
       <c r="K50" s="37" t="s">
         <v>31</v>
       </c>
@@ -11629,10 +11639,10 @@
       <c r="H51" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I51" s="163" t="s">
+      <c r="I51" s="126" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="127"/>
+      <c r="J51" s="124"/>
       <c r="K51" s="37" t="s">
         <v>33</v>
       </c>
@@ -11653,10 +11663,10 @@
       <c r="H52" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="I52" s="164" t="s">
+      <c r="I52" s="127" t="s">
         <v>35</v>
       </c>
-      <c r="J52" s="123"/>
+      <c r="J52" s="128"/>
       <c r="K52" s="43" t="s">
         <v>35</v>
       </c>
@@ -11679,23 +11689,23 @@
       <c r="B54" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="161" t="s">
+      <c r="C54" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="D54" s="127"/>
-      <c r="E54" s="161" t="s">
+      <c r="D54" s="124"/>
+      <c r="E54" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="F54" s="126"/>
-      <c r="G54" s="127"/>
-      <c r="H54" s="161" t="s">
+      <c r="F54" s="125"/>
+      <c r="G54" s="124"/>
+      <c r="H54" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="I54" s="127"/>
-      <c r="J54" s="161" t="s">
+      <c r="I54" s="124"/>
+      <c r="J54" s="122" t="s">
         <v>106</v>
       </c>
-      <c r="K54" s="127"/>
+      <c r="K54" s="124"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1">
       <c r="A55" s="1"/>
@@ -11752,42 +11762,42 @@
     <row r="59" spans="1:11" ht="15.75" customHeight="1">
       <c r="A59" s="51"/>
       <c r="B59" s="52"/>
-      <c r="C59" s="125" t="s">
+      <c r="C59" s="170" t="s">
         <v>107</v>
       </c>
-      <c r="D59" s="127"/>
-      <c r="E59" s="125" t="s">
+      <c r="D59" s="124"/>
+      <c r="E59" s="170" t="s">
         <v>108</v>
       </c>
-      <c r="F59" s="126"/>
-      <c r="G59" s="127"/>
-      <c r="H59" s="125" t="s">
+      <c r="F59" s="125"/>
+      <c r="G59" s="124"/>
+      <c r="H59" s="170" t="s">
         <v>109</v>
       </c>
-      <c r="I59" s="127"/>
-      <c r="J59" s="125" t="s">
+      <c r="I59" s="124"/>
+      <c r="J59" s="170" t="s">
         <v>110</v>
       </c>
-      <c r="K59" s="127"/>
+      <c r="K59" s="124"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="53"/>
-      <c r="C60" s="122"/>
-      <c r="D60" s="123"/>
-      <c r="E60" s="122" t="s">
+      <c r="C60" s="169"/>
+      <c r="D60" s="128"/>
+      <c r="E60" s="169" t="s">
         <v>111</v>
       </c>
-      <c r="F60" s="124"/>
-      <c r="G60" s="123"/>
-      <c r="H60" s="122" t="s">
+      <c r="F60" s="132"/>
+      <c r="G60" s="128"/>
+      <c r="H60" s="169" t="s">
         <v>112</v>
       </c>
-      <c r="I60" s="123"/>
-      <c r="J60" s="122" t="s">
+      <c r="I60" s="128"/>
+      <c r="J60" s="169" t="s">
         <v>113</v>
       </c>
-      <c r="K60" s="123"/>
+      <c r="K60" s="128"/>
     </row>
     <row r="61" spans="1:11" ht="15.75" customHeight="1">
       <c r="A61" s="1"/>
@@ -15131,6 +15141,56 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="H42:K44"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="E2:H3"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K6"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:K8"/>
+    <mergeCell ref="I9:K9"/>
     <mergeCell ref="C60:D60"/>
     <mergeCell ref="E60:G60"/>
     <mergeCell ref="H60:I60"/>
@@ -15147,56 +15207,6 @@
     <mergeCell ref="C59:D59"/>
     <mergeCell ref="E59:G59"/>
     <mergeCell ref="H59:I59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="B2:D5"/>
-    <mergeCell ref="E2:H3"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K6"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="H42:K44"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I37:K37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -15240,56 +15250,56 @@
     </row>
     <row r="2" spans="1:11" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="136"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="140"/>
-      <c r="E2" s="132" t="s">
+      <c r="B2" s="145"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="132" t="s">
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="133"/>
-      <c r="K2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="135"/>
     </row>
     <row r="3" spans="1:11" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="144"/>
+      <c r="B3" s="130"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="152"/>
     </row>
     <row r="4" spans="1:11" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="137"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="182"/>
-      <c r="E4" s="145" t="s">
+      <c r="B4" s="130"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="183" t="s">
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="155"/>
+      <c r="I4" s="174" t="s">
         <v>116</v>
       </c>
-      <c r="J4" s="149"/>
-      <c r="K4" s="150"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="158"/>
     </row>
     <row r="5" spans="1:11" ht="14.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="138"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="142"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="150"/>
       <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
@@ -15298,70 +15308,70 @@
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="83"/>
-      <c r="I5" s="184"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="127"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="124"/>
     </row>
     <row r="6" spans="1:11" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="179" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="187"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="178"/>
       <c r="E6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="185">
+      <c r="F6" s="176">
         <v>20230682322</v>
       </c>
-      <c r="G6" s="186"/>
-      <c r="H6" s="187"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="123"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="144"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="128"/>
     </row>
     <row r="7" spans="1:11" ht="14.4">
       <c r="A7" s="1"/>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="163" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="157" t="s">
+      <c r="C7" s="165" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="158"/>
-      <c r="E7" s="136" t="s">
+      <c r="D7" s="166"/>
+      <c r="E7" s="145" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="134"/>
-      <c r="G7" s="189" t="s">
+      <c r="F7" s="135"/>
+      <c r="G7" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="193" t="s">
+      <c r="H7" s="198" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="143" t="s">
+      <c r="I7" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="133"/>
-      <c r="K7" s="134"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="135"/>
     </row>
     <row r="8" spans="1:11" ht="14.4">
       <c r="A8" s="1"/>
-      <c r="B8" s="156"/>
+      <c r="B8" s="164"/>
       <c r="C8" s="8">
         <v>0.33333333333333331</v>
       </c>
       <c r="D8" s="55">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="166"/>
-      <c r="F8" s="123"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="191"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="124"/>
-      <c r="K8" s="123"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="182"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="128"/>
     </row>
     <row r="9" spans="1:11" ht="14.4">
       <c r="A9" s="1"/>
@@ -15387,11 +15397,11 @@
       <c r="H9" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I9" s="181" t="s">
+      <c r="I9" s="185" t="s">
         <v>117</v>
       </c>
-      <c r="J9" s="146"/>
-      <c r="K9" s="178"/>
+      <c r="J9" s="154"/>
+      <c r="K9" s="184"/>
     </row>
     <row r="10" spans="1:11" ht="14.4">
       <c r="A10" s="82"/>
@@ -15417,11 +15427,11 @@
       <c r="H10" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I10" s="181" t="s">
+      <c r="I10" s="185" t="s">
         <v>118</v>
       </c>
-      <c r="J10" s="146"/>
-      <c r="K10" s="178"/>
+      <c r="J10" s="154"/>
+      <c r="K10" s="184"/>
     </row>
     <row r="11" spans="1:11" ht="14.4">
       <c r="A11" s="1"/>
@@ -15447,11 +15457,11 @@
       <c r="H11" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I11" s="181" t="s">
+      <c r="I11" s="185" t="s">
         <v>119</v>
       </c>
-      <c r="J11" s="146"/>
-      <c r="K11" s="178"/>
+      <c r="J11" s="154"/>
+      <c r="K11" s="184"/>
     </row>
     <row r="12" spans="1:11" ht="14.4">
       <c r="A12" s="1"/>
@@ -15477,11 +15487,11 @@
       <c r="H12" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I12" s="177" t="s">
+      <c r="I12" s="183" t="s">
         <v>120</v>
       </c>
-      <c r="J12" s="146"/>
-      <c r="K12" s="178"/>
+      <c r="J12" s="154"/>
+      <c r="K12" s="184"/>
     </row>
     <row r="13" spans="1:11" ht="21.75" customHeight="1">
       <c r="A13" s="1"/>
@@ -15501,9 +15511,9 @@
         <v>0</v>
       </c>
       <c r="H13" s="83"/>
-      <c r="I13" s="177"/>
-      <c r="J13" s="146"/>
-      <c r="K13" s="178"/>
+      <c r="I13" s="183"/>
+      <c r="J13" s="154"/>
+      <c r="K13" s="184"/>
     </row>
     <row r="14" spans="1:11" ht="21.75" customHeight="1">
       <c r="A14" s="1"/>
@@ -15523,9 +15533,9 @@
         <v>0</v>
       </c>
       <c r="H14" s="83"/>
-      <c r="I14" s="181"/>
-      <c r="J14" s="146"/>
-      <c r="K14" s="178"/>
+      <c r="I14" s="185"/>
+      <c r="J14" s="154"/>
+      <c r="K14" s="184"/>
     </row>
     <row r="15" spans="1:11" ht="14.4">
       <c r="A15" s="1"/>
@@ -15551,11 +15561,11 @@
       <c r="H15" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="181" t="s">
+      <c r="I15" s="185" t="s">
         <v>121</v>
       </c>
-      <c r="J15" s="146"/>
-      <c r="K15" s="178"/>
+      <c r="J15" s="154"/>
+      <c r="K15" s="184"/>
     </row>
     <row r="16" spans="1:11" ht="20.25" customHeight="1">
       <c r="A16" s="1"/>
@@ -15577,11 +15587,11 @@
       <c r="H16" s="93" t="s">
         <v>122</v>
       </c>
-      <c r="I16" s="181" t="s">
+      <c r="I16" s="185" t="s">
         <v>123</v>
       </c>
-      <c r="J16" s="146"/>
-      <c r="K16" s="178"/>
+      <c r="J16" s="154"/>
+      <c r="K16" s="184"/>
     </row>
     <row r="17" spans="1:11" ht="14.4">
       <c r="A17" s="1"/>
@@ -15607,11 +15617,11 @@
       <c r="H17" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="192" t="s">
+      <c r="I17" s="199" t="s">
         <v>124</v>
       </c>
-      <c r="J17" s="146"/>
-      <c r="K17" s="178"/>
+      <c r="J17" s="154"/>
+      <c r="K17" s="184"/>
     </row>
     <row r="18" spans="1:11" ht="14.4">
       <c r="A18" s="1"/>
@@ -15637,11 +15647,11 @@
       <c r="H18" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="181" t="s">
+      <c r="I18" s="185" t="s">
         <v>121</v>
       </c>
-      <c r="J18" s="146"/>
-      <c r="K18" s="178"/>
+      <c r="J18" s="154"/>
+      <c r="K18" s="184"/>
     </row>
     <row r="19" spans="1:11" ht="14.4">
       <c r="A19" s="1"/>
@@ -15667,11 +15677,11 @@
       <c r="H19" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I19" s="181" t="s">
+      <c r="I19" s="185" t="s">
         <v>125</v>
       </c>
-      <c r="J19" s="146"/>
-      <c r="K19" s="178"/>
+      <c r="J19" s="154"/>
+      <c r="K19" s="184"/>
     </row>
     <row r="20" spans="1:11" ht="21.75" customHeight="1">
       <c r="A20" s="1"/>
@@ -15691,9 +15701,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="83"/>
-      <c r="I20" s="181"/>
-      <c r="J20" s="146"/>
-      <c r="K20" s="178"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="154"/>
+      <c r="K20" s="184"/>
     </row>
     <row r="21" spans="1:11" ht="21.75" customHeight="1">
       <c r="A21" s="1"/>
@@ -15713,9 +15723,9 @@
         <v>0</v>
       </c>
       <c r="H21" s="83"/>
-      <c r="I21" s="181"/>
-      <c r="J21" s="146"/>
-      <c r="K21" s="178"/>
+      <c r="I21" s="185"/>
+      <c r="J21" s="154"/>
+      <c r="K21" s="184"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
@@ -15741,11 +15751,11 @@
       <c r="H22" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="181" t="s">
+      <c r="I22" s="185" t="s">
         <v>126</v>
       </c>
-      <c r="J22" s="146"/>
-      <c r="K22" s="178"/>
+      <c r="J22" s="154"/>
+      <c r="K22" s="184"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
       <c r="A23" s="1"/>
@@ -15771,11 +15781,11 @@
       <c r="H23" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="181" t="s">
+      <c r="I23" s="185" t="s">
         <v>127</v>
       </c>
-      <c r="J23" s="146"/>
-      <c r="K23" s="178"/>
+      <c r="J23" s="154"/>
+      <c r="K23" s="184"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
@@ -15801,11 +15811,11 @@
       <c r="H24" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="181" t="s">
+      <c r="I24" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J24" s="146"/>
-      <c r="K24" s="178"/>
+      <c r="J24" s="154"/>
+      <c r="K24" s="184"/>
     </row>
     <row r="25" spans="1:11" ht="21.75" customHeight="1">
       <c r="A25" s="1"/>
@@ -15825,9 +15835,9 @@
         <v>0</v>
       </c>
       <c r="H25" s="83"/>
-      <c r="I25" s="181"/>
-      <c r="J25" s="146"/>
-      <c r="K25" s="178"/>
+      <c r="I25" s="185"/>
+      <c r="J25" s="154"/>
+      <c r="K25" s="184"/>
     </row>
     <row r="26" spans="1:11" ht="31.5" customHeight="1">
       <c r="A26" s="1"/>
@@ -15853,11 +15863,11 @@
       <c r="H26" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="181" t="s">
+      <c r="I26" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J26" s="146"/>
-      <c r="K26" s="178"/>
+      <c r="J26" s="154"/>
+      <c r="K26" s="184"/>
     </row>
     <row r="27" spans="1:11" ht="21.75" customHeight="1">
       <c r="A27" s="1"/>
@@ -15877,9 +15887,9 @@
         <v>0</v>
       </c>
       <c r="H27" s="83"/>
-      <c r="I27" s="181"/>
-      <c r="J27" s="146"/>
-      <c r="K27" s="178"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="154"/>
+      <c r="K27" s="184"/>
     </row>
     <row r="28" spans="1:11" ht="21.75" customHeight="1">
       <c r="A28" s="1"/>
@@ -15899,9 +15909,9 @@
         <v>0</v>
       </c>
       <c r="H28" s="83"/>
-      <c r="I28" s="181"/>
-      <c r="J28" s="146"/>
-      <c r="K28" s="178"/>
+      <c r="I28" s="185"/>
+      <c r="J28" s="154"/>
+      <c r="K28" s="184"/>
     </row>
     <row r="29" spans="1:11" ht="29.25" customHeight="1">
       <c r="A29" s="1"/>
@@ -15927,11 +15937,11 @@
       <c r="H29" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="181" t="s">
+      <c r="I29" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J29" s="146"/>
-      <c r="K29" s="178"/>
+      <c r="J29" s="154"/>
+      <c r="K29" s="184"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
@@ -15957,11 +15967,11 @@
       <c r="H30" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I30" s="181" t="s">
+      <c r="I30" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J30" s="146"/>
-      <c r="K30" s="178"/>
+      <c r="J30" s="154"/>
+      <c r="K30" s="184"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1">
       <c r="A31" s="1"/>
@@ -15987,11 +15997,11 @@
       <c r="H31" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I31" s="181" t="s">
+      <c r="I31" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J31" s="146"/>
-      <c r="K31" s="178"/>
+      <c r="J31" s="154"/>
+      <c r="K31" s="184"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="1"/>
@@ -16017,11 +16027,11 @@
       <c r="H32" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I32" s="181" t="s">
+      <c r="I32" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J32" s="146"/>
-      <c r="K32" s="178"/>
+      <c r="J32" s="154"/>
+      <c r="K32" s="184"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1">
       <c r="A33" s="1"/>
@@ -16047,11 +16057,11 @@
       <c r="H33" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I33" s="181" t="s">
+      <c r="I33" s="185" t="s">
         <v>129</v>
       </c>
-      <c r="J33" s="146"/>
-      <c r="K33" s="178"/>
+      <c r="J33" s="154"/>
+      <c r="K33" s="184"/>
     </row>
     <row r="34" spans="1:11" ht="21.75" customHeight="1">
       <c r="A34" s="1"/>
@@ -16071,9 +16081,9 @@
         <v>0</v>
       </c>
       <c r="H34" s="83"/>
-      <c r="I34" s="181"/>
-      <c r="J34" s="146"/>
-      <c r="K34" s="178"/>
+      <c r="I34" s="185"/>
+      <c r="J34" s="154"/>
+      <c r="K34" s="184"/>
     </row>
     <row r="35" spans="1:11" ht="21.75" customHeight="1">
       <c r="A35" s="1"/>
@@ -16093,9 +16103,9 @@
         <v>0</v>
       </c>
       <c r="H35" s="83"/>
-      <c r="I35" s="181"/>
-      <c r="J35" s="146"/>
-      <c r="K35" s="178"/>
+      <c r="I35" s="185"/>
+      <c r="J35" s="154"/>
+      <c r="K35" s="184"/>
     </row>
     <row r="36" spans="1:11" ht="21.75" customHeight="1">
       <c r="A36" s="1"/>
@@ -16117,11 +16127,11 @@
       <c r="H36" s="93" t="s">
         <v>115</v>
       </c>
-      <c r="I36" s="181" t="s">
+      <c r="I36" s="185" t="s">
         <v>130</v>
       </c>
-      <c r="J36" s="146"/>
-      <c r="K36" s="178"/>
+      <c r="J36" s="154"/>
+      <c r="K36" s="184"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1">
       <c r="A37" s="1"/>
@@ -16147,11 +16157,11 @@
       <c r="H37" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I37" s="181" t="s">
+      <c r="I37" s="185" t="s">
         <v>131</v>
       </c>
-      <c r="J37" s="146"/>
-      <c r="K37" s="178"/>
+      <c r="J37" s="154"/>
+      <c r="K37" s="184"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1">
       <c r="A38" s="1"/>
@@ -16177,21 +16187,21 @@
       <c r="H38" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I38" s="181" t="s">
+      <c r="I38" s="185" t="s">
         <v>132</v>
       </c>
-      <c r="J38" s="146"/>
-      <c r="K38" s="178"/>
+      <c r="J38" s="154"/>
+      <c r="K38" s="184"/>
     </row>
     <row r="39" spans="1:11" ht="18" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="199" t="s">
+      <c r="B39" s="192" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="124"/>
-      <c r="D39" s="124"/>
-      <c r="E39" s="124"/>
-      <c r="F39" s="159"/>
+      <c r="C39" s="132"/>
+      <c r="D39" s="132"/>
+      <c r="E39" s="132"/>
+      <c r="F39" s="167"/>
       <c r="G39" s="91">
         <f>SUM(G9:G38)</f>
         <v>152</v>
@@ -16211,12 +16221,12 @@
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
       <c r="G40" s="23"/>
-      <c r="H40" s="196" t="s">
+      <c r="H40" s="193" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="133"/>
-      <c r="J40" s="133"/>
-      <c r="K40" s="134"/>
+      <c r="I40" s="134"/>
+      <c r="J40" s="134"/>
+      <c r="K40" s="135"/>
     </row>
     <row r="41" spans="1:11" ht="20.25" customHeight="1">
       <c r="A41" s="1"/>
@@ -16230,12 +16240,12 @@
       <c r="G41" s="26">
         <v>21</v>
       </c>
-      <c r="H41" s="197" t="s">
+      <c r="H41" s="194" t="s">
         <v>17</v>
       </c>
-      <c r="I41" s="126"/>
-      <c r="J41" s="126"/>
-      <c r="K41" s="127"/>
+      <c r="I41" s="125"/>
+      <c r="J41" s="125"/>
+      <c r="K41" s="124"/>
     </row>
     <row r="42" spans="1:11" ht="20.25" customHeight="1">
       <c r="A42" s="1"/>
@@ -16249,10 +16259,10 @@
       <c r="G42" s="27">
         <v>9</v>
       </c>
-      <c r="H42" s="126"/>
-      <c r="I42" s="126"/>
-      <c r="J42" s="126"/>
-      <c r="K42" s="127"/>
+      <c r="H42" s="125"/>
+      <c r="I42" s="125"/>
+      <c r="J42" s="125"/>
+      <c r="K42" s="124"/>
     </row>
     <row r="43" spans="1:11" ht="20.25" customHeight="1">
       <c r="A43" s="1"/>
@@ -16266,10 +16276,10 @@
       <c r="G43" s="27">
         <v>1</v>
       </c>
-      <c r="H43" s="124"/>
-      <c r="I43" s="124"/>
-      <c r="J43" s="124"/>
-      <c r="K43" s="123"/>
+      <c r="H43" s="132"/>
+      <c r="I43" s="132"/>
+      <c r="J43" s="132"/>
+      <c r="K43" s="128"/>
     </row>
     <row r="44" spans="1:11" ht="20.25" customHeight="1">
       <c r="A44" s="1"/>
@@ -16302,7 +16312,7 @@
       <c r="G45" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H45" s="197" t="s">
+      <c r="H45" s="194" t="s">
         <v>23</v>
       </c>
       <c r="I45" s="1"/>
@@ -16321,7 +16331,7 @@
       <c r="G46" s="27">
         <v>19</v>
       </c>
-      <c r="H46" s="124"/>
+      <c r="H46" s="132"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="48"/>
@@ -16342,10 +16352,10 @@
       <c r="H47" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="I47" s="171" t="s">
+      <c r="I47" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="J47" s="172"/>
+      <c r="J47" s="140"/>
       <c r="K47" s="32" t="s">
         <v>28</v>
       </c>
@@ -16363,10 +16373,10 @@
       <c r="H48" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="I48" s="163" t="s">
+      <c r="I48" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="J48" s="127"/>
+      <c r="J48" s="124"/>
       <c r="K48" s="37" t="s">
         <v>29</v>
       </c>
@@ -16386,10 +16396,10 @@
       <c r="H49" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="I49" s="163" t="s">
+      <c r="I49" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="J49" s="127"/>
+      <c r="J49" s="124"/>
       <c r="K49" s="37" t="s">
         <v>31</v>
       </c>
@@ -16410,10 +16420,10 @@
       <c r="H50" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="I50" s="163" t="s">
+      <c r="I50" s="126" t="s">
         <v>33</v>
       </c>
-      <c r="J50" s="127"/>
+      <c r="J50" s="124"/>
       <c r="K50" s="37" t="s">
         <v>33</v>
       </c>
@@ -16434,10 +16444,10 @@
       <c r="H51" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="I51" s="164" t="s">
+      <c r="I51" s="127" t="s">
         <v>35</v>
       </c>
-      <c r="J51" s="123"/>
+      <c r="J51" s="128"/>
       <c r="K51" s="43" t="s">
         <v>35</v>
       </c>
@@ -16460,23 +16470,23 @@
       <c r="B53" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C53" s="161" t="s">
+      <c r="C53" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="D53" s="127"/>
-      <c r="E53" s="161" t="s">
+      <c r="D53" s="124"/>
+      <c r="E53" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="F53" s="126"/>
-      <c r="G53" s="127"/>
-      <c r="H53" s="198" t="s">
+      <c r="F53" s="125"/>
+      <c r="G53" s="124"/>
+      <c r="H53" s="195" t="s">
         <v>38</v>
       </c>
-      <c r="I53" s="127"/>
-      <c r="J53" s="161" t="s">
+      <c r="I53" s="124"/>
+      <c r="J53" s="122" t="s">
         <v>106</v>
       </c>
-      <c r="K53" s="127"/>
+      <c r="K53" s="124"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1">
       <c r="A54" s="1"/>
@@ -16533,42 +16543,42 @@
     <row r="58" spans="1:11" ht="15.75" customHeight="1">
       <c r="A58" s="51"/>
       <c r="B58" s="52"/>
-      <c r="C58" s="125" t="s">
+      <c r="C58" s="170" t="s">
         <v>143</v>
       </c>
-      <c r="D58" s="127"/>
-      <c r="E58" s="125" t="s">
+      <c r="D58" s="124"/>
+      <c r="E58" s="170" t="s">
         <v>108</v>
       </c>
-      <c r="F58" s="126"/>
-      <c r="G58" s="127"/>
-      <c r="H58" s="194" t="s">
+      <c r="F58" s="125"/>
+      <c r="G58" s="124"/>
+      <c r="H58" s="196" t="s">
         <v>109</v>
       </c>
-      <c r="I58" s="127"/>
-      <c r="J58" s="125" t="s">
+      <c r="I58" s="124"/>
+      <c r="J58" s="170" t="s">
         <v>110</v>
       </c>
-      <c r="K58" s="127"/>
+      <c r="K58" s="124"/>
     </row>
     <row r="59" spans="1:11" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="53"/>
-      <c r="C59" s="122"/>
-      <c r="D59" s="123"/>
-      <c r="E59" s="122" t="s">
+      <c r="C59" s="169"/>
+      <c r="D59" s="128"/>
+      <c r="E59" s="169" t="s">
         <v>111</v>
       </c>
-      <c r="F59" s="124"/>
-      <c r="G59" s="123"/>
-      <c r="H59" s="195" t="s">
+      <c r="F59" s="132"/>
+      <c r="G59" s="128"/>
+      <c r="H59" s="197" t="s">
         <v>112</v>
       </c>
-      <c r="I59" s="123"/>
-      <c r="J59" s="122" t="s">
+      <c r="I59" s="128"/>
+      <c r="J59" s="169" t="s">
         <v>113</v>
       </c>
-      <c r="K59" s="123"/>
+      <c r="K59" s="128"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
@@ -19913,11 +19923,54 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="E2:H3"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="J59:K59"/>
     <mergeCell ref="H40:K40"/>
     <mergeCell ref="H41:K43"/>
     <mergeCell ref="E53:G53"/>
@@ -19929,54 +19982,11 @@
     <mergeCell ref="I49:J49"/>
     <mergeCell ref="I50:J50"/>
     <mergeCell ref="I51:J51"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B2:D5"/>
-    <mergeCell ref="E2:H3"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="B39:F39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>

--- a/TimesheetBankJakarta_Anggit_Ari_Utomo_2.xlsx
+++ b/TimesheetBankJakarta_Anggit_Ari_Utomo_2.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -2495,62 +2495,29 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2561,11 +2528,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2636,17 +2612,68 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2678,35 +2705,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2717,17 +2726,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5451,137 +5451,137 @@
     </row>
     <row r="2" spans="1:12" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="145"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="143" t="s">
+      <c r="B2" s="136"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="148"/>
-      <c r="J2" s="151" t="s">
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="134"/>
-      <c r="L2" s="135"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="134"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="147"/>
-      <c r="H3" s="147"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="147"/>
-      <c r="K3" s="147"/>
-      <c r="L3" s="152"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="139"/>
+      <c r="H3" s="139"/>
+      <c r="I3" s="142"/>
+      <c r="J3" s="139"/>
+      <c r="K3" s="139"/>
+      <c r="L3" s="144"/>
     </row>
     <row r="4" spans="1:12" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="153" t="s">
+      <c r="B4" s="137"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="145" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="154"/>
-      <c r="G4" s="154"/>
-      <c r="H4" s="154"/>
-      <c r="I4" s="155"/>
-      <c r="J4" s="156" t="s">
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="148" t="s">
         <v>152</v>
       </c>
-      <c r="K4" s="157"/>
-      <c r="L4" s="158"/>
+      <c r="K4" s="149"/>
+      <c r="L4" s="150"/>
     </row>
     <row r="5" spans="1:12" ht="14.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="146"/>
-      <c r="C5" s="147"/>
-      <c r="D5" s="147"/>
+      <c r="B5" s="138"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="139"/>
       <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="159" t="s">
+      <c r="F5" s="151" t="s">
         <v>146</v>
       </c>
-      <c r="G5" s="154"/>
-      <c r="H5" s="154"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="125"/>
-      <c r="L5" s="124"/>
+      <c r="G5" s="146"/>
+      <c r="H5" s="146"/>
+      <c r="I5" s="147"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="127"/>
     </row>
     <row r="6" spans="1:12" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="162" t="s">
+      <c r="B6" s="154" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="157"/>
-      <c r="D6" s="157"/>
+      <c r="C6" s="149"/>
+      <c r="D6" s="149"/>
       <c r="E6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="160">
+      <c r="F6" s="152">
         <v>0</v>
       </c>
-      <c r="G6" s="157"/>
-      <c r="H6" s="157"/>
-      <c r="I6" s="161"/>
-      <c r="J6" s="125"/>
-      <c r="K6" s="125"/>
-      <c r="L6" s="124"/>
+      <c r="G6" s="149"/>
+      <c r="H6" s="149"/>
+      <c r="I6" s="153"/>
+      <c r="J6" s="126"/>
+      <c r="K6" s="126"/>
+      <c r="L6" s="127"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="163" t="s">
+      <c r="B7" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="165" t="s">
+      <c r="C7" s="157" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="166"/>
-      <c r="E7" s="143" t="s">
+      <c r="D7" s="158"/>
+      <c r="E7" s="132" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="148"/>
-      <c r="G7" s="168" t="s">
+      <c r="F7" s="140"/>
+      <c r="G7" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="141" t="s">
+      <c r="H7" s="130" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="141" t="s">
+      <c r="I7" s="130" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="143" t="s">
+      <c r="J7" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="134"/>
-      <c r="L7" s="135"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="134"/>
     </row>
     <row r="8" spans="1:12" thickBot="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="164"/>
+      <c r="B8" s="156"/>
       <c r="C8" s="8">
         <v>0.33333333333333331</v>
       </c>
       <c r="D8" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="144"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="142"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="142"/>
-      <c r="J8" s="144"/>
-      <c r="K8" s="132"/>
-      <c r="L8" s="128"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="159"/>
+      <c r="G8" s="131"/>
+      <c r="H8" s="131"/>
+      <c r="I8" s="131"/>
+      <c r="J8" s="135"/>
+      <c r="K8" s="124"/>
+      <c r="L8" s="123"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1">
       <c r="A9" s="9"/>
@@ -6412,13 +6412,13 @@
     </row>
     <row r="43" spans="1:12" ht="18" customHeight="1" thickBot="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="136" t="s">
+      <c r="B43" s="168" t="s">
         <v>13</v>
       </c>
-      <c r="C43" s="137"/>
-      <c r="D43" s="137"/>
-      <c r="E43" s="137"/>
-      <c r="F43" s="138"/>
+      <c r="C43" s="169"/>
+      <c r="D43" s="169"/>
+      <c r="E43" s="169"/>
+      <c r="F43" s="170"/>
       <c r="G43" s="18">
         <f>SUM(G9:G39)</f>
         <v>174.5</v>
@@ -6439,13 +6439,13 @@
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
       <c r="G44" s="23"/>
-      <c r="H44" s="133" t="s">
+      <c r="H44" s="167" t="s">
         <v>15</v>
       </c>
-      <c r="I44" s="134"/>
-      <c r="J44" s="134"/>
-      <c r="K44" s="134"/>
-      <c r="L44" s="135"/>
+      <c r="I44" s="133"/>
+      <c r="J44" s="133"/>
+      <c r="K44" s="133"/>
+      <c r="L44" s="134"/>
     </row>
     <row r="45" spans="1:12" ht="20.25" customHeight="1">
       <c r="A45" s="1"/>
@@ -6459,13 +6459,13 @@
       <c r="G45" s="26">
         <v>21</v>
       </c>
-      <c r="H45" s="129" t="s">
+      <c r="H45" s="165" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="125"/>
-      <c r="J45" s="125"/>
-      <c r="K45" s="125"/>
-      <c r="L45" s="124"/>
+      <c r="I45" s="126"/>
+      <c r="J45" s="126"/>
+      <c r="K45" s="126"/>
+      <c r="L45" s="127"/>
     </row>
     <row r="46" spans="1:12" ht="20.25" customHeight="1">
       <c r="A46" s="1"/>
@@ -6479,11 +6479,11 @@
       <c r="G46" s="27">
         <v>0</v>
       </c>
-      <c r="H46" s="130"/>
-      <c r="I46" s="125"/>
-      <c r="J46" s="125"/>
-      <c r="K46" s="125"/>
-      <c r="L46" s="124"/>
+      <c r="H46" s="137"/>
+      <c r="I46" s="126"/>
+      <c r="J46" s="126"/>
+      <c r="K46" s="126"/>
+      <c r="L46" s="127"/>
     </row>
     <row r="47" spans="1:12" ht="20.25" customHeight="1" thickBot="1">
       <c r="A47" s="1"/>
@@ -6497,11 +6497,11 @@
       <c r="G47" s="27">
         <v>0</v>
       </c>
-      <c r="H47" s="131"/>
-      <c r="I47" s="132"/>
-      <c r="J47" s="132"/>
-      <c r="K47" s="132"/>
-      <c r="L47" s="128"/>
+      <c r="H47" s="166"/>
+      <c r="I47" s="124"/>
+      <c r="J47" s="124"/>
+      <c r="K47" s="124"/>
+      <c r="L47" s="123"/>
     </row>
     <row r="48" spans="1:12" ht="20.25" customHeight="1">
       <c r="A48" s="1"/>
@@ -6515,13 +6515,13 @@
       <c r="G48" s="27">
         <v>0</v>
       </c>
-      <c r="H48" s="133" t="s">
+      <c r="H48" s="167" t="s">
         <v>21</v>
       </c>
-      <c r="I48" s="134"/>
-      <c r="J48" s="134"/>
-      <c r="K48" s="134"/>
-      <c r="L48" s="135"/>
+      <c r="I48" s="133"/>
+      <c r="J48" s="133"/>
+      <c r="K48" s="133"/>
+      <c r="L48" s="134"/>
     </row>
     <row r="49" spans="1:12" ht="20.25" customHeight="1">
       <c r="A49" s="1"/>
@@ -6535,13 +6535,13 @@
       <c r="G49" s="27">
         <v>0</v>
       </c>
-      <c r="H49" s="122" t="s">
+      <c r="H49" s="161" t="s">
         <v>23</v>
       </c>
-      <c r="I49" s="125"/>
-      <c r="J49" s="125"/>
-      <c r="K49" s="125"/>
-      <c r="L49" s="124"/>
+      <c r="I49" s="126"/>
+      <c r="J49" s="126"/>
+      <c r="K49" s="126"/>
+      <c r="L49" s="127"/>
     </row>
     <row r="50" spans="1:12" ht="20.25" customHeight="1" thickBot="1">
       <c r="A50" s="1"/>
@@ -6555,11 +6555,11 @@
       <c r="G50" s="27">
         <v>22</v>
       </c>
-      <c r="H50" s="131"/>
-      <c r="I50" s="132"/>
-      <c r="J50" s="132"/>
-      <c r="K50" s="132"/>
-      <c r="L50" s="128"/>
+      <c r="H50" s="166"/>
+      <c r="I50" s="124"/>
+      <c r="J50" s="124"/>
+      <c r="K50" s="124"/>
+      <c r="L50" s="123"/>
     </row>
     <row r="51" spans="1:12" ht="24" customHeight="1" thickBot="1">
       <c r="A51" s="1"/>
@@ -6578,10 +6578,10 @@
         <v>26</v>
       </c>
       <c r="I51" s="31"/>
-      <c r="J51" s="139" t="s">
+      <c r="J51" s="171" t="s">
         <v>27</v>
       </c>
-      <c r="K51" s="140"/>
+      <c r="K51" s="172"/>
       <c r="L51" s="32" t="s">
         <v>28</v>
       </c>
@@ -6600,10 +6600,10 @@
         <v>29</v>
       </c>
       <c r="I52" s="36"/>
-      <c r="J52" s="126" t="s">
+      <c r="J52" s="163" t="s">
         <v>29</v>
       </c>
-      <c r="K52" s="124"/>
+      <c r="K52" s="127"/>
       <c r="L52" s="37" t="s">
         <v>29</v>
       </c>
@@ -6625,10 +6625,10 @@
         <v>31</v>
       </c>
       <c r="I53" s="36"/>
-      <c r="J53" s="126" t="s">
+      <c r="J53" s="163" t="s">
         <v>31</v>
       </c>
-      <c r="K53" s="124"/>
+      <c r="K53" s="127"/>
       <c r="L53" s="37" t="s">
         <v>31</v>
       </c>
@@ -6650,10 +6650,10 @@
         <v>33</v>
       </c>
       <c r="I54" s="36"/>
-      <c r="J54" s="126" t="s">
+      <c r="J54" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="K54" s="124"/>
+      <c r="K54" s="127"/>
       <c r="L54" s="37" t="s">
         <v>33</v>
       </c>
@@ -6675,10 +6675,10 @@
         <v>35</v>
       </c>
       <c r="I55" s="42"/>
-      <c r="J55" s="127" t="s">
+      <c r="J55" s="164" t="s">
         <v>35</v>
       </c>
-      <c r="K55" s="128"/>
+      <c r="K55" s="123"/>
       <c r="L55" s="43" t="s">
         <v>35</v>
       </c>
@@ -6700,32 +6700,32 @@
     <row r="57" spans="1:12" ht="15.75" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="28"/>
-      <c r="C57" s="122" t="s">
+      <c r="C57" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="D57" s="124"/>
-      <c r="E57" s="122" t="s">
+      <c r="D57" s="127"/>
+      <c r="E57" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="F57" s="125"/>
-      <c r="G57" s="124"/>
-      <c r="H57" s="122" t="s">
+      <c r="F57" s="126"/>
+      <c r="G57" s="127"/>
+      <c r="H57" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="I57" s="125"/>
-      <c r="J57" s="124"/>
-      <c r="K57" s="122" t="s">
+      <c r="I57" s="126"/>
+      <c r="J57" s="127"/>
+      <c r="K57" s="161" t="s">
         <v>39</v>
       </c>
-      <c r="L57" s="124"/>
+      <c r="L57" s="127"/>
     </row>
     <row r="58" spans="1:12" ht="15.75" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="122"/>
-      <c r="D58" s="123"/>
+      <c r="C58" s="161"/>
+      <c r="D58" s="162"/>
       <c r="E58" s="47"/>
       <c r="F58" s="1"/>
       <c r="G58" s="48"/>
@@ -6740,8 +6740,8 @@
       <c r="B59" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="C59" s="122"/>
-      <c r="D59" s="123"/>
+      <c r="C59" s="161"/>
+      <c r="D59" s="162"/>
       <c r="E59" s="47"/>
       <c r="F59" s="1"/>
       <c r="G59" s="48"/>
@@ -6756,8 +6756,8 @@
       <c r="B60" s="50">
         <v>46257</v>
       </c>
-      <c r="C60" s="122"/>
-      <c r="D60" s="123"/>
+      <c r="C60" s="161"/>
+      <c r="D60" s="162"/>
       <c r="E60" s="47"/>
       <c r="F60" s="1"/>
       <c r="G60" s="48"/>
@@ -6770,8 +6770,8 @@
     <row r="61" spans="1:12" ht="15.75" customHeight="1">
       <c r="A61" s="51"/>
       <c r="B61" s="47"/>
-      <c r="C61" s="122"/>
-      <c r="D61" s="123"/>
+      <c r="C61" s="161"/>
+      <c r="D61" s="162"/>
       <c r="E61" s="47"/>
       <c r="F61" s="1"/>
       <c r="G61" s="48"/>
@@ -6784,44 +6784,44 @@
     <row r="62" spans="1:12" ht="15.75" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="52"/>
-      <c r="C62" s="172" t="s">
+      <c r="C62" s="129" t="s">
         <v>151</v>
       </c>
-      <c r="D62" s="124"/>
-      <c r="E62" s="170" t="s">
+      <c r="D62" s="127"/>
+      <c r="E62" s="125" t="s">
         <v>41</v>
       </c>
-      <c r="F62" s="125"/>
-      <c r="G62" s="124"/>
-      <c r="H62" s="171" t="s">
+      <c r="F62" s="126"/>
+      <c r="G62" s="127"/>
+      <c r="H62" s="128" t="s">
         <v>145</v>
       </c>
-      <c r="I62" s="125"/>
-      <c r="J62" s="124"/>
-      <c r="K62" s="170" t="s">
+      <c r="I62" s="126"/>
+      <c r="J62" s="127"/>
+      <c r="K62" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="L62" s="124"/>
+      <c r="L62" s="127"/>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A63" s="1"/>
       <c r="B63" s="53"/>
-      <c r="C63" s="169"/>
-      <c r="D63" s="128"/>
-      <c r="E63" s="169" t="s">
+      <c r="C63" s="122"/>
+      <c r="D63" s="123"/>
+      <c r="E63" s="122" t="s">
         <v>43</v>
       </c>
-      <c r="F63" s="132"/>
-      <c r="G63" s="128"/>
-      <c r="H63" s="169" t="s">
+      <c r="F63" s="124"/>
+      <c r="G63" s="123"/>
+      <c r="H63" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="I63" s="132"/>
-      <c r="J63" s="128"/>
-      <c r="K63" s="169" t="s">
+      <c r="I63" s="124"/>
+      <c r="J63" s="123"/>
+      <c r="K63" s="122" t="s">
         <v>45</v>
       </c>
-      <c r="L63" s="128"/>
+      <c r="L63" s="123"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1">
       <c r="A64" s="1"/>
@@ -10361,32 +10361,22 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="H63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="C58:D61"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="H57:J57"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="H45:L47"/>
+    <mergeCell ref="H48:L48"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="H49:L50"/>
+    <mergeCell ref="H44:L44"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="J7:L8"/>
@@ -10403,22 +10393,32 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F8"/>
     <mergeCell ref="G7:G8"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="C58:D61"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="H57:J57"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="H45:L47"/>
-    <mergeCell ref="H48:L48"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="H49:L50"/>
-    <mergeCell ref="H44:L44"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="H63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="J21:L21"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.19685039370078741" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="81" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -10461,128 +10461,128 @@
     </row>
     <row r="2" spans="1:11" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="145"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="148"/>
-      <c r="E2" s="143" t="s">
+      <c r="B2" s="136"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="143" t="s">
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="134"/>
-      <c r="K2" s="135"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="134"/>
     </row>
     <row r="3" spans="1:11" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="147"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="149"/>
-      <c r="J3" s="147"/>
-      <c r="K3" s="152"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="139"/>
+      <c r="H3" s="142"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="139"/>
+      <c r="K3" s="144"/>
     </row>
     <row r="4" spans="1:11" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="153" t="s">
+      <c r="B4" s="137"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="182"/>
+      <c r="E4" s="145" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="154"/>
-      <c r="G4" s="154"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="174" t="s">
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="183" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="157"/>
-      <c r="K4" s="158"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="150"/>
     </row>
     <row r="5" spans="1:11" ht="14.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="146"/>
-      <c r="C5" s="147"/>
-      <c r="D5" s="150"/>
+      <c r="B5" s="138"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="142"/>
       <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="159" t="s">
+      <c r="F5" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="154"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="124"/>
+      <c r="G5" s="146"/>
+      <c r="H5" s="147"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="127"/>
     </row>
     <row r="6" spans="1:11" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="179" t="s">
+      <c r="B6" s="188" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="177"/>
-      <c r="D6" s="178"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="187"/>
       <c r="E6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="176">
+      <c r="F6" s="185">
         <v>20230682322</v>
       </c>
-      <c r="G6" s="177"/>
-      <c r="H6" s="178"/>
-      <c r="I6" s="144"/>
-      <c r="J6" s="132"/>
-      <c r="K6" s="128"/>
+      <c r="G6" s="186"/>
+      <c r="H6" s="187"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="124"/>
+      <c r="K6" s="123"/>
     </row>
     <row r="7" spans="1:11" ht="14.4">
       <c r="A7" s="1"/>
-      <c r="B7" s="163" t="s">
+      <c r="B7" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="165" t="s">
+      <c r="C7" s="157" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="166"/>
-      <c r="E7" s="145" t="s">
+      <c r="D7" s="158"/>
+      <c r="E7" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="135"/>
-      <c r="G7" s="180" t="s">
+      <c r="F7" s="134"/>
+      <c r="G7" s="189" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="181" t="s">
+      <c r="H7" s="190" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="151" t="s">
+      <c r="I7" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="134"/>
-      <c r="K7" s="135"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="134"/>
     </row>
     <row r="8" spans="1:11" ht="14.4">
       <c r="A8" s="1"/>
-      <c r="B8" s="164"/>
+      <c r="B8" s="156"/>
       <c r="C8" s="8">
         <v>0.33333333333333331</v>
       </c>
       <c r="D8" s="55">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="131"/>
-      <c r="F8" s="128"/>
-      <c r="G8" s="132"/>
-      <c r="H8" s="182"/>
-      <c r="I8" s="132"/>
-      <c r="J8" s="132"/>
-      <c r="K8" s="128"/>
+      <c r="E8" s="166"/>
+      <c r="F8" s="123"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="191"/>
+      <c r="I8" s="124"/>
+      <c r="J8" s="124"/>
+      <c r="K8" s="123"/>
     </row>
     <row r="9" spans="1:11" ht="14.4">
       <c r="A9" s="2"/>
@@ -10607,11 +10607,11 @@
       <c r="H9" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="183" t="s">
+      <c r="I9" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="154"/>
-      <c r="K9" s="184"/>
+      <c r="J9" s="146"/>
+      <c r="K9" s="178"/>
     </row>
     <row r="10" spans="1:11" ht="14.4">
       <c r="A10" s="9"/>
@@ -10636,11 +10636,11 @@
       <c r="H10" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="183" t="s">
+      <c r="I10" s="177" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="154"/>
-      <c r="K10" s="184"/>
+      <c r="J10" s="146"/>
+      <c r="K10" s="178"/>
     </row>
     <row r="11" spans="1:11" ht="14.4">
       <c r="A11" s="2"/>
@@ -10665,11 +10665,11 @@
       <c r="H11" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I11" s="183" t="s">
+      <c r="I11" s="177" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="154"/>
-      <c r="K11" s="184"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="178"/>
     </row>
     <row r="12" spans="1:11" ht="14.4">
       <c r="A12" s="2"/>
@@ -10688,9 +10688,9 @@
         <v>0</v>
       </c>
       <c r="H12" s="13"/>
-      <c r="I12" s="183"/>
-      <c r="J12" s="154"/>
-      <c r="K12" s="184"/>
+      <c r="I12" s="177"/>
+      <c r="J12" s="146"/>
+      <c r="K12" s="178"/>
     </row>
     <row r="13" spans="1:11" ht="14.4">
       <c r="A13" s="2"/>
@@ -10709,9 +10709,9 @@
         <v>0</v>
       </c>
       <c r="H13" s="13"/>
-      <c r="I13" s="183"/>
-      <c r="J13" s="154"/>
-      <c r="K13" s="184"/>
+      <c r="I13" s="177"/>
+      <c r="J13" s="146"/>
+      <c r="K13" s="178"/>
     </row>
     <row r="14" spans="1:11" ht="14.4">
       <c r="A14" s="2"/>
@@ -10736,11 +10736,11 @@
       <c r="H14" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I14" s="183" t="s">
+      <c r="I14" s="177" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="154"/>
-      <c r="K14" s="184"/>
+      <c r="J14" s="146"/>
+      <c r="K14" s="178"/>
     </row>
     <row r="15" spans="1:11" ht="14.4">
       <c r="A15" s="2"/>
@@ -10765,11 +10765,11 @@
       <c r="H15" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="183" t="s">
+      <c r="I15" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="154"/>
-      <c r="K15" s="184"/>
+      <c r="J15" s="146"/>
+      <c r="K15" s="178"/>
     </row>
     <row r="16" spans="1:11" ht="14.4">
       <c r="A16" s="2"/>
@@ -10788,9 +10788,9 @@
         <v>0</v>
       </c>
       <c r="H16" s="11"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="154"/>
-      <c r="K16" s="184"/>
+      <c r="I16" s="181"/>
+      <c r="J16" s="146"/>
+      <c r="K16" s="178"/>
     </row>
     <row r="17" spans="1:11" ht="14.4">
       <c r="A17" s="2"/>
@@ -10815,11 +10815,11 @@
       <c r="H17" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="183" t="s">
+      <c r="I17" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="J17" s="154"/>
-      <c r="K17" s="184"/>
+      <c r="J17" s="146"/>
+      <c r="K17" s="178"/>
     </row>
     <row r="18" spans="1:11" ht="14.4">
       <c r="A18" s="2"/>
@@ -10844,11 +10844,11 @@
       <c r="H18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="183" t="s">
+      <c r="I18" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="J18" s="154"/>
-      <c r="K18" s="184"/>
+      <c r="J18" s="146"/>
+      <c r="K18" s="178"/>
     </row>
     <row r="19" spans="1:11" ht="14.4">
       <c r="A19" s="2"/>
@@ -10867,9 +10867,9 @@
         <v>0</v>
       </c>
       <c r="H19" s="11"/>
-      <c r="I19" s="185"/>
-      <c r="J19" s="154"/>
-      <c r="K19" s="184"/>
+      <c r="I19" s="181"/>
+      <c r="J19" s="146"/>
+      <c r="K19" s="178"/>
     </row>
     <row r="20" spans="1:11" ht="14.4">
       <c r="A20" s="2"/>
@@ -10888,9 +10888,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="11"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="154"/>
-      <c r="K20" s="184"/>
+      <c r="I20" s="181"/>
+      <c r="J20" s="146"/>
+      <c r="K20" s="178"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1">
       <c r="A21" s="2"/>
@@ -10915,11 +10915,11 @@
       <c r="H21" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I21" s="183" t="s">
+      <c r="I21" s="177" t="s">
         <v>68</v>
       </c>
-      <c r="J21" s="154"/>
-      <c r="K21" s="184"/>
+      <c r="J21" s="146"/>
+      <c r="K21" s="178"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
       <c r="A22" s="2"/>
@@ -10944,11 +10944,11 @@
       <c r="H22" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="183" t="s">
+      <c r="I22" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="154"/>
-      <c r="K22" s="184"/>
+      <c r="J22" s="146"/>
+      <c r="K22" s="178"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
       <c r="A23" s="2"/>
@@ -10973,11 +10973,11 @@
       <c r="H23" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="183" t="s">
+      <c r="I23" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="154"/>
-      <c r="K23" s="184"/>
+      <c r="J23" s="146"/>
+      <c r="K23" s="178"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="2"/>
@@ -11002,11 +11002,11 @@
       <c r="H24" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="183" t="s">
+      <c r="I24" s="177" t="s">
         <v>72</v>
       </c>
-      <c r="J24" s="154"/>
-      <c r="K24" s="184"/>
+      <c r="J24" s="146"/>
+      <c r="K24" s="178"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1">
       <c r="A25" s="2"/>
@@ -11031,11 +11031,11 @@
       <c r="H25" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="183" t="s">
+      <c r="I25" s="177" t="s">
         <v>74</v>
       </c>
-      <c r="J25" s="154"/>
-      <c r="K25" s="184"/>
+      <c r="J25" s="146"/>
+      <c r="K25" s="178"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1">
       <c r="A26" s="2"/>
@@ -11054,9 +11054,9 @@
         <v>0</v>
       </c>
       <c r="H26" s="11"/>
-      <c r="I26" s="185"/>
-      <c r="J26" s="154"/>
-      <c r="K26" s="184"/>
+      <c r="I26" s="181"/>
+      <c r="J26" s="146"/>
+      <c r="K26" s="178"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
       <c r="A27" s="2"/>
@@ -11075,9 +11075,9 @@
         <v>0</v>
       </c>
       <c r="H27" s="11"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="154"/>
-      <c r="K27" s="184"/>
+      <c r="I27" s="181"/>
+      <c r="J27" s="146"/>
+      <c r="K27" s="178"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1">
       <c r="A28" s="2"/>
@@ -11102,11 +11102,11 @@
       <c r="H28" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I28" s="183" t="s">
+      <c r="I28" s="177" t="s">
         <v>78</v>
       </c>
-      <c r="J28" s="154"/>
-      <c r="K28" s="184"/>
+      <c r="J28" s="146"/>
+      <c r="K28" s="178"/>
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1">
       <c r="A29" s="2"/>
@@ -11131,11 +11131,11 @@
       <c r="H29" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="183" t="s">
+      <c r="I29" s="177" t="s">
         <v>80</v>
       </c>
-      <c r="J29" s="154"/>
-      <c r="K29" s="184"/>
+      <c r="J29" s="146"/>
+      <c r="K29" s="178"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="2"/>
@@ -11160,11 +11160,11 @@
       <c r="H30" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I30" s="183" t="s">
+      <c r="I30" s="177" t="s">
         <v>82</v>
       </c>
-      <c r="J30" s="154"/>
-      <c r="K30" s="184"/>
+      <c r="J30" s="146"/>
+      <c r="K30" s="178"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1">
       <c r="A31" s="2"/>
@@ -11189,11 +11189,11 @@
       <c r="H31" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I31" s="183" t="s">
+      <c r="I31" s="177" t="s">
         <v>84</v>
       </c>
-      <c r="J31" s="154"/>
-      <c r="K31" s="184"/>
+      <c r="J31" s="146"/>
+      <c r="K31" s="178"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="2"/>
@@ -11218,11 +11218,11 @@
       <c r="H32" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I32" s="183" t="s">
+      <c r="I32" s="177" t="s">
         <v>86</v>
       </c>
-      <c r="J32" s="154"/>
-      <c r="K32" s="184"/>
+      <c r="J32" s="146"/>
+      <c r="K32" s="178"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1">
       <c r="A33" s="2"/>
@@ -11241,9 +11241,9 @@
         <v>0</v>
       </c>
       <c r="H33" s="11"/>
-      <c r="I33" s="185"/>
-      <c r="J33" s="154"/>
-      <c r="K33" s="184"/>
+      <c r="I33" s="181"/>
+      <c r="J33" s="146"/>
+      <c r="K33" s="178"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1">
       <c r="A34" s="2"/>
@@ -11262,9 +11262,9 @@
         <v>0</v>
       </c>
       <c r="H34" s="11"/>
-      <c r="I34" s="185"/>
-      <c r="J34" s="154"/>
-      <c r="K34" s="184"/>
+      <c r="I34" s="181"/>
+      <c r="J34" s="146"/>
+      <c r="K34" s="178"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1">
       <c r="A35" s="2"/>
@@ -11289,11 +11289,11 @@
       <c r="H35" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I35" s="183" t="s">
+      <c r="I35" s="177" t="s">
         <v>90</v>
       </c>
-      <c r="J35" s="154"/>
-      <c r="K35" s="184"/>
+      <c r="J35" s="146"/>
+      <c r="K35" s="178"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1">
       <c r="A36" s="2"/>
@@ -11318,11 +11318,11 @@
       <c r="H36" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I36" s="183" t="s">
+      <c r="I36" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="J36" s="154"/>
-      <c r="K36" s="184"/>
+      <c r="J36" s="146"/>
+      <c r="K36" s="178"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1">
       <c r="A37" s="2"/>
@@ -11347,11 +11347,11 @@
       <c r="H37" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I37" s="183" t="s">
+      <c r="I37" s="177" t="s">
         <v>68</v>
       </c>
-      <c r="J37" s="154"/>
-      <c r="K37" s="184"/>
+      <c r="J37" s="146"/>
+      <c r="K37" s="178"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1">
       <c r="A38" s="2"/>
@@ -11376,11 +11376,11 @@
       <c r="H38" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I38" s="183" t="s">
+      <c r="I38" s="177" t="s">
         <v>94</v>
       </c>
-      <c r="J38" s="154"/>
-      <c r="K38" s="184"/>
+      <c r="J38" s="146"/>
+      <c r="K38" s="178"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1">
       <c r="A39" s="2"/>
@@ -11405,21 +11405,21 @@
       <c r="H39" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I39" s="187" t="s">
+      <c r="I39" s="180" t="s">
         <v>94</v>
       </c>
-      <c r="J39" s="157"/>
-      <c r="K39" s="158"/>
+      <c r="J39" s="149"/>
+      <c r="K39" s="150"/>
     </row>
     <row r="40" spans="1:11" ht="18" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="136" t="s">
+      <c r="B40" s="168" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="188"/>
-      <c r="D40" s="188"/>
-      <c r="E40" s="188"/>
-      <c r="F40" s="189"/>
+      <c r="C40" s="173"/>
+      <c r="D40" s="173"/>
+      <c r="E40" s="173"/>
+      <c r="F40" s="174"/>
       <c r="G40" s="18">
         <f>SUM(G9:G39)</f>
         <v>176</v>
@@ -11439,12 +11439,12 @@
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
       <c r="G41" s="23"/>
-      <c r="H41" s="190" t="s">
+      <c r="H41" s="175" t="s">
         <v>15</v>
       </c>
-      <c r="I41" s="134"/>
-      <c r="J41" s="134"/>
-      <c r="K41" s="135"/>
+      <c r="I41" s="133"/>
+      <c r="J41" s="133"/>
+      <c r="K41" s="134"/>
     </row>
     <row r="42" spans="1:11" ht="20.25" customHeight="1">
       <c r="A42" s="1"/>
@@ -11458,12 +11458,12 @@
       <c r="G42" s="26">
         <v>22</v>
       </c>
-      <c r="H42" s="191" t="s">
+      <c r="H42" s="176" t="s">
         <v>17</v>
       </c>
-      <c r="I42" s="125"/>
-      <c r="J42" s="125"/>
-      <c r="K42" s="124"/>
+      <c r="I42" s="126"/>
+      <c r="J42" s="126"/>
+      <c r="K42" s="127"/>
     </row>
     <row r="43" spans="1:11" ht="20.25" customHeight="1">
       <c r="A43" s="1"/>
@@ -11477,10 +11477,10 @@
       <c r="G43" s="27">
         <v>9</v>
       </c>
-      <c r="H43" s="125"/>
-      <c r="I43" s="125"/>
-      <c r="J43" s="125"/>
-      <c r="K43" s="124"/>
+      <c r="H43" s="126"/>
+      <c r="I43" s="126"/>
+      <c r="J43" s="126"/>
+      <c r="K43" s="127"/>
     </row>
     <row r="44" spans="1:11" ht="20.25" customHeight="1">
       <c r="A44" s="1"/>
@@ -11494,10 +11494,10 @@
       <c r="G44" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H44" s="132"/>
-      <c r="I44" s="132"/>
-      <c r="J44" s="132"/>
-      <c r="K44" s="128"/>
+      <c r="H44" s="124"/>
+      <c r="I44" s="124"/>
+      <c r="J44" s="124"/>
+      <c r="K44" s="123"/>
     </row>
     <row r="45" spans="1:11" ht="20.25" customHeight="1">
       <c r="A45" s="1"/>
@@ -11530,7 +11530,7 @@
       <c r="G46" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H46" s="186" t="s">
+      <c r="H46" s="179" t="s">
         <v>23</v>
       </c>
       <c r="I46" s="1"/>
@@ -11549,7 +11549,7 @@
       <c r="G47" s="27">
         <v>22</v>
       </c>
-      <c r="H47" s="132"/>
+      <c r="H47" s="124"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="48"/>
@@ -11570,10 +11570,10 @@
       <c r="H48" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="I48" s="139" t="s">
+      <c r="I48" s="171" t="s">
         <v>27</v>
       </c>
-      <c r="J48" s="140"/>
+      <c r="J48" s="172"/>
       <c r="K48" s="32" t="s">
         <v>28</v>
       </c>
@@ -11591,10 +11591,10 @@
       <c r="H49" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="I49" s="126" t="s">
+      <c r="I49" s="163" t="s">
         <v>29</v>
       </c>
-      <c r="J49" s="124"/>
+      <c r="J49" s="127"/>
       <c r="K49" s="37" t="s">
         <v>29</v>
       </c>
@@ -11615,10 +11615,10 @@
       <c r="H50" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="I50" s="126" t="s">
+      <c r="I50" s="163" t="s">
         <v>31</v>
       </c>
-      <c r="J50" s="124"/>
+      <c r="J50" s="127"/>
       <c r="K50" s="37" t="s">
         <v>31</v>
       </c>
@@ -11639,10 +11639,10 @@
       <c r="H51" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I51" s="126" t="s">
+      <c r="I51" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="124"/>
+      <c r="J51" s="127"/>
       <c r="K51" s="37" t="s">
         <v>33</v>
       </c>
@@ -11663,10 +11663,10 @@
       <c r="H52" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="I52" s="127" t="s">
+      <c r="I52" s="164" t="s">
         <v>35</v>
       </c>
-      <c r="J52" s="128"/>
+      <c r="J52" s="123"/>
       <c r="K52" s="43" t="s">
         <v>35</v>
       </c>
@@ -11689,23 +11689,23 @@
       <c r="B54" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="122" t="s">
+      <c r="C54" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="D54" s="124"/>
-      <c r="E54" s="122" t="s">
+      <c r="D54" s="127"/>
+      <c r="E54" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="F54" s="125"/>
-      <c r="G54" s="124"/>
-      <c r="H54" s="122" t="s">
+      <c r="F54" s="126"/>
+      <c r="G54" s="127"/>
+      <c r="H54" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="I54" s="124"/>
-      <c r="J54" s="122" t="s">
+      <c r="I54" s="127"/>
+      <c r="J54" s="161" t="s">
         <v>106</v>
       </c>
-      <c r="K54" s="124"/>
+      <c r="K54" s="127"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1">
       <c r="A55" s="1"/>
@@ -11762,42 +11762,42 @@
     <row r="59" spans="1:11" ht="15.75" customHeight="1">
       <c r="A59" s="51"/>
       <c r="B59" s="52"/>
-      <c r="C59" s="170" t="s">
+      <c r="C59" s="125" t="s">
         <v>107</v>
       </c>
-      <c r="D59" s="124"/>
-      <c r="E59" s="170" t="s">
+      <c r="D59" s="127"/>
+      <c r="E59" s="125" t="s">
         <v>108</v>
       </c>
-      <c r="F59" s="125"/>
-      <c r="G59" s="124"/>
-      <c r="H59" s="170" t="s">
+      <c r="F59" s="126"/>
+      <c r="G59" s="127"/>
+      <c r="H59" s="125" t="s">
         <v>109</v>
       </c>
-      <c r="I59" s="124"/>
-      <c r="J59" s="170" t="s">
+      <c r="I59" s="127"/>
+      <c r="J59" s="125" t="s">
         <v>110</v>
       </c>
-      <c r="K59" s="124"/>
+      <c r="K59" s="127"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="53"/>
-      <c r="C60" s="169"/>
-      <c r="D60" s="128"/>
-      <c r="E60" s="169" t="s">
+      <c r="C60" s="122"/>
+      <c r="D60" s="123"/>
+      <c r="E60" s="122" t="s">
         <v>111</v>
       </c>
-      <c r="F60" s="132"/>
-      <c r="G60" s="128"/>
-      <c r="H60" s="169" t="s">
+      <c r="F60" s="124"/>
+      <c r="G60" s="123"/>
+      <c r="H60" s="122" t="s">
         <v>112</v>
       </c>
-      <c r="I60" s="128"/>
-      <c r="J60" s="169" t="s">
+      <c r="I60" s="123"/>
+      <c r="J60" s="122" t="s">
         <v>113</v>
       </c>
-      <c r="K60" s="128"/>
+      <c r="K60" s="123"/>
     </row>
     <row r="61" spans="1:11" ht="15.75" customHeight="1">
       <c r="A61" s="1"/>
@@ -15141,40 +15141,22 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="H42:K44"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:G60"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="H59:I59"/>
     <mergeCell ref="J59:K59"/>
     <mergeCell ref="B2:D5"/>
     <mergeCell ref="E2:H3"/>
@@ -15191,22 +15173,40 @@
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:K8"/>
     <mergeCell ref="I9:K9"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:G60"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="H42:K44"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I37:K37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -15250,56 +15250,56 @@
     </row>
     <row r="2" spans="1:11" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="145"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="148"/>
-      <c r="E2" s="143" t="s">
+      <c r="B2" s="136"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="143" t="s">
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="134"/>
-      <c r="K2" s="135"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="134"/>
     </row>
     <row r="3" spans="1:11" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="147"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="149"/>
-      <c r="J3" s="147"/>
-      <c r="K3" s="152"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="139"/>
+      <c r="H3" s="142"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="139"/>
+      <c r="K3" s="144"/>
     </row>
     <row r="4" spans="1:11" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="153" t="s">
+      <c r="B4" s="137"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="182"/>
+      <c r="E4" s="145" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="154"/>
-      <c r="G4" s="154"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="174" t="s">
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="J4" s="157"/>
-      <c r="K4" s="158"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="150"/>
     </row>
     <row r="5" spans="1:11" ht="14.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="146"/>
-      <c r="C5" s="147"/>
-      <c r="D5" s="150"/>
+      <c r="B5" s="138"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="142"/>
       <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
@@ -15308,70 +15308,70 @@
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="83"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="124"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="127"/>
     </row>
     <row r="6" spans="1:11" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="179" t="s">
+      <c r="B6" s="188" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="177"/>
-      <c r="D6" s="178"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="187"/>
       <c r="E6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="176">
+      <c r="F6" s="185">
         <v>20230682322</v>
       </c>
-      <c r="G6" s="177"/>
-      <c r="H6" s="178"/>
-      <c r="I6" s="144"/>
-      <c r="J6" s="132"/>
-      <c r="K6" s="128"/>
+      <c r="G6" s="186"/>
+      <c r="H6" s="187"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="124"/>
+      <c r="K6" s="123"/>
     </row>
     <row r="7" spans="1:11" ht="14.4">
       <c r="A7" s="1"/>
-      <c r="B7" s="163" t="s">
+      <c r="B7" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="165" t="s">
+      <c r="C7" s="157" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="166"/>
-      <c r="E7" s="145" t="s">
+      <c r="D7" s="158"/>
+      <c r="E7" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="135"/>
-      <c r="G7" s="180" t="s">
+      <c r="F7" s="134"/>
+      <c r="G7" s="189" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="198" t="s">
+      <c r="H7" s="193" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="151" t="s">
+      <c r="I7" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="134"/>
-      <c r="K7" s="135"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="134"/>
     </row>
     <row r="8" spans="1:11" ht="14.4">
       <c r="A8" s="1"/>
-      <c r="B8" s="164"/>
+      <c r="B8" s="156"/>
       <c r="C8" s="8">
         <v>0.33333333333333331</v>
       </c>
       <c r="D8" s="55">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="131"/>
-      <c r="F8" s="128"/>
-      <c r="G8" s="132"/>
-      <c r="H8" s="182"/>
-      <c r="I8" s="132"/>
-      <c r="J8" s="132"/>
-      <c r="K8" s="128"/>
+      <c r="E8" s="166"/>
+      <c r="F8" s="123"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="191"/>
+      <c r="I8" s="124"/>
+      <c r="J8" s="124"/>
+      <c r="K8" s="123"/>
     </row>
     <row r="9" spans="1:11" ht="14.4">
       <c r="A9" s="1"/>
@@ -15397,11 +15397,11 @@
       <c r="H9" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I9" s="185" t="s">
+      <c r="I9" s="181" t="s">
         <v>117</v>
       </c>
-      <c r="J9" s="154"/>
-      <c r="K9" s="184"/>
+      <c r="J9" s="146"/>
+      <c r="K9" s="178"/>
     </row>
     <row r="10" spans="1:11" ht="14.4">
       <c r="A10" s="82"/>
@@ -15427,11 +15427,11 @@
       <c r="H10" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I10" s="185" t="s">
+      <c r="I10" s="181" t="s">
         <v>118</v>
       </c>
-      <c r="J10" s="154"/>
-      <c r="K10" s="184"/>
+      <c r="J10" s="146"/>
+      <c r="K10" s="178"/>
     </row>
     <row r="11" spans="1:11" ht="14.4">
       <c r="A11" s="1"/>
@@ -15457,11 +15457,11 @@
       <c r="H11" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I11" s="185" t="s">
+      <c r="I11" s="181" t="s">
         <v>119</v>
       </c>
-      <c r="J11" s="154"/>
-      <c r="K11" s="184"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="178"/>
     </row>
     <row r="12" spans="1:11" ht="14.4">
       <c r="A12" s="1"/>
@@ -15487,11 +15487,11 @@
       <c r="H12" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I12" s="183" t="s">
+      <c r="I12" s="177" t="s">
         <v>120</v>
       </c>
-      <c r="J12" s="154"/>
-      <c r="K12" s="184"/>
+      <c r="J12" s="146"/>
+      <c r="K12" s="178"/>
     </row>
     <row r="13" spans="1:11" ht="21.75" customHeight="1">
       <c r="A13" s="1"/>
@@ -15511,9 +15511,9 @@
         <v>0</v>
       </c>
       <c r="H13" s="83"/>
-      <c r="I13" s="183"/>
-      <c r="J13" s="154"/>
-      <c r="K13" s="184"/>
+      <c r="I13" s="177"/>
+      <c r="J13" s="146"/>
+      <c r="K13" s="178"/>
     </row>
     <row r="14" spans="1:11" ht="21.75" customHeight="1">
       <c r="A14" s="1"/>
@@ -15533,9 +15533,9 @@
         <v>0</v>
       </c>
       <c r="H14" s="83"/>
-      <c r="I14" s="185"/>
-      <c r="J14" s="154"/>
-      <c r="K14" s="184"/>
+      <c r="I14" s="181"/>
+      <c r="J14" s="146"/>
+      <c r="K14" s="178"/>
     </row>
     <row r="15" spans="1:11" ht="14.4">
       <c r="A15" s="1"/>
@@ -15561,11 +15561,11 @@
       <c r="H15" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="185" t="s">
+      <c r="I15" s="181" t="s">
         <v>121</v>
       </c>
-      <c r="J15" s="154"/>
-      <c r="K15" s="184"/>
+      <c r="J15" s="146"/>
+      <c r="K15" s="178"/>
     </row>
     <row r="16" spans="1:11" ht="20.25" customHeight="1">
       <c r="A16" s="1"/>
@@ -15587,11 +15587,11 @@
       <c r="H16" s="93" t="s">
         <v>122</v>
       </c>
-      <c r="I16" s="185" t="s">
+      <c r="I16" s="181" t="s">
         <v>123</v>
       </c>
-      <c r="J16" s="154"/>
-      <c r="K16" s="184"/>
+      <c r="J16" s="146"/>
+      <c r="K16" s="178"/>
     </row>
     <row r="17" spans="1:11" ht="14.4">
       <c r="A17" s="1"/>
@@ -15617,11 +15617,11 @@
       <c r="H17" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="199" t="s">
+      <c r="I17" s="192" t="s">
         <v>124</v>
       </c>
-      <c r="J17" s="154"/>
-      <c r="K17" s="184"/>
+      <c r="J17" s="146"/>
+      <c r="K17" s="178"/>
     </row>
     <row r="18" spans="1:11" ht="14.4">
       <c r="A18" s="1"/>
@@ -15647,11 +15647,11 @@
       <c r="H18" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="185" t="s">
+      <c r="I18" s="181" t="s">
         <v>121</v>
       </c>
-      <c r="J18" s="154"/>
-      <c r="K18" s="184"/>
+      <c r="J18" s="146"/>
+      <c r="K18" s="178"/>
     </row>
     <row r="19" spans="1:11" ht="14.4">
       <c r="A19" s="1"/>
@@ -15677,11 +15677,11 @@
       <c r="H19" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I19" s="185" t="s">
+      <c r="I19" s="181" t="s">
         <v>125</v>
       </c>
-      <c r="J19" s="154"/>
-      <c r="K19" s="184"/>
+      <c r="J19" s="146"/>
+      <c r="K19" s="178"/>
     </row>
     <row r="20" spans="1:11" ht="21.75" customHeight="1">
       <c r="A20" s="1"/>
@@ -15701,9 +15701,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="83"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="154"/>
-      <c r="K20" s="184"/>
+      <c r="I20" s="181"/>
+      <c r="J20" s="146"/>
+      <c r="K20" s="178"/>
     </row>
     <row r="21" spans="1:11" ht="21.75" customHeight="1">
       <c r="A21" s="1"/>
@@ -15723,9 +15723,9 @@
         <v>0</v>
       </c>
       <c r="H21" s="83"/>
-      <c r="I21" s="185"/>
-      <c r="J21" s="154"/>
-      <c r="K21" s="184"/>
+      <c r="I21" s="181"/>
+      <c r="J21" s="146"/>
+      <c r="K21" s="178"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
@@ -15751,11 +15751,11 @@
       <c r="H22" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="185" t="s">
+      <c r="I22" s="181" t="s">
         <v>126</v>
       </c>
-      <c r="J22" s="154"/>
-      <c r="K22" s="184"/>
+      <c r="J22" s="146"/>
+      <c r="K22" s="178"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
       <c r="A23" s="1"/>
@@ -15781,11 +15781,11 @@
       <c r="H23" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="185" t="s">
+      <c r="I23" s="181" t="s">
         <v>127</v>
       </c>
-      <c r="J23" s="154"/>
-      <c r="K23" s="184"/>
+      <c r="J23" s="146"/>
+      <c r="K23" s="178"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
@@ -15811,11 +15811,11 @@
       <c r="H24" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="185" t="s">
+      <c r="I24" s="181" t="s">
         <v>128</v>
       </c>
-      <c r="J24" s="154"/>
-      <c r="K24" s="184"/>
+      <c r="J24" s="146"/>
+      <c r="K24" s="178"/>
     </row>
     <row r="25" spans="1:11" ht="21.75" customHeight="1">
       <c r="A25" s="1"/>
@@ -15835,9 +15835,9 @@
         <v>0</v>
       </c>
       <c r="H25" s="83"/>
-      <c r="I25" s="185"/>
-      <c r="J25" s="154"/>
-      <c r="K25" s="184"/>
+      <c r="I25" s="181"/>
+      <c r="J25" s="146"/>
+      <c r="K25" s="178"/>
     </row>
     <row r="26" spans="1:11" ht="31.5" customHeight="1">
       <c r="A26" s="1"/>
@@ -15863,11 +15863,11 @@
       <c r="H26" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="185" t="s">
+      <c r="I26" s="181" t="s">
         <v>128</v>
       </c>
-      <c r="J26" s="154"/>
-      <c r="K26" s="184"/>
+      <c r="J26" s="146"/>
+      <c r="K26" s="178"/>
     </row>
     <row r="27" spans="1:11" ht="21.75" customHeight="1">
       <c r="A27" s="1"/>
@@ -15887,9 +15887,9 @@
         <v>0</v>
       </c>
       <c r="H27" s="83"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="154"/>
-      <c r="K27" s="184"/>
+      <c r="I27" s="181"/>
+      <c r="J27" s="146"/>
+      <c r="K27" s="178"/>
     </row>
     <row r="28" spans="1:11" ht="21.75" customHeight="1">
       <c r="A28" s="1"/>
@@ -15909,9 +15909,9 @@
         <v>0</v>
       </c>
       <c r="H28" s="83"/>
-      <c r="I28" s="185"/>
-      <c r="J28" s="154"/>
-      <c r="K28" s="184"/>
+      <c r="I28" s="181"/>
+      <c r="J28" s="146"/>
+      <c r="K28" s="178"/>
     </row>
     <row r="29" spans="1:11" ht="29.25" customHeight="1">
       <c r="A29" s="1"/>
@@ -15937,11 +15937,11 @@
       <c r="H29" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="185" t="s">
+      <c r="I29" s="181" t="s">
         <v>128</v>
       </c>
-      <c r="J29" s="154"/>
-      <c r="K29" s="184"/>
+      <c r="J29" s="146"/>
+      <c r="K29" s="178"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
@@ -15967,11 +15967,11 @@
       <c r="H30" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I30" s="185" t="s">
+      <c r="I30" s="181" t="s">
         <v>128</v>
       </c>
-      <c r="J30" s="154"/>
-      <c r="K30" s="184"/>
+      <c r="J30" s="146"/>
+      <c r="K30" s="178"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1">
       <c r="A31" s="1"/>
@@ -15997,11 +15997,11 @@
       <c r="H31" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I31" s="185" t="s">
+      <c r="I31" s="181" t="s">
         <v>128</v>
       </c>
-      <c r="J31" s="154"/>
-      <c r="K31" s="184"/>
+      <c r="J31" s="146"/>
+      <c r="K31" s="178"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="1"/>
@@ -16027,11 +16027,11 @@
       <c r="H32" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I32" s="185" t="s">
+      <c r="I32" s="181" t="s">
         <v>128</v>
       </c>
-      <c r="J32" s="154"/>
-      <c r="K32" s="184"/>
+      <c r="J32" s="146"/>
+      <c r="K32" s="178"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1">
       <c r="A33" s="1"/>
@@ -16057,11 +16057,11 @@
       <c r="H33" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I33" s="185" t="s">
+      <c r="I33" s="181" t="s">
         <v>129</v>
       </c>
-      <c r="J33" s="154"/>
-      <c r="K33" s="184"/>
+      <c r="J33" s="146"/>
+      <c r="K33" s="178"/>
     </row>
     <row r="34" spans="1:11" ht="21.75" customHeight="1">
       <c r="A34" s="1"/>
@@ -16081,9 +16081,9 @@
         <v>0</v>
       </c>
       <c r="H34" s="83"/>
-      <c r="I34" s="185"/>
-      <c r="J34" s="154"/>
-      <c r="K34" s="184"/>
+      <c r="I34" s="181"/>
+      <c r="J34" s="146"/>
+      <c r="K34" s="178"/>
     </row>
     <row r="35" spans="1:11" ht="21.75" customHeight="1">
       <c r="A35" s="1"/>
@@ -16103,9 +16103,9 @@
         <v>0</v>
       </c>
       <c r="H35" s="83"/>
-      <c r="I35" s="185"/>
-      <c r="J35" s="154"/>
-      <c r="K35" s="184"/>
+      <c r="I35" s="181"/>
+      <c r="J35" s="146"/>
+      <c r="K35" s="178"/>
     </row>
     <row r="36" spans="1:11" ht="21.75" customHeight="1">
       <c r="A36" s="1"/>
@@ -16127,11 +16127,11 @@
       <c r="H36" s="93" t="s">
         <v>115</v>
       </c>
-      <c r="I36" s="185" t="s">
+      <c r="I36" s="181" t="s">
         <v>130</v>
       </c>
-      <c r="J36" s="154"/>
-      <c r="K36" s="184"/>
+      <c r="J36" s="146"/>
+      <c r="K36" s="178"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1">
       <c r="A37" s="1"/>
@@ -16157,11 +16157,11 @@
       <c r="H37" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I37" s="185" t="s">
+      <c r="I37" s="181" t="s">
         <v>131</v>
       </c>
-      <c r="J37" s="154"/>
-      <c r="K37" s="184"/>
+      <c r="J37" s="146"/>
+      <c r="K37" s="178"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1">
       <c r="A38" s="1"/>
@@ -16187,21 +16187,21 @@
       <c r="H38" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I38" s="185" t="s">
+      <c r="I38" s="181" t="s">
         <v>132</v>
       </c>
-      <c r="J38" s="154"/>
-      <c r="K38" s="184"/>
+      <c r="J38" s="146"/>
+      <c r="K38" s="178"/>
     </row>
     <row r="39" spans="1:11" ht="18" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="192" t="s">
+      <c r="B39" s="199" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="132"/>
-      <c r="D39" s="132"/>
-      <c r="E39" s="132"/>
-      <c r="F39" s="167"/>
+      <c r="C39" s="124"/>
+      <c r="D39" s="124"/>
+      <c r="E39" s="124"/>
+      <c r="F39" s="159"/>
       <c r="G39" s="91">
         <f>SUM(G9:G38)</f>
         <v>152</v>
@@ -16221,12 +16221,12 @@
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
       <c r="G40" s="23"/>
-      <c r="H40" s="193" t="s">
+      <c r="H40" s="196" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="134"/>
-      <c r="J40" s="134"/>
-      <c r="K40" s="135"/>
+      <c r="I40" s="133"/>
+      <c r="J40" s="133"/>
+      <c r="K40" s="134"/>
     </row>
     <row r="41" spans="1:11" ht="20.25" customHeight="1">
       <c r="A41" s="1"/>
@@ -16240,12 +16240,12 @@
       <c r="G41" s="26">
         <v>21</v>
       </c>
-      <c r="H41" s="194" t="s">
+      <c r="H41" s="197" t="s">
         <v>17</v>
       </c>
-      <c r="I41" s="125"/>
-      <c r="J41" s="125"/>
-      <c r="K41" s="124"/>
+      <c r="I41" s="126"/>
+      <c r="J41" s="126"/>
+      <c r="K41" s="127"/>
     </row>
     <row r="42" spans="1:11" ht="20.25" customHeight="1">
       <c r="A42" s="1"/>
@@ -16259,10 +16259,10 @@
       <c r="G42" s="27">
         <v>9</v>
       </c>
-      <c r="H42" s="125"/>
-      <c r="I42" s="125"/>
-      <c r="J42" s="125"/>
-      <c r="K42" s="124"/>
+      <c r="H42" s="126"/>
+      <c r="I42" s="126"/>
+      <c r="J42" s="126"/>
+      <c r="K42" s="127"/>
     </row>
     <row r="43" spans="1:11" ht="20.25" customHeight="1">
       <c r="A43" s="1"/>
@@ -16276,10 +16276,10 @@
       <c r="G43" s="27">
         <v>1</v>
       </c>
-      <c r="H43" s="132"/>
-      <c r="I43" s="132"/>
-      <c r="J43" s="132"/>
-      <c r="K43" s="128"/>
+      <c r="H43" s="124"/>
+      <c r="I43" s="124"/>
+      <c r="J43" s="124"/>
+      <c r="K43" s="123"/>
     </row>
     <row r="44" spans="1:11" ht="20.25" customHeight="1">
       <c r="A44" s="1"/>
@@ -16312,7 +16312,7 @@
       <c r="G45" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H45" s="194" t="s">
+      <c r="H45" s="197" t="s">
         <v>23</v>
       </c>
       <c r="I45" s="1"/>
@@ -16331,7 +16331,7 @@
       <c r="G46" s="27">
         <v>19</v>
       </c>
-      <c r="H46" s="132"/>
+      <c r="H46" s="124"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="48"/>
@@ -16352,10 +16352,10 @@
       <c r="H47" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="I47" s="139" t="s">
+      <c r="I47" s="171" t="s">
         <v>27</v>
       </c>
-      <c r="J47" s="140"/>
+      <c r="J47" s="172"/>
       <c r="K47" s="32" t="s">
         <v>28</v>
       </c>
@@ -16373,10 +16373,10 @@
       <c r="H48" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="I48" s="126" t="s">
+      <c r="I48" s="163" t="s">
         <v>29</v>
       </c>
-      <c r="J48" s="124"/>
+      <c r="J48" s="127"/>
       <c r="K48" s="37" t="s">
         <v>29</v>
       </c>
@@ -16396,10 +16396,10 @@
       <c r="H49" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="I49" s="126" t="s">
+      <c r="I49" s="163" t="s">
         <v>31</v>
       </c>
-      <c r="J49" s="124"/>
+      <c r="J49" s="127"/>
       <c r="K49" s="37" t="s">
         <v>31</v>
       </c>
@@ -16420,10 +16420,10 @@
       <c r="H50" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="I50" s="126" t="s">
+      <c r="I50" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="J50" s="124"/>
+      <c r="J50" s="127"/>
       <c r="K50" s="37" t="s">
         <v>33</v>
       </c>
@@ -16444,10 +16444,10 @@
       <c r="H51" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="I51" s="127" t="s">
+      <c r="I51" s="164" t="s">
         <v>35</v>
       </c>
-      <c r="J51" s="128"/>
+      <c r="J51" s="123"/>
       <c r="K51" s="43" t="s">
         <v>35</v>
       </c>
@@ -16470,23 +16470,23 @@
       <c r="B53" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C53" s="122" t="s">
+      <c r="C53" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="D53" s="124"/>
-      <c r="E53" s="122" t="s">
+      <c r="D53" s="127"/>
+      <c r="E53" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="F53" s="125"/>
-      <c r="G53" s="124"/>
-      <c r="H53" s="195" t="s">
+      <c r="F53" s="126"/>
+      <c r="G53" s="127"/>
+      <c r="H53" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="I53" s="124"/>
-      <c r="J53" s="122" t="s">
+      <c r="I53" s="127"/>
+      <c r="J53" s="161" t="s">
         <v>106</v>
       </c>
-      <c r="K53" s="124"/>
+      <c r="K53" s="127"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1">
       <c r="A54" s="1"/>
@@ -16543,42 +16543,42 @@
     <row r="58" spans="1:11" ht="15.75" customHeight="1">
       <c r="A58" s="51"/>
       <c r="B58" s="52"/>
-      <c r="C58" s="170" t="s">
+      <c r="C58" s="125" t="s">
         <v>143</v>
       </c>
-      <c r="D58" s="124"/>
-      <c r="E58" s="170" t="s">
+      <c r="D58" s="127"/>
+      <c r="E58" s="125" t="s">
         <v>108</v>
       </c>
-      <c r="F58" s="125"/>
-      <c r="G58" s="124"/>
-      <c r="H58" s="196" t="s">
+      <c r="F58" s="126"/>
+      <c r="G58" s="127"/>
+      <c r="H58" s="194" t="s">
         <v>109</v>
       </c>
-      <c r="I58" s="124"/>
-      <c r="J58" s="170" t="s">
+      <c r="I58" s="127"/>
+      <c r="J58" s="125" t="s">
         <v>110</v>
       </c>
-      <c r="K58" s="124"/>
+      <c r="K58" s="127"/>
     </row>
     <row r="59" spans="1:11" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="53"/>
-      <c r="C59" s="169"/>
-      <c r="D59" s="128"/>
-      <c r="E59" s="169" t="s">
+      <c r="C59" s="122"/>
+      <c r="D59" s="123"/>
+      <c r="E59" s="122" t="s">
         <v>111</v>
       </c>
-      <c r="F59" s="132"/>
-      <c r="G59" s="128"/>
-      <c r="H59" s="197" t="s">
+      <c r="F59" s="124"/>
+      <c r="G59" s="123"/>
+      <c r="H59" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="I59" s="128"/>
-      <c r="J59" s="169" t="s">
+      <c r="I59" s="123"/>
+      <c r="J59" s="122" t="s">
         <v>113</v>
       </c>
-      <c r="K59" s="128"/>
+      <c r="K59" s="123"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
@@ -19923,54 +19923,11 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="B2:D5"/>
-    <mergeCell ref="E2:H3"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="B39:F39"/>
     <mergeCell ref="H40:K40"/>
     <mergeCell ref="H41:K43"/>
     <mergeCell ref="E53:G53"/>
@@ -19982,11 +19939,54 @@
     <mergeCell ref="I49:J49"/>
     <mergeCell ref="I50:J50"/>
     <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="E2:H3"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>

--- a/TimesheetBankJakarta_Anggit_Ari_Utomo_2.xlsx
+++ b/TimesheetBankJakarta_Anggit_Ari_Utomo_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\anggit\absen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF4F9BE-BEE6-4C77-BF16-6FD7099F30DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FA1D2B-64A5-4098-BA48-9EEE7F67820C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2495,29 +2495,62 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2528,20 +2561,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2612,68 +2636,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2705,17 +2678,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2726,8 +2717,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5451,137 +5451,137 @@
     </row>
     <row r="2" spans="1:12" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="136"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="132" t="s">
+      <c r="B2" s="145"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="143" t="s">
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="148"/>
+      <c r="J2" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="133"/>
-      <c r="L2" s="134"/>
+      <c r="K2" s="134"/>
+      <c r="L2" s="135"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="142"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
-      <c r="L3" s="144"/>
+      <c r="B3" s="130"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="147"/>
+      <c r="L3" s="152"/>
     </row>
     <row r="4" spans="1:12" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="137"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="145" t="s">
+      <c r="B4" s="130"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="153" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="148" t="s">
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="154"/>
+      <c r="I4" s="155"/>
+      <c r="J4" s="156" t="s">
         <v>152</v>
       </c>
-      <c r="K4" s="149"/>
-      <c r="L4" s="150"/>
+      <c r="K4" s="157"/>
+      <c r="L4" s="158"/>
     </row>
     <row r="5" spans="1:12" ht="14.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="138"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="139"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="147"/>
       <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="151" t="s">
+      <c r="F5" s="159" t="s">
         <v>146</v>
       </c>
-      <c r="G5" s="146"/>
-      <c r="H5" s="146"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="126"/>
-      <c r="L5" s="127"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="154"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="124"/>
     </row>
     <row r="6" spans="1:12" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="154" t="s">
+      <c r="B6" s="162" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="149"/>
-      <c r="D6" s="149"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="157"/>
       <c r="E6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="152">
+      <c r="F6" s="160">
         <v>0</v>
       </c>
-      <c r="G6" s="149"/>
-      <c r="H6" s="149"/>
-      <c r="I6" s="153"/>
-      <c r="J6" s="126"/>
-      <c r="K6" s="126"/>
-      <c r="L6" s="127"/>
+      <c r="G6" s="157"/>
+      <c r="H6" s="157"/>
+      <c r="I6" s="161"/>
+      <c r="J6" s="125"/>
+      <c r="K6" s="125"/>
+      <c r="L6" s="124"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="163" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="157" t="s">
+      <c r="C7" s="165" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="158"/>
-      <c r="E7" s="132" t="s">
+      <c r="D7" s="166"/>
+      <c r="E7" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="140"/>
-      <c r="G7" s="160" t="s">
+      <c r="F7" s="148"/>
+      <c r="G7" s="168" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="130" t="s">
+      <c r="H7" s="141" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="130" t="s">
+      <c r="I7" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="132" t="s">
+      <c r="J7" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="133"/>
-      <c r="L7" s="134"/>
+      <c r="K7" s="134"/>
+      <c r="L7" s="135"/>
     </row>
     <row r="8" spans="1:12" thickBot="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="156"/>
+      <c r="B8" s="164"/>
       <c r="C8" s="8">
         <v>0.33333333333333331</v>
       </c>
       <c r="D8" s="8">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="135"/>
-      <c r="F8" s="159"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="131"/>
-      <c r="I8" s="131"/>
-      <c r="J8" s="135"/>
-      <c r="K8" s="124"/>
-      <c r="L8" s="123"/>
+      <c r="E8" s="144"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="142"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142"/>
+      <c r="J8" s="144"/>
+      <c r="K8" s="132"/>
+      <c r="L8" s="128"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1">
       <c r="A9" s="9"/>
@@ -6412,13 +6412,13 @@
     </row>
     <row r="43" spans="1:12" ht="18" customHeight="1" thickBot="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="168" t="s">
+      <c r="B43" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="C43" s="169"/>
-      <c r="D43" s="169"/>
-      <c r="E43" s="169"/>
-      <c r="F43" s="170"/>
+      <c r="C43" s="137"/>
+      <c r="D43" s="137"/>
+      <c r="E43" s="137"/>
+      <c r="F43" s="138"/>
       <c r="G43" s="18">
         <f>SUM(G9:G39)</f>
         <v>174.5</v>
@@ -6439,13 +6439,13 @@
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
       <c r="G44" s="23"/>
-      <c r="H44" s="167" t="s">
+      <c r="H44" s="133" t="s">
         <v>15</v>
       </c>
-      <c r="I44" s="133"/>
-      <c r="J44" s="133"/>
-      <c r="K44" s="133"/>
-      <c r="L44" s="134"/>
+      <c r="I44" s="134"/>
+      <c r="J44" s="134"/>
+      <c r="K44" s="134"/>
+      <c r="L44" s="135"/>
     </row>
     <row r="45" spans="1:12" ht="20.25" customHeight="1">
       <c r="A45" s="1"/>
@@ -6459,13 +6459,13 @@
       <c r="G45" s="26">
         <v>21</v>
       </c>
-      <c r="H45" s="165" t="s">
+      <c r="H45" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="126"/>
-      <c r="J45" s="126"/>
-      <c r="K45" s="126"/>
-      <c r="L45" s="127"/>
+      <c r="I45" s="125"/>
+      <c r="J45" s="125"/>
+      <c r="K45" s="125"/>
+      <c r="L45" s="124"/>
     </row>
     <row r="46" spans="1:12" ht="20.25" customHeight="1">
       <c r="A46" s="1"/>
@@ -6477,13 +6477,13 @@
       <c r="E46" s="25"/>
       <c r="F46" s="25"/>
       <c r="G46" s="27">
-        <v>0</v>
-      </c>
-      <c r="H46" s="137"/>
-      <c r="I46" s="126"/>
-      <c r="J46" s="126"/>
-      <c r="K46" s="126"/>
-      <c r="L46" s="127"/>
+        <v>1</v>
+      </c>
+      <c r="H46" s="130"/>
+      <c r="I46" s="125"/>
+      <c r="J46" s="125"/>
+      <c r="K46" s="125"/>
+      <c r="L46" s="124"/>
     </row>
     <row r="47" spans="1:12" ht="20.25" customHeight="1" thickBot="1">
       <c r="A47" s="1"/>
@@ -6497,11 +6497,11 @@
       <c r="G47" s="27">
         <v>0</v>
       </c>
-      <c r="H47" s="166"/>
-      <c r="I47" s="124"/>
-      <c r="J47" s="124"/>
-      <c r="K47" s="124"/>
-      <c r="L47" s="123"/>
+      <c r="H47" s="131"/>
+      <c r="I47" s="132"/>
+      <c r="J47" s="132"/>
+      <c r="K47" s="132"/>
+      <c r="L47" s="128"/>
     </row>
     <row r="48" spans="1:12" ht="20.25" customHeight="1">
       <c r="A48" s="1"/>
@@ -6515,13 +6515,13 @@
       <c r="G48" s="27">
         <v>0</v>
       </c>
-      <c r="H48" s="167" t="s">
+      <c r="H48" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="I48" s="133"/>
-      <c r="J48" s="133"/>
-      <c r="K48" s="133"/>
-      <c r="L48" s="134"/>
+      <c r="I48" s="134"/>
+      <c r="J48" s="134"/>
+      <c r="K48" s="134"/>
+      <c r="L48" s="135"/>
     </row>
     <row r="49" spans="1:12" ht="20.25" customHeight="1">
       <c r="A49" s="1"/>
@@ -6535,13 +6535,13 @@
       <c r="G49" s="27">
         <v>0</v>
       </c>
-      <c r="H49" s="161" t="s">
+      <c r="H49" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="I49" s="126"/>
-      <c r="J49" s="126"/>
-      <c r="K49" s="126"/>
-      <c r="L49" s="127"/>
+      <c r="I49" s="125"/>
+      <c r="J49" s="125"/>
+      <c r="K49" s="125"/>
+      <c r="L49" s="124"/>
     </row>
     <row r="50" spans="1:12" ht="20.25" customHeight="1" thickBot="1">
       <c r="A50" s="1"/>
@@ -6553,13 +6553,13 @@
       <c r="E50" s="25"/>
       <c r="F50" s="25"/>
       <c r="G50" s="27">
-        <v>22</v>
-      </c>
-      <c r="H50" s="166"/>
-      <c r="I50" s="124"/>
-      <c r="J50" s="124"/>
-      <c r="K50" s="124"/>
-      <c r="L50" s="123"/>
+        <v>21</v>
+      </c>
+      <c r="H50" s="131"/>
+      <c r="I50" s="132"/>
+      <c r="J50" s="132"/>
+      <c r="K50" s="132"/>
+      <c r="L50" s="128"/>
     </row>
     <row r="51" spans="1:12" ht="24" customHeight="1" thickBot="1">
       <c r="A51" s="1"/>
@@ -6572,16 +6572,16 @@
       <c r="F51" s="25"/>
       <c r="G51" s="29">
         <f>G50/G45</f>
-        <v>1.0476190476190477</v>
+        <v>1</v>
       </c>
       <c r="H51" s="30" t="s">
         <v>26</v>
       </c>
       <c r="I51" s="31"/>
-      <c r="J51" s="171" t="s">
+      <c r="J51" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="K51" s="172"/>
+      <c r="K51" s="140"/>
       <c r="L51" s="32" t="s">
         <v>28</v>
       </c>
@@ -6600,10 +6600,10 @@
         <v>29</v>
       </c>
       <c r="I52" s="36"/>
-      <c r="J52" s="163" t="s">
+      <c r="J52" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="K52" s="127"/>
+      <c r="K52" s="124"/>
       <c r="L52" s="37" t="s">
         <v>29</v>
       </c>
@@ -6625,10 +6625,10 @@
         <v>31</v>
       </c>
       <c r="I53" s="36"/>
-      <c r="J53" s="163" t="s">
+      <c r="J53" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="K53" s="127"/>
+      <c r="K53" s="124"/>
       <c r="L53" s="37" t="s">
         <v>31</v>
       </c>
@@ -6650,10 +6650,10 @@
         <v>33</v>
       </c>
       <c r="I54" s="36"/>
-      <c r="J54" s="163" t="s">
+      <c r="J54" s="126" t="s">
         <v>33</v>
       </c>
-      <c r="K54" s="127"/>
+      <c r="K54" s="124"/>
       <c r="L54" s="37" t="s">
         <v>33</v>
       </c>
@@ -6675,10 +6675,10 @@
         <v>35</v>
       </c>
       <c r="I55" s="42"/>
-      <c r="J55" s="164" t="s">
+      <c r="J55" s="127" t="s">
         <v>35</v>
       </c>
-      <c r="K55" s="123"/>
+      <c r="K55" s="128"/>
       <c r="L55" s="43" t="s">
         <v>35</v>
       </c>
@@ -6700,32 +6700,32 @@
     <row r="57" spans="1:12" ht="15.75" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="28"/>
-      <c r="C57" s="161" t="s">
+      <c r="C57" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="D57" s="127"/>
-      <c r="E57" s="161" t="s">
+      <c r="D57" s="124"/>
+      <c r="E57" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="F57" s="126"/>
-      <c r="G57" s="127"/>
-      <c r="H57" s="161" t="s">
+      <c r="F57" s="125"/>
+      <c r="G57" s="124"/>
+      <c r="H57" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="I57" s="126"/>
-      <c r="J57" s="127"/>
-      <c r="K57" s="161" t="s">
+      <c r="I57" s="125"/>
+      <c r="J57" s="124"/>
+      <c r="K57" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="L57" s="127"/>
+      <c r="L57" s="124"/>
     </row>
     <row r="58" spans="1:12" ht="15.75" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="161"/>
-      <c r="D58" s="162"/>
+      <c r="C58" s="122"/>
+      <c r="D58" s="123"/>
       <c r="E58" s="47"/>
       <c r="F58" s="1"/>
       <c r="G58" s="48"/>
@@ -6740,8 +6740,8 @@
       <c r="B59" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="C59" s="161"/>
-      <c r="D59" s="162"/>
+      <c r="C59" s="122"/>
+      <c r="D59" s="123"/>
       <c r="E59" s="47"/>
       <c r="F59" s="1"/>
       <c r="G59" s="48"/>
@@ -6756,8 +6756,8 @@
       <c r="B60" s="50">
         <v>46257</v>
       </c>
-      <c r="C60" s="161"/>
-      <c r="D60" s="162"/>
+      <c r="C60" s="122"/>
+      <c r="D60" s="123"/>
       <c r="E60" s="47"/>
       <c r="F60" s="1"/>
       <c r="G60" s="48"/>
@@ -6770,8 +6770,8 @@
     <row r="61" spans="1:12" ht="15.75" customHeight="1">
       <c r="A61" s="51"/>
       <c r="B61" s="47"/>
-      <c r="C61" s="161"/>
-      <c r="D61" s="162"/>
+      <c r="C61" s="122"/>
+      <c r="D61" s="123"/>
       <c r="E61" s="47"/>
       <c r="F61" s="1"/>
       <c r="G61" s="48"/>
@@ -6784,44 +6784,44 @@
     <row r="62" spans="1:12" ht="15.75" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="52"/>
-      <c r="C62" s="129" t="s">
+      <c r="C62" s="172" t="s">
         <v>151</v>
       </c>
-      <c r="D62" s="127"/>
-      <c r="E62" s="125" t="s">
+      <c r="D62" s="124"/>
+      <c r="E62" s="170" t="s">
         <v>41</v>
       </c>
-      <c r="F62" s="126"/>
-      <c r="G62" s="127"/>
-      <c r="H62" s="128" t="s">
+      <c r="F62" s="125"/>
+      <c r="G62" s="124"/>
+      <c r="H62" s="171" t="s">
         <v>145</v>
       </c>
-      <c r="I62" s="126"/>
-      <c r="J62" s="127"/>
-      <c r="K62" s="125" t="s">
+      <c r="I62" s="125"/>
+      <c r="J62" s="124"/>
+      <c r="K62" s="170" t="s">
         <v>42</v>
       </c>
-      <c r="L62" s="127"/>
+      <c r="L62" s="124"/>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A63" s="1"/>
       <c r="B63" s="53"/>
-      <c r="C63" s="122"/>
-      <c r="D63" s="123"/>
-      <c r="E63" s="122" t="s">
+      <c r="C63" s="169"/>
+      <c r="D63" s="128"/>
+      <c r="E63" s="169" t="s">
         <v>43</v>
       </c>
-      <c r="F63" s="124"/>
-      <c r="G63" s="123"/>
-      <c r="H63" s="122" t="s">
+      <c r="F63" s="132"/>
+      <c r="G63" s="128"/>
+      <c r="H63" s="169" t="s">
         <v>44</v>
       </c>
-      <c r="I63" s="124"/>
-      <c r="J63" s="123"/>
-      <c r="K63" s="122" t="s">
+      <c r="I63" s="132"/>
+      <c r="J63" s="128"/>
+      <c r="K63" s="169" t="s">
         <v>45</v>
       </c>
-      <c r="L63" s="123"/>
+      <c r="L63" s="128"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1">
       <c r="A64" s="1"/>
@@ -10361,6 +10361,48 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="H63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:L8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="E2:I3"/>
+    <mergeCell ref="J2:L3"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="J4:L6"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:G8"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="C58:D61"/>
     <mergeCell ref="C57:D57"/>
@@ -10377,48 +10419,6 @@
     <mergeCell ref="J51:K51"/>
     <mergeCell ref="H49:L50"/>
     <mergeCell ref="H44:L44"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:L8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="B2:D5"/>
-    <mergeCell ref="E2:I3"/>
-    <mergeCell ref="J2:L3"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="J4:L6"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="J30:L30"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="H63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="J21:L21"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.19685039370078741" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="81" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -10461,128 +10461,128 @@
     </row>
     <row r="2" spans="1:11" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="136"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="140"/>
-      <c r="E2" s="132" t="s">
+      <c r="B2" s="145"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="132" t="s">
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="133"/>
-      <c r="K2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="135"/>
     </row>
     <row r="3" spans="1:11" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="144"/>
+      <c r="B3" s="130"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="152"/>
     </row>
     <row r="4" spans="1:11" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="137"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="182"/>
-      <c r="E4" s="145" t="s">
+      <c r="B4" s="130"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="183" t="s">
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="155"/>
+      <c r="I4" s="174" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="149"/>
-      <c r="K4" s="150"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="158"/>
     </row>
     <row r="5" spans="1:11" ht="14.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="138"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="142"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="150"/>
       <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="151" t="s">
+      <c r="F5" s="159" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="146"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="184"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="127"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="124"/>
     </row>
     <row r="6" spans="1:11" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="179" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="187"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="178"/>
       <c r="E6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="185">
+      <c r="F6" s="176">
         <v>20230682322</v>
       </c>
-      <c r="G6" s="186"/>
-      <c r="H6" s="187"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="123"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="144"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="128"/>
     </row>
     <row r="7" spans="1:11" ht="14.4">
       <c r="A7" s="1"/>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="163" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="157" t="s">
+      <c r="C7" s="165" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="158"/>
-      <c r="E7" s="136" t="s">
+      <c r="D7" s="166"/>
+      <c r="E7" s="145" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="134"/>
-      <c r="G7" s="189" t="s">
+      <c r="F7" s="135"/>
+      <c r="G7" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="190" t="s">
+      <c r="H7" s="181" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="143" t="s">
+      <c r="I7" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="133"/>
-      <c r="K7" s="134"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="135"/>
     </row>
     <row r="8" spans="1:11" ht="14.4">
       <c r="A8" s="1"/>
-      <c r="B8" s="156"/>
+      <c r="B8" s="164"/>
       <c r="C8" s="8">
         <v>0.33333333333333331</v>
       </c>
       <c r="D8" s="55">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="166"/>
-      <c r="F8" s="123"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="191"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="124"/>
-      <c r="K8" s="123"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="182"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="128"/>
     </row>
     <row r="9" spans="1:11" ht="14.4">
       <c r="A9" s="2"/>
@@ -10607,11 +10607,11 @@
       <c r="H9" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="177" t="s">
+      <c r="I9" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="146"/>
-      <c r="K9" s="178"/>
+      <c r="J9" s="154"/>
+      <c r="K9" s="184"/>
     </row>
     <row r="10" spans="1:11" ht="14.4">
       <c r="A10" s="9"/>
@@ -10636,11 +10636,11 @@
       <c r="H10" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="177" t="s">
+      <c r="I10" s="183" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="146"/>
-      <c r="K10" s="178"/>
+      <c r="J10" s="154"/>
+      <c r="K10" s="184"/>
     </row>
     <row r="11" spans="1:11" ht="14.4">
       <c r="A11" s="2"/>
@@ -10665,11 +10665,11 @@
       <c r="H11" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I11" s="177" t="s">
+      <c r="I11" s="183" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="146"/>
-      <c r="K11" s="178"/>
+      <c r="J11" s="154"/>
+      <c r="K11" s="184"/>
     </row>
     <row r="12" spans="1:11" ht="14.4">
       <c r="A12" s="2"/>
@@ -10688,9 +10688,9 @@
         <v>0</v>
       </c>
       <c r="H12" s="13"/>
-      <c r="I12" s="177"/>
-      <c r="J12" s="146"/>
-      <c r="K12" s="178"/>
+      <c r="I12" s="183"/>
+      <c r="J12" s="154"/>
+      <c r="K12" s="184"/>
     </row>
     <row r="13" spans="1:11" ht="14.4">
       <c r="A13" s="2"/>
@@ -10709,9 +10709,9 @@
         <v>0</v>
       </c>
       <c r="H13" s="13"/>
-      <c r="I13" s="177"/>
-      <c r="J13" s="146"/>
-      <c r="K13" s="178"/>
+      <c r="I13" s="183"/>
+      <c r="J13" s="154"/>
+      <c r="K13" s="184"/>
     </row>
     <row r="14" spans="1:11" ht="14.4">
       <c r="A14" s="2"/>
@@ -10736,11 +10736,11 @@
       <c r="H14" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I14" s="177" t="s">
+      <c r="I14" s="183" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="146"/>
-      <c r="K14" s="178"/>
+      <c r="J14" s="154"/>
+      <c r="K14" s="184"/>
     </row>
     <row r="15" spans="1:11" ht="14.4">
       <c r="A15" s="2"/>
@@ -10765,11 +10765,11 @@
       <c r="H15" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="177" t="s">
+      <c r="I15" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="146"/>
-      <c r="K15" s="178"/>
+      <c r="J15" s="154"/>
+      <c r="K15" s="184"/>
     </row>
     <row r="16" spans="1:11" ht="14.4">
       <c r="A16" s="2"/>
@@ -10788,9 +10788,9 @@
         <v>0</v>
       </c>
       <c r="H16" s="11"/>
-      <c r="I16" s="181"/>
-      <c r="J16" s="146"/>
-      <c r="K16" s="178"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="154"/>
+      <c r="K16" s="184"/>
     </row>
     <row r="17" spans="1:11" ht="14.4">
       <c r="A17" s="2"/>
@@ -10815,11 +10815,11 @@
       <c r="H17" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="177" t="s">
+      <c r="I17" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="J17" s="146"/>
-      <c r="K17" s="178"/>
+      <c r="J17" s="154"/>
+      <c r="K17" s="184"/>
     </row>
     <row r="18" spans="1:11" ht="14.4">
       <c r="A18" s="2"/>
@@ -10844,11 +10844,11 @@
       <c r="H18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="177" t="s">
+      <c r="I18" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="J18" s="146"/>
-      <c r="K18" s="178"/>
+      <c r="J18" s="154"/>
+      <c r="K18" s="184"/>
     </row>
     <row r="19" spans="1:11" ht="14.4">
       <c r="A19" s="2"/>
@@ -10867,9 +10867,9 @@
         <v>0</v>
       </c>
       <c r="H19" s="11"/>
-      <c r="I19" s="181"/>
-      <c r="J19" s="146"/>
-      <c r="K19" s="178"/>
+      <c r="I19" s="185"/>
+      <c r="J19" s="154"/>
+      <c r="K19" s="184"/>
     </row>
     <row r="20" spans="1:11" ht="14.4">
       <c r="A20" s="2"/>
@@ -10888,9 +10888,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="11"/>
-      <c r="I20" s="181"/>
-      <c r="J20" s="146"/>
-      <c r="K20" s="178"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="154"/>
+      <c r="K20" s="184"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1">
       <c r="A21" s="2"/>
@@ -10915,11 +10915,11 @@
       <c r="H21" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I21" s="177" t="s">
+      <c r="I21" s="183" t="s">
         <v>68</v>
       </c>
-      <c r="J21" s="146"/>
-      <c r="K21" s="178"/>
+      <c r="J21" s="154"/>
+      <c r="K21" s="184"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
       <c r="A22" s="2"/>
@@ -10944,11 +10944,11 @@
       <c r="H22" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="177" t="s">
+      <c r="I22" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="146"/>
-      <c r="K22" s="178"/>
+      <c r="J22" s="154"/>
+      <c r="K22" s="184"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
       <c r="A23" s="2"/>
@@ -10973,11 +10973,11 @@
       <c r="H23" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="177" t="s">
+      <c r="I23" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="146"/>
-      <c r="K23" s="178"/>
+      <c r="J23" s="154"/>
+      <c r="K23" s="184"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="2"/>
@@ -11002,11 +11002,11 @@
       <c r="H24" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="177" t="s">
+      <c r="I24" s="183" t="s">
         <v>72</v>
       </c>
-      <c r="J24" s="146"/>
-      <c r="K24" s="178"/>
+      <c r="J24" s="154"/>
+      <c r="K24" s="184"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1">
       <c r="A25" s="2"/>
@@ -11031,11 +11031,11 @@
       <c r="H25" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="177" t="s">
+      <c r="I25" s="183" t="s">
         <v>74</v>
       </c>
-      <c r="J25" s="146"/>
-      <c r="K25" s="178"/>
+      <c r="J25" s="154"/>
+      <c r="K25" s="184"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1">
       <c r="A26" s="2"/>
@@ -11054,9 +11054,9 @@
         <v>0</v>
       </c>
       <c r="H26" s="11"/>
-      <c r="I26" s="181"/>
-      <c r="J26" s="146"/>
-      <c r="K26" s="178"/>
+      <c r="I26" s="185"/>
+      <c r="J26" s="154"/>
+      <c r="K26" s="184"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
       <c r="A27" s="2"/>
@@ -11075,9 +11075,9 @@
         <v>0</v>
       </c>
       <c r="H27" s="11"/>
-      <c r="I27" s="181"/>
-      <c r="J27" s="146"/>
-      <c r="K27" s="178"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="154"/>
+      <c r="K27" s="184"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1">
       <c r="A28" s="2"/>
@@ -11102,11 +11102,11 @@
       <c r="H28" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I28" s="177" t="s">
+      <c r="I28" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="J28" s="146"/>
-      <c r="K28" s="178"/>
+      <c r="J28" s="154"/>
+      <c r="K28" s="184"/>
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1">
       <c r="A29" s="2"/>
@@ -11131,11 +11131,11 @@
       <c r="H29" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="177" t="s">
+      <c r="I29" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="J29" s="146"/>
-      <c r="K29" s="178"/>
+      <c r="J29" s="154"/>
+      <c r="K29" s="184"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="2"/>
@@ -11160,11 +11160,11 @@
       <c r="H30" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I30" s="177" t="s">
+      <c r="I30" s="183" t="s">
         <v>82</v>
       </c>
-      <c r="J30" s="146"/>
-      <c r="K30" s="178"/>
+      <c r="J30" s="154"/>
+      <c r="K30" s="184"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1">
       <c r="A31" s="2"/>
@@ -11189,11 +11189,11 @@
       <c r="H31" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I31" s="177" t="s">
+      <c r="I31" s="183" t="s">
         <v>84</v>
       </c>
-      <c r="J31" s="146"/>
-      <c r="K31" s="178"/>
+      <c r="J31" s="154"/>
+      <c r="K31" s="184"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="2"/>
@@ -11218,11 +11218,11 @@
       <c r="H32" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I32" s="177" t="s">
+      <c r="I32" s="183" t="s">
         <v>86</v>
       </c>
-      <c r="J32" s="146"/>
-      <c r="K32" s="178"/>
+      <c r="J32" s="154"/>
+      <c r="K32" s="184"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1">
       <c r="A33" s="2"/>
@@ -11241,9 +11241,9 @@
         <v>0</v>
       </c>
       <c r="H33" s="11"/>
-      <c r="I33" s="181"/>
-      <c r="J33" s="146"/>
-      <c r="K33" s="178"/>
+      <c r="I33" s="185"/>
+      <c r="J33" s="154"/>
+      <c r="K33" s="184"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1">
       <c r="A34" s="2"/>
@@ -11262,9 +11262,9 @@
         <v>0</v>
       </c>
       <c r="H34" s="11"/>
-      <c r="I34" s="181"/>
-      <c r="J34" s="146"/>
-      <c r="K34" s="178"/>
+      <c r="I34" s="185"/>
+      <c r="J34" s="154"/>
+      <c r="K34" s="184"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1">
       <c r="A35" s="2"/>
@@ -11289,11 +11289,11 @@
       <c r="H35" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I35" s="177" t="s">
+      <c r="I35" s="183" t="s">
         <v>90</v>
       </c>
-      <c r="J35" s="146"/>
-      <c r="K35" s="178"/>
+      <c r="J35" s="154"/>
+      <c r="K35" s="184"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1">
       <c r="A36" s="2"/>
@@ -11318,11 +11318,11 @@
       <c r="H36" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I36" s="177" t="s">
+      <c r="I36" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="J36" s="146"/>
-      <c r="K36" s="178"/>
+      <c r="J36" s="154"/>
+      <c r="K36" s="184"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1">
       <c r="A37" s="2"/>
@@ -11347,11 +11347,11 @@
       <c r="H37" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I37" s="177" t="s">
+      <c r="I37" s="183" t="s">
         <v>68</v>
       </c>
-      <c r="J37" s="146"/>
-      <c r="K37" s="178"/>
+      <c r="J37" s="154"/>
+      <c r="K37" s="184"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1">
       <c r="A38" s="2"/>
@@ -11376,11 +11376,11 @@
       <c r="H38" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I38" s="177" t="s">
+      <c r="I38" s="183" t="s">
         <v>94</v>
       </c>
-      <c r="J38" s="146"/>
-      <c r="K38" s="178"/>
+      <c r="J38" s="154"/>
+      <c r="K38" s="184"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1">
       <c r="A39" s="2"/>
@@ -11405,21 +11405,21 @@
       <c r="H39" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I39" s="180" t="s">
+      <c r="I39" s="187" t="s">
         <v>94</v>
       </c>
-      <c r="J39" s="149"/>
-      <c r="K39" s="150"/>
+      <c r="J39" s="157"/>
+      <c r="K39" s="158"/>
     </row>
     <row r="40" spans="1:11" ht="18" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="168" t="s">
+      <c r="B40" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="173"/>
-      <c r="D40" s="173"/>
-      <c r="E40" s="173"/>
-      <c r="F40" s="174"/>
+      <c r="C40" s="188"/>
+      <c r="D40" s="188"/>
+      <c r="E40" s="188"/>
+      <c r="F40" s="189"/>
       <c r="G40" s="18">
         <f>SUM(G9:G39)</f>
         <v>176</v>
@@ -11439,12 +11439,12 @@
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
       <c r="G41" s="23"/>
-      <c r="H41" s="175" t="s">
+      <c r="H41" s="190" t="s">
         <v>15</v>
       </c>
-      <c r="I41" s="133"/>
-      <c r="J41" s="133"/>
-      <c r="K41" s="134"/>
+      <c r="I41" s="134"/>
+      <c r="J41" s="134"/>
+      <c r="K41" s="135"/>
     </row>
     <row r="42" spans="1:11" ht="20.25" customHeight="1">
       <c r="A42" s="1"/>
@@ -11458,12 +11458,12 @@
       <c r="G42" s="26">
         <v>22</v>
       </c>
-      <c r="H42" s="176" t="s">
+      <c r="H42" s="191" t="s">
         <v>17</v>
       </c>
-      <c r="I42" s="126"/>
-      <c r="J42" s="126"/>
-      <c r="K42" s="127"/>
+      <c r="I42" s="125"/>
+      <c r="J42" s="125"/>
+      <c r="K42" s="124"/>
     </row>
     <row r="43" spans="1:11" ht="20.25" customHeight="1">
       <c r="A43" s="1"/>
@@ -11477,10 +11477,10 @@
       <c r="G43" s="27">
         <v>9</v>
       </c>
-      <c r="H43" s="126"/>
-      <c r="I43" s="126"/>
-      <c r="J43" s="126"/>
-      <c r="K43" s="127"/>
+      <c r="H43" s="125"/>
+      <c r="I43" s="125"/>
+      <c r="J43" s="125"/>
+      <c r="K43" s="124"/>
     </row>
     <row r="44" spans="1:11" ht="20.25" customHeight="1">
       <c r="A44" s="1"/>
@@ -11494,10 +11494,10 @@
       <c r="G44" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H44" s="124"/>
-      <c r="I44" s="124"/>
-      <c r="J44" s="124"/>
-      <c r="K44" s="123"/>
+      <c r="H44" s="132"/>
+      <c r="I44" s="132"/>
+      <c r="J44" s="132"/>
+      <c r="K44" s="128"/>
     </row>
     <row r="45" spans="1:11" ht="20.25" customHeight="1">
       <c r="A45" s="1"/>
@@ -11530,7 +11530,7 @@
       <c r="G46" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H46" s="179" t="s">
+      <c r="H46" s="186" t="s">
         <v>23</v>
       </c>
       <c r="I46" s="1"/>
@@ -11549,7 +11549,7 @@
       <c r="G47" s="27">
         <v>22</v>
       </c>
-      <c r="H47" s="124"/>
+      <c r="H47" s="132"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="48"/>
@@ -11570,10 +11570,10 @@
       <c r="H48" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="I48" s="171" t="s">
+      <c r="I48" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="J48" s="172"/>
+      <c r="J48" s="140"/>
       <c r="K48" s="32" t="s">
         <v>28</v>
       </c>
@@ -11591,10 +11591,10 @@
       <c r="H49" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="I49" s="163" t="s">
+      <c r="I49" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="J49" s="127"/>
+      <c r="J49" s="124"/>
       <c r="K49" s="37" t="s">
         <v>29</v>
       </c>
@@ -11615,10 +11615,10 @@
       <c r="H50" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="I50" s="163" t="s">
+      <c r="I50" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="J50" s="127"/>
+      <c r="J50" s="124"/>
       <c r="K50" s="37" t="s">
         <v>31</v>
       </c>
@@ -11639,10 +11639,10 @@
       <c r="H51" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I51" s="163" t="s">
+      <c r="I51" s="126" t="s">
         <v>33</v>
       </c>
-      <c r="J51" s="127"/>
+      <c r="J51" s="124"/>
       <c r="K51" s="37" t="s">
         <v>33</v>
       </c>
@@ -11663,10 +11663,10 @@
       <c r="H52" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="I52" s="164" t="s">
+      <c r="I52" s="127" t="s">
         <v>35</v>
       </c>
-      <c r="J52" s="123"/>
+      <c r="J52" s="128"/>
       <c r="K52" s="43" t="s">
         <v>35</v>
       </c>
@@ -11689,23 +11689,23 @@
       <c r="B54" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="161" t="s">
+      <c r="C54" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="D54" s="127"/>
-      <c r="E54" s="161" t="s">
+      <c r="D54" s="124"/>
+      <c r="E54" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="F54" s="126"/>
-      <c r="G54" s="127"/>
-      <c r="H54" s="161" t="s">
+      <c r="F54" s="125"/>
+      <c r="G54" s="124"/>
+      <c r="H54" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="I54" s="127"/>
-      <c r="J54" s="161" t="s">
+      <c r="I54" s="124"/>
+      <c r="J54" s="122" t="s">
         <v>106</v>
       </c>
-      <c r="K54" s="127"/>
+      <c r="K54" s="124"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1">
       <c r="A55" s="1"/>
@@ -11762,42 +11762,42 @@
     <row r="59" spans="1:11" ht="15.75" customHeight="1">
       <c r="A59" s="51"/>
       <c r="B59" s="52"/>
-      <c r="C59" s="125" t="s">
+      <c r="C59" s="170" t="s">
         <v>107</v>
       </c>
-      <c r="D59" s="127"/>
-      <c r="E59" s="125" t="s">
+      <c r="D59" s="124"/>
+      <c r="E59" s="170" t="s">
         <v>108</v>
       </c>
-      <c r="F59" s="126"/>
-      <c r="G59" s="127"/>
-      <c r="H59" s="125" t="s">
+      <c r="F59" s="125"/>
+      <c r="G59" s="124"/>
+      <c r="H59" s="170" t="s">
         <v>109</v>
       </c>
-      <c r="I59" s="127"/>
-      <c r="J59" s="125" t="s">
+      <c r="I59" s="124"/>
+      <c r="J59" s="170" t="s">
         <v>110</v>
       </c>
-      <c r="K59" s="127"/>
+      <c r="K59" s="124"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="53"/>
-      <c r="C60" s="122"/>
-      <c r="D60" s="123"/>
-      <c r="E60" s="122" t="s">
+      <c r="C60" s="169"/>
+      <c r="D60" s="128"/>
+      <c r="E60" s="169" t="s">
         <v>111</v>
       </c>
-      <c r="F60" s="124"/>
-      <c r="G60" s="123"/>
-      <c r="H60" s="122" t="s">
+      <c r="F60" s="132"/>
+      <c r="G60" s="128"/>
+      <c r="H60" s="169" t="s">
         <v>112</v>
       </c>
-      <c r="I60" s="123"/>
-      <c r="J60" s="122" t="s">
+      <c r="I60" s="128"/>
+      <c r="J60" s="169" t="s">
         <v>113</v>
       </c>
-      <c r="K60" s="123"/>
+      <c r="K60" s="128"/>
     </row>
     <row r="61" spans="1:11" ht="15.75" customHeight="1">
       <c r="A61" s="1"/>
@@ -15141,6 +15141,56 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="H42:K44"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="E2:H3"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K6"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:K8"/>
+    <mergeCell ref="I9:K9"/>
     <mergeCell ref="C60:D60"/>
     <mergeCell ref="E60:G60"/>
     <mergeCell ref="H60:I60"/>
@@ -15157,56 +15207,6 @@
     <mergeCell ref="C59:D59"/>
     <mergeCell ref="E59:G59"/>
     <mergeCell ref="H59:I59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="B2:D5"/>
-    <mergeCell ref="E2:H3"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K6"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="H42:K44"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I37:K37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -15250,56 +15250,56 @@
     </row>
     <row r="2" spans="1:11" ht="14.4">
       <c r="A2" s="1"/>
-      <c r="B2" s="136"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="140"/>
-      <c r="E2" s="132" t="s">
+      <c r="B2" s="145"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="132" t="s">
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="133"/>
-      <c r="K2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="135"/>
     </row>
     <row r="3" spans="1:11" ht="14.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="144"/>
+      <c r="B3" s="130"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="152"/>
     </row>
     <row r="4" spans="1:11" ht="14.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="137"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="182"/>
-      <c r="E4" s="145" t="s">
+      <c r="B4" s="130"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="183" t="s">
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="155"/>
+      <c r="I4" s="174" t="s">
         <v>116</v>
       </c>
-      <c r="J4" s="149"/>
-      <c r="K4" s="150"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="158"/>
     </row>
     <row r="5" spans="1:11" ht="14.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="138"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="142"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="150"/>
       <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
@@ -15308,70 +15308,70 @@
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="83"/>
-      <c r="I5" s="184"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="127"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="124"/>
     </row>
     <row r="6" spans="1:11" ht="14.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="179" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="187"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="178"/>
       <c r="E6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="185">
+      <c r="F6" s="176">
         <v>20230682322</v>
       </c>
-      <c r="G6" s="186"/>
-      <c r="H6" s="187"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="123"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="144"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="128"/>
     </row>
     <row r="7" spans="1:11" ht="14.4">
       <c r="A7" s="1"/>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="163" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="157" t="s">
+      <c r="C7" s="165" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="158"/>
-      <c r="E7" s="136" t="s">
+      <c r="D7" s="166"/>
+      <c r="E7" s="145" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="134"/>
-      <c r="G7" s="189" t="s">
+      <c r="F7" s="135"/>
+      <c r="G7" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="193" t="s">
+      <c r="H7" s="198" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="143" t="s">
+      <c r="I7" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="133"/>
-      <c r="K7" s="134"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="135"/>
     </row>
     <row r="8" spans="1:11" ht="14.4">
       <c r="A8" s="1"/>
-      <c r="B8" s="156"/>
+      <c r="B8" s="164"/>
       <c r="C8" s="8">
         <v>0.33333333333333331</v>
       </c>
       <c r="D8" s="55">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="166"/>
-      <c r="F8" s="123"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="191"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="124"/>
-      <c r="K8" s="123"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="182"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="128"/>
     </row>
     <row r="9" spans="1:11" ht="14.4">
       <c r="A9" s="1"/>
@@ -15397,11 +15397,11 @@
       <c r="H9" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I9" s="181" t="s">
+      <c r="I9" s="185" t="s">
         <v>117</v>
       </c>
-      <c r="J9" s="146"/>
-      <c r="K9" s="178"/>
+      <c r="J9" s="154"/>
+      <c r="K9" s="184"/>
     </row>
     <row r="10" spans="1:11" ht="14.4">
       <c r="A10" s="82"/>
@@ -15427,11 +15427,11 @@
       <c r="H10" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I10" s="181" t="s">
+      <c r="I10" s="185" t="s">
         <v>118</v>
       </c>
-      <c r="J10" s="146"/>
-      <c r="K10" s="178"/>
+      <c r="J10" s="154"/>
+      <c r="K10" s="184"/>
     </row>
     <row r="11" spans="1:11" ht="14.4">
       <c r="A11" s="1"/>
@@ -15457,11 +15457,11 @@
       <c r="H11" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I11" s="181" t="s">
+      <c r="I11" s="185" t="s">
         <v>119</v>
       </c>
-      <c r="J11" s="146"/>
-      <c r="K11" s="178"/>
+      <c r="J11" s="154"/>
+      <c r="K11" s="184"/>
     </row>
     <row r="12" spans="1:11" ht="14.4">
       <c r="A12" s="1"/>
@@ -15487,11 +15487,11 @@
       <c r="H12" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I12" s="177" t="s">
+      <c r="I12" s="183" t="s">
         <v>120</v>
       </c>
-      <c r="J12" s="146"/>
-      <c r="K12" s="178"/>
+      <c r="J12" s="154"/>
+      <c r="K12" s="184"/>
     </row>
     <row r="13" spans="1:11" ht="21.75" customHeight="1">
       <c r="A13" s="1"/>
@@ -15511,9 +15511,9 @@
         <v>0</v>
       </c>
       <c r="H13" s="83"/>
-      <c r="I13" s="177"/>
-      <c r="J13" s="146"/>
-      <c r="K13" s="178"/>
+      <c r="I13" s="183"/>
+      <c r="J13" s="154"/>
+      <c r="K13" s="184"/>
     </row>
     <row r="14" spans="1:11" ht="21.75" customHeight="1">
       <c r="A14" s="1"/>
@@ -15533,9 +15533,9 @@
         <v>0</v>
       </c>
       <c r="H14" s="83"/>
-      <c r="I14" s="181"/>
-      <c r="J14" s="146"/>
-      <c r="K14" s="178"/>
+      <c r="I14" s="185"/>
+      <c r="J14" s="154"/>
+      <c r="K14" s="184"/>
     </row>
     <row r="15" spans="1:11" ht="14.4">
       <c r="A15" s="1"/>
@@ -15561,11 +15561,11 @@
       <c r="H15" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="181" t="s">
+      <c r="I15" s="185" t="s">
         <v>121</v>
       </c>
-      <c r="J15" s="146"/>
-      <c r="K15" s="178"/>
+      <c r="J15" s="154"/>
+      <c r="K15" s="184"/>
     </row>
     <row r="16" spans="1:11" ht="20.25" customHeight="1">
       <c r="A16" s="1"/>
@@ -15587,11 +15587,11 @@
       <c r="H16" s="93" t="s">
         <v>122</v>
       </c>
-      <c r="I16" s="181" t="s">
+      <c r="I16" s="185" t="s">
         <v>123</v>
       </c>
-      <c r="J16" s="146"/>
-      <c r="K16" s="178"/>
+      <c r="J16" s="154"/>
+      <c r="K16" s="184"/>
     </row>
     <row r="17" spans="1:11" ht="14.4">
       <c r="A17" s="1"/>
@@ -15617,11 +15617,11 @@
       <c r="H17" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="192" t="s">
+      <c r="I17" s="199" t="s">
         <v>124</v>
       </c>
-      <c r="J17" s="146"/>
-      <c r="K17" s="178"/>
+      <c r="J17" s="154"/>
+      <c r="K17" s="184"/>
     </row>
     <row r="18" spans="1:11" ht="14.4">
       <c r="A18" s="1"/>
@@ -15647,11 +15647,11 @@
       <c r="H18" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="181" t="s">
+      <c r="I18" s="185" t="s">
         <v>121</v>
       </c>
-      <c r="J18" s="146"/>
-      <c r="K18" s="178"/>
+      <c r="J18" s="154"/>
+      <c r="K18" s="184"/>
     </row>
     <row r="19" spans="1:11" ht="14.4">
       <c r="A19" s="1"/>
@@ -15677,11 +15677,11 @@
       <c r="H19" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I19" s="181" t="s">
+      <c r="I19" s="185" t="s">
         <v>125</v>
       </c>
-      <c r="J19" s="146"/>
-      <c r="K19" s="178"/>
+      <c r="J19" s="154"/>
+      <c r="K19" s="184"/>
     </row>
     <row r="20" spans="1:11" ht="21.75" customHeight="1">
       <c r="A20" s="1"/>
@@ -15701,9 +15701,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="83"/>
-      <c r="I20" s="181"/>
-      <c r="J20" s="146"/>
-      <c r="K20" s="178"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="154"/>
+      <c r="K20" s="184"/>
     </row>
     <row r="21" spans="1:11" ht="21.75" customHeight="1">
       <c r="A21" s="1"/>
@@ -15723,9 +15723,9 @@
         <v>0</v>
       </c>
       <c r="H21" s="83"/>
-      <c r="I21" s="181"/>
-      <c r="J21" s="146"/>
-      <c r="K21" s="178"/>
+      <c r="I21" s="185"/>
+      <c r="J21" s="154"/>
+      <c r="K21" s="184"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
@@ -15751,11 +15751,11 @@
       <c r="H22" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="181" t="s">
+      <c r="I22" s="185" t="s">
         <v>126</v>
       </c>
-      <c r="J22" s="146"/>
-      <c r="K22" s="178"/>
+      <c r="J22" s="154"/>
+      <c r="K22" s="184"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
       <c r="A23" s="1"/>
@@ -15781,11 +15781,11 @@
       <c r="H23" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="181" t="s">
+      <c r="I23" s="185" t="s">
         <v>127</v>
       </c>
-      <c r="J23" s="146"/>
-      <c r="K23" s="178"/>
+      <c r="J23" s="154"/>
+      <c r="K23" s="184"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
@@ -15811,11 +15811,11 @@
       <c r="H24" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="181" t="s">
+      <c r="I24" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J24" s="146"/>
-      <c r="K24" s="178"/>
+      <c r="J24" s="154"/>
+      <c r="K24" s="184"/>
     </row>
     <row r="25" spans="1:11" ht="21.75" customHeight="1">
       <c r="A25" s="1"/>
@@ -15835,9 +15835,9 @@
         <v>0</v>
       </c>
       <c r="H25" s="83"/>
-      <c r="I25" s="181"/>
-      <c r="J25" s="146"/>
-      <c r="K25" s="178"/>
+      <c r="I25" s="185"/>
+      <c r="J25" s="154"/>
+      <c r="K25" s="184"/>
     </row>
     <row r="26" spans="1:11" ht="31.5" customHeight="1">
       <c r="A26" s="1"/>
@@ -15863,11 +15863,11 @@
       <c r="H26" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="181" t="s">
+      <c r="I26" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J26" s="146"/>
-      <c r="K26" s="178"/>
+      <c r="J26" s="154"/>
+      <c r="K26" s="184"/>
     </row>
     <row r="27" spans="1:11" ht="21.75" customHeight="1">
       <c r="A27" s="1"/>
@@ -15887,9 +15887,9 @@
         <v>0</v>
       </c>
       <c r="H27" s="83"/>
-      <c r="I27" s="181"/>
-      <c r="J27" s="146"/>
-      <c r="K27" s="178"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="154"/>
+      <c r="K27" s="184"/>
     </row>
     <row r="28" spans="1:11" ht="21.75" customHeight="1">
       <c r="A28" s="1"/>
@@ -15909,9 +15909,9 @@
         <v>0</v>
       </c>
       <c r="H28" s="83"/>
-      <c r="I28" s="181"/>
-      <c r="J28" s="146"/>
-      <c r="K28" s="178"/>
+      <c r="I28" s="185"/>
+      <c r="J28" s="154"/>
+      <c r="K28" s="184"/>
     </row>
     <row r="29" spans="1:11" ht="29.25" customHeight="1">
       <c r="A29" s="1"/>
@@ -15937,11 +15937,11 @@
       <c r="H29" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="181" t="s">
+      <c r="I29" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J29" s="146"/>
-      <c r="K29" s="178"/>
+      <c r="J29" s="154"/>
+      <c r="K29" s="184"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
@@ -15967,11 +15967,11 @@
       <c r="H30" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I30" s="181" t="s">
+      <c r="I30" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J30" s="146"/>
-      <c r="K30" s="178"/>
+      <c r="J30" s="154"/>
+      <c r="K30" s="184"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1">
       <c r="A31" s="1"/>
@@ -15997,11 +15997,11 @@
       <c r="H31" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I31" s="181" t="s">
+      <c r="I31" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J31" s="146"/>
-      <c r="K31" s="178"/>
+      <c r="J31" s="154"/>
+      <c r="K31" s="184"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="1"/>
@@ -16027,11 +16027,11 @@
       <c r="H32" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I32" s="181" t="s">
+      <c r="I32" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="J32" s="146"/>
-      <c r="K32" s="178"/>
+      <c r="J32" s="154"/>
+      <c r="K32" s="184"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1">
       <c r="A33" s="1"/>
@@ -16057,11 +16057,11 @@
       <c r="H33" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="I33" s="181" t="s">
+      <c r="I33" s="185" t="s">
         <v>129</v>
       </c>
-      <c r="J33" s="146"/>
-      <c r="K33" s="178"/>
+      <c r="J33" s="154"/>
+      <c r="K33" s="184"/>
     </row>
     <row r="34" spans="1:11" ht="21.75" customHeight="1">
       <c r="A34" s="1"/>
@@ -16081,9 +16081,9 @@
         <v>0</v>
       </c>
       <c r="H34" s="83"/>
-      <c r="I34" s="181"/>
-      <c r="J34" s="146"/>
-      <c r="K34" s="178"/>
+      <c r="I34" s="185"/>
+      <c r="J34" s="154"/>
+      <c r="K34" s="184"/>
     </row>
     <row r="35" spans="1:11" ht="21.75" customHeight="1">
       <c r="A35" s="1"/>
@@ -16103,9 +16103,9 @@
         <v>0</v>
       </c>
       <c r="H35" s="83"/>
-      <c r="I35" s="181"/>
-      <c r="J35" s="146"/>
-      <c r="K35" s="178"/>
+      <c r="I35" s="185"/>
+      <c r="J35" s="154"/>
+      <c r="K35" s="184"/>
     </row>
     <row r="36" spans="1:11" ht="21.75" customHeight="1">
       <c r="A36" s="1"/>
@@ -16127,11 +16127,11 @@
       <c r="H36" s="93" t="s">
         <v>115</v>
       </c>
-      <c r="I36" s="181" t="s">
+      <c r="I36" s="185" t="s">
         <v>130</v>
       </c>
-      <c r="J36" s="146"/>
-      <c r="K36" s="178"/>
+      <c r="J36" s="154"/>
+      <c r="K36" s="184"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1">
       <c r="A37" s="1"/>
@@ -16157,11 +16157,11 @@
       <c r="H37" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I37" s="181" t="s">
+      <c r="I37" s="185" t="s">
         <v>131</v>
       </c>
-      <c r="J37" s="146"/>
-      <c r="K37" s="178"/>
+      <c r="J37" s="154"/>
+      <c r="K37" s="184"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1">
       <c r="A38" s="1"/>
@@ -16187,21 +16187,21 @@
       <c r="H38" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="I38" s="181" t="s">
+      <c r="I38" s="185" t="s">
         <v>132</v>
       </c>
-      <c r="J38" s="146"/>
-      <c r="K38" s="178"/>
+      <c r="J38" s="154"/>
+      <c r="K38" s="184"/>
     </row>
     <row r="39" spans="1:11" ht="18" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="199" t="s">
+      <c r="B39" s="192" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="124"/>
-      <c r="D39" s="124"/>
-      <c r="E39" s="124"/>
-      <c r="F39" s="159"/>
+      <c r="C39" s="132"/>
+      <c r="D39" s="132"/>
+      <c r="E39" s="132"/>
+      <c r="F39" s="167"/>
       <c r="G39" s="91">
         <f>SUM(G9:G38)</f>
         <v>152</v>
@@ -16221,12 +16221,12 @@
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
       <c r="G40" s="23"/>
-      <c r="H40" s="196" t="s">
+      <c r="H40" s="193" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="133"/>
-      <c r="J40" s="133"/>
-      <c r="K40" s="134"/>
+      <c r="I40" s="134"/>
+      <c r="J40" s="134"/>
+      <c r="K40" s="135"/>
     </row>
     <row r="41" spans="1:11" ht="20.25" customHeight="1">
       <c r="A41" s="1"/>
@@ -16240,12 +16240,12 @@
       <c r="G41" s="26">
         <v>21</v>
       </c>
-      <c r="H41" s="197" t="s">
+      <c r="H41" s="194" t="s">
         <v>17</v>
       </c>
-      <c r="I41" s="126"/>
-      <c r="J41" s="126"/>
-      <c r="K41" s="127"/>
+      <c r="I41" s="125"/>
+      <c r="J41" s="125"/>
+      <c r="K41" s="124"/>
     </row>
     <row r="42" spans="1:11" ht="20.25" customHeight="1">
       <c r="A42" s="1"/>
@@ -16259,10 +16259,10 @@
       <c r="G42" s="27">
         <v>9</v>
       </c>
-      <c r="H42" s="126"/>
-      <c r="I42" s="126"/>
-      <c r="J42" s="126"/>
-      <c r="K42" s="127"/>
+      <c r="H42" s="125"/>
+      <c r="I42" s="125"/>
+      <c r="J42" s="125"/>
+      <c r="K42" s="124"/>
     </row>
     <row r="43" spans="1:11" ht="20.25" customHeight="1">
       <c r="A43" s="1"/>
@@ -16276,10 +16276,10 @@
       <c r="G43" s="27">
         <v>1</v>
       </c>
-      <c r="H43" s="124"/>
-      <c r="I43" s="124"/>
-      <c r="J43" s="124"/>
-      <c r="K43" s="123"/>
+      <c r="H43" s="132"/>
+      <c r="I43" s="132"/>
+      <c r="J43" s="132"/>
+      <c r="K43" s="128"/>
     </row>
     <row r="44" spans="1:11" ht="20.25" customHeight="1">
       <c r="A44" s="1"/>
@@ -16312,7 +16312,7 @@
       <c r="G45" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H45" s="197" t="s">
+      <c r="H45" s="194" t="s">
         <v>23</v>
       </c>
       <c r="I45" s="1"/>
@@ -16331,7 +16331,7 @@
       <c r="G46" s="27">
         <v>19</v>
       </c>
-      <c r="H46" s="124"/>
+      <c r="H46" s="132"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="48"/>
@@ -16352,10 +16352,10 @@
       <c r="H47" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="I47" s="171" t="s">
+      <c r="I47" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="J47" s="172"/>
+      <c r="J47" s="140"/>
       <c r="K47" s="32" t="s">
         <v>28</v>
       </c>
@@ -16373,10 +16373,10 @@
       <c r="H48" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="I48" s="163" t="s">
+      <c r="I48" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="J48" s="127"/>
+      <c r="J48" s="124"/>
       <c r="K48" s="37" t="s">
         <v>29</v>
       </c>
@@ -16396,10 +16396,10 @@
       <c r="H49" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="I49" s="163" t="s">
+      <c r="I49" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="J49" s="127"/>
+      <c r="J49" s="124"/>
       <c r="K49" s="37" t="s">
         <v>31</v>
       </c>
@@ -16420,10 +16420,10 @@
       <c r="H50" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="I50" s="163" t="s">
+      <c r="I50" s="126" t="s">
         <v>33</v>
       </c>
-      <c r="J50" s="127"/>
+      <c r="J50" s="124"/>
       <c r="K50" s="37" t="s">
         <v>33</v>
       </c>
@@ -16444,10 +16444,10 @@
       <c r="H51" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="I51" s="164" t="s">
+      <c r="I51" s="127" t="s">
         <v>35</v>
       </c>
-      <c r="J51" s="123"/>
+      <c r="J51" s="128"/>
       <c r="K51" s="43" t="s">
         <v>35</v>
       </c>
@@ -16470,23 +16470,23 @@
       <c r="B53" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C53" s="161" t="s">
+      <c r="C53" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="D53" s="127"/>
-      <c r="E53" s="161" t="s">
+      <c r="D53" s="124"/>
+      <c r="E53" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="F53" s="126"/>
-      <c r="G53" s="127"/>
-      <c r="H53" s="198" t="s">
+      <c r="F53" s="125"/>
+      <c r="G53" s="124"/>
+      <c r="H53" s="195" t="s">
         <v>38</v>
       </c>
-      <c r="I53" s="127"/>
-      <c r="J53" s="161" t="s">
+      <c r="I53" s="124"/>
+      <c r="J53" s="122" t="s">
         <v>106</v>
       </c>
-      <c r="K53" s="127"/>
+      <c r="K53" s="124"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1">
       <c r="A54" s="1"/>
@@ -16543,42 +16543,42 @@
     <row r="58" spans="1:11" ht="15.75" customHeight="1">
       <c r="A58" s="51"/>
       <c r="B58" s="52"/>
-      <c r="C58" s="125" t="s">
+      <c r="C58" s="170" t="s">
         <v>143</v>
       </c>
-      <c r="D58" s="127"/>
-      <c r="E58" s="125" t="s">
+      <c r="D58" s="124"/>
+      <c r="E58" s="170" t="s">
         <v>108</v>
       </c>
-      <c r="F58" s="126"/>
-      <c r="G58" s="127"/>
-      <c r="H58" s="194" t="s">
+      <c r="F58" s="125"/>
+      <c r="G58" s="124"/>
+      <c r="H58" s="196" t="s">
         <v>109</v>
       </c>
-      <c r="I58" s="127"/>
-      <c r="J58" s="125" t="s">
+      <c r="I58" s="124"/>
+      <c r="J58" s="170" t="s">
         <v>110</v>
       </c>
-      <c r="K58" s="127"/>
+      <c r="K58" s="124"/>
     </row>
     <row r="59" spans="1:11" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="53"/>
-      <c r="C59" s="122"/>
-      <c r="D59" s="123"/>
-      <c r="E59" s="122" t="s">
+      <c r="C59" s="169"/>
+      <c r="D59" s="128"/>
+      <c r="E59" s="169" t="s">
         <v>111</v>
       </c>
-      <c r="F59" s="124"/>
-      <c r="G59" s="123"/>
-      <c r="H59" s="195" t="s">
+      <c r="F59" s="132"/>
+      <c r="G59" s="128"/>
+      <c r="H59" s="197" t="s">
         <v>112</v>
       </c>
-      <c r="I59" s="123"/>
-      <c r="J59" s="122" t="s">
+      <c r="I59" s="128"/>
+      <c r="J59" s="169" t="s">
         <v>113</v>
       </c>
-      <c r="K59" s="123"/>
+      <c r="K59" s="128"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
@@ -19923,11 +19923,54 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="E2:H3"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="J59:K59"/>
     <mergeCell ref="H40:K40"/>
     <mergeCell ref="H41:K43"/>
     <mergeCell ref="E53:G53"/>
@@ -19939,54 +19982,11 @@
     <mergeCell ref="I49:J49"/>
     <mergeCell ref="I50:J50"/>
     <mergeCell ref="I51:J51"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B2:D5"/>
-    <mergeCell ref="E2:H3"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="B39:F39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
